--- a/Convolution-Radiomics-Wavelet.xlsx
+++ b/Convolution-Radiomics-Wavelet.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BN\Documents\univ\講義\AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HN-Data-1\教育\講義\講義2年生-AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45ED7017-9DE1-4D3C-A318-859D04368D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C85957D-9932-4E37-8636-05352A0549D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="3" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
   </bookViews>
   <sheets>
-    <sheet name="演習・確認用" sheetId="2" r:id="rId1"/>
-    <sheet name="完成版" sheetId="4" r:id="rId2"/>
-    <sheet name="GLCM-右隣り" sheetId="5" r:id="rId3"/>
-    <sheet name="GLCM-角度指定" sheetId="6" r:id="rId4"/>
-    <sheet name="GLCM-8近傍（簡易版）" sheetId="9" r:id="rId5"/>
-    <sheet name="参考 GLCM（正規版）の例" sheetId="10" r:id="rId6"/>
-    <sheet name="2D-Wavelet" sheetId="8" r:id="rId7"/>
+    <sheet name="目次" sheetId="11" r:id="rId1"/>
+    <sheet name="演習・確認用" sheetId="2" r:id="rId2"/>
+    <sheet name="完成版" sheetId="4" r:id="rId3"/>
+    <sheet name="GLCM-右隣り" sheetId="5" r:id="rId4"/>
+    <sheet name="GLCM-角度指定" sheetId="6" r:id="rId5"/>
+    <sheet name="GLCM-8近傍（簡易版）" sheetId="9" r:id="rId6"/>
+    <sheet name="参考 GLCM（正規版）の例" sheetId="10" r:id="rId7"/>
+    <sheet name="2D-Wavelet" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="111">
   <si>
     <t>畳み込みフィルタの数値データによる確認シート（By H.Nishiyama / Niigata Univ. 2024/11/29, Ver 1.0）</t>
     <rPh sb="0" eb="1">
@@ -1372,7 +1373,21 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>量子化レベル数：4での8近傍GLCMの各種ソフトでの通常の計算手順と結果例（By H.Nishiyama / Niigata Univ. 2026/06/27, Ver 2.1）</t>
+    <t>↑値</t>
+    <rPh sb="1" eb="2">
+      <t>アタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>↑差</t>
+    <rPh sb="1" eb="2">
+      <t>サ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>量子化レベル数：4での8近傍GLCMの各種ソフトでの通常の計算手順と結果例（By H.Nishiyama / Niigata Univ. 2026/07/05, Ver 2.2）</t>
     <rPh sb="0" eb="3">
       <t>リョウシカ</t>
     </rPh>
@@ -1399,6 +1414,110 @@
     </rPh>
     <rPh sb="36" eb="37">
       <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>畳み込みフィルタ</t>
+    <rPh sb="0" eb="1">
+      <t>タタ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RadiomicsのGLCM</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[目次へ]</t>
+    <rPh sb="1" eb="3">
+      <t>モクジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（By H.Nishiyama / Niigata Univ. 2026/07/05, Ver 2.2）</t>
+  </si>
+  <si>
+    <t>演習・確認用 --- 畳み込みフィルタの数値データによる確認シート</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>カクニンヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>完成版 --- 畳み込みフィルタの数値データによる確認シート</t>
+    <rPh sb="0" eb="3">
+      <t>カンセイバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GLCM-右隣限定 --- 量子化レベル数：4（画素値：1～4）でのRadiomics特徴量の例（GLCM：右隣）</t>
+    <rPh sb="5" eb="7">
+      <t>ミギドナリ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ゲンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GLCM-角度指定 --- 量子化レベル数：4（画素値：1～4）でのRadiomics特徴量の例（GLCM：８近傍・角度指定）</t>
+    <rPh sb="5" eb="7">
+      <t>カクド</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GLCM-8近傍(簡易版) --- 量子化レベル数：4（画素値：1～4）でのRadiomics特徴量の例（GLCM：８近傍）</t>
+    <rPh sb="6" eb="8">
+      <t>キンボウ</t>
+    </rPh>
+    <rPh sb="9" eb="12">
+      <t>カンイバン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>参考GLCM（正規版）の例 --- 量子化レベル数：4での8近傍GLCMの各種ソフトでの通常の計算手順と結果例</t>
+    <rPh sb="0" eb="2">
+      <t>サンコウ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>セイキバン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2D-Wavelet --- ハール（Haar）ウェーブレットの数値データによる確認シート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2年生・画像処理におけるAI・参考資料・目次</t>
+    <rPh sb="1" eb="3">
+      <t>ネンセイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>サンコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>モクジ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2766,7 +2885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="281">
+  <cellXfs count="283">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3515,33 +3634,6 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3569,6 +3661,24 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3585,6 +3695,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3637,6 +3756,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4782,13 +4907,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>62753</xdr:colOff>
+      <xdr:colOff>62754</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>62751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>376518</xdr:colOff>
+      <xdr:colOff>324972</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>170330</xdr:rowOff>
     </xdr:to>
@@ -4805,8 +4930,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="340659" y="5011269"/>
-          <a:ext cx="14782800" cy="1550896"/>
+          <a:off x="365313" y="4903692"/>
+          <a:ext cx="16443512" cy="1519520"/>
         </a:xfrm>
         <a:prstGeom prst="uturnArrow">
           <a:avLst>
@@ -4860,13 +4985,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>144827</xdr:colOff>
+      <xdr:colOff>178445</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>52552</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
-      <xdr:colOff>320565</xdr:colOff>
+      <xdr:colOff>354183</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -4883,8 +5008,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="13634314" y="2484383"/>
-          <a:ext cx="2215518" cy="650867"/>
+          <a:off x="15403722" y="2398098"/>
+          <a:ext cx="2166213" cy="702415"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4987,6 +5112,153 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>652181</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>142314</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>459441</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>33617</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22625A8F-F8F5-66C6-E923-9E9650FFC93A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15242240" y="5588373"/>
+          <a:ext cx="2227730" cy="294715"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>`weightingNorm` = 'no_weighting'</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>44824</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>48184</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>981634</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>78441</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="テキスト ボックス 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE5A9BA1-4300-4066-9CBE-9B885751E857}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8426824" y="1661831"/>
+          <a:ext cx="1620369" cy="231963"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+            <a:t>`weightingNorm` = None</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -6333,15 +6605,97 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AC3236B-8782-403C-A43D-DC2DBF2CC73B}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="2" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C4" s="281" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C5" s="281" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C7" s="281" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C8" s="281" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C9" s="281" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="C10" s="281" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="B11" s="281" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="Oh/wyZBJM5QXqBYt/YMfLyL775haBs3z05CTY8EsL5+tBU3eVRuXMx35sIFjv+Ro+u7B8n+9aqyMZz5VtnOmng==" saltValue="tfBPuFgM89XraVHWdEg+jQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="C4" location="演習・確認用!A1" display="演習・確認用" xr:uid="{05CA92A6-2BA4-4345-812D-B9966056781D}"/>
+    <hyperlink ref="C5" location="完成版!A1" display="完成版" xr:uid="{22B87359-16FD-442F-9617-0112844A2AC2}"/>
+    <hyperlink ref="C7" location="'GLCM-右隣り'!A1" display="GLCM-右隣限定" xr:uid="{201A695C-177F-481A-A25B-08109B979B39}"/>
+    <hyperlink ref="C8" location="'GLCM-角度指定'!A1" display="GLCM-角度指定" xr:uid="{E14A77BF-4C78-491A-B986-802AA11F6F4B}"/>
+    <hyperlink ref="C9" location="'GLCM-8近傍（簡易版）'!A1" display="GLCM-8近傍(簡易版)" xr:uid="{1D5B5307-4A37-44A3-89B4-C010D515279B}"/>
+    <hyperlink ref="C10" location="'参考 GLCM（正規版）の例'!A1" display="参考GLCM（正規版）の例" xr:uid="{6E275308-997E-4B92-9184-A9D06CFEF301}"/>
+    <hyperlink ref="B11" location="'2D-Wavelet'!A1" display="2D-Wavelet" xr:uid="{BD902995-0745-46D9-9042-EE99A17A981C}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B670EFBA-54F0-42F8-82FF-C2CDC326B627}">
   <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="29" width="4.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="29" width="4.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
@@ -6373,7 +6727,7 @@
       <c r="AB1" s="19"/>
       <c r="AC1" s="19"/>
     </row>
-    <row r="2" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -6402,7 +6756,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -6424,7 +6778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -6465,7 +6819,7 @@
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
     </row>
-    <row r="5" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -6519,7 +6873,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <f t="shared" ref="B6:I13" si="1">L6</f>
         <v>1</v>
@@ -6594,7 +6948,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6669,7 +7023,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6742,7 +7096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6817,7 +7171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6883,7 +7237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -6949,7 +7303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -7015,7 +7369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -7081,7 +7435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="K14" s="20">
         <f>(K13+L14)/2</f>
         <v>1</v>
@@ -7131,23 +7485,23 @@
       <c r="AB14" s="39"/>
       <c r="AC14" s="40"/>
     </row>
-    <row r="15" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="249" t="s">
+      <c r="X15" s="240" t="s">
         <v>19</v>
       </c>
-      <c r="Y15" s="250"/>
-      <c r="Z15" s="250"/>
-      <c r="AA15" s="250"/>
-      <c r="AB15" s="250"/>
-      <c r="AC15" s="251"/>
+      <c r="Y15" s="241"/>
+      <c r="Z15" s="241"/>
+      <c r="AA15" s="241"/>
+      <c r="AB15" s="241"/>
+      <c r="AC15" s="242"/>
     </row>
-    <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <f t="shared" ref="B16:I23" si="5">L16</f>
         <v>1</v>
@@ -7191,14 +7545,14 @@
       <c r="Q16" s="49"/>
       <c r="R16" s="49"/>
       <c r="S16" s="49"/>
-      <c r="X16" s="252"/>
-      <c r="Y16" s="253"/>
-      <c r="Z16" s="253"/>
-      <c r="AA16" s="253"/>
-      <c r="AB16" s="253"/>
-      <c r="AC16" s="254"/>
+      <c r="X16" s="243"/>
+      <c r="Y16" s="244"/>
+      <c r="Z16" s="244"/>
+      <c r="AA16" s="244"/>
+      <c r="AB16" s="244"/>
+      <c r="AC16" s="245"/>
     </row>
-    <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7239,14 +7593,14 @@
       <c r="Q17" s="49"/>
       <c r="R17" s="49"/>
       <c r="S17" s="49"/>
-      <c r="X17" s="252"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
-      <c r="AA17" s="253"/>
-      <c r="AB17" s="253"/>
-      <c r="AC17" s="254"/>
+      <c r="X17" s="243"/>
+      <c r="Y17" s="244"/>
+      <c r="Z17" s="244"/>
+      <c r="AA17" s="244"/>
+      <c r="AB17" s="244"/>
+      <c r="AC17" s="245"/>
     </row>
-    <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7287,14 +7641,14 @@
       <c r="Q18" s="49"/>
       <c r="R18" s="49"/>
       <c r="S18" s="49"/>
-      <c r="X18" s="252"/>
-      <c r="Y18" s="253"/>
-      <c r="Z18" s="253"/>
-      <c r="AA18" s="253"/>
-      <c r="AB18" s="253"/>
-      <c r="AC18" s="254"/>
+      <c r="X18" s="243"/>
+      <c r="Y18" s="244"/>
+      <c r="Z18" s="244"/>
+      <c r="AA18" s="244"/>
+      <c r="AB18" s="244"/>
+      <c r="AC18" s="245"/>
     </row>
-    <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7335,14 +7689,14 @@
       <c r="Q19" s="49"/>
       <c r="R19" s="49"/>
       <c r="S19" s="49"/>
-      <c r="X19" s="252"/>
-      <c r="Y19" s="253"/>
-      <c r="Z19" s="253"/>
-      <c r="AA19" s="253"/>
-      <c r="AB19" s="253"/>
-      <c r="AC19" s="254"/>
+      <c r="X19" s="243"/>
+      <c r="Y19" s="244"/>
+      <c r="Z19" s="244"/>
+      <c r="AA19" s="244"/>
+      <c r="AB19" s="244"/>
+      <c r="AC19" s="245"/>
     </row>
-    <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7383,14 +7737,14 @@
       <c r="Q20" s="49"/>
       <c r="R20" s="49"/>
       <c r="S20" s="49"/>
-      <c r="X20" s="252"/>
-      <c r="Y20" s="253"/>
-      <c r="Z20" s="253"/>
-      <c r="AA20" s="253"/>
-      <c r="AB20" s="253"/>
-      <c r="AC20" s="254"/>
+      <c r="X20" s="243"/>
+      <c r="Y20" s="244"/>
+      <c r="Z20" s="244"/>
+      <c r="AA20" s="244"/>
+      <c r="AB20" s="244"/>
+      <c r="AC20" s="245"/>
     </row>
-    <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7431,14 +7785,14 @@
       <c r="Q21" s="49"/>
       <c r="R21" s="49"/>
       <c r="S21" s="49"/>
-      <c r="X21" s="252"/>
-      <c r="Y21" s="253"/>
-      <c r="Z21" s="253"/>
-      <c r="AA21" s="253"/>
-      <c r="AB21" s="253"/>
-      <c r="AC21" s="254"/>
+      <c r="X21" s="243"/>
+      <c r="Y21" s="244"/>
+      <c r="Z21" s="244"/>
+      <c r="AA21" s="244"/>
+      <c r="AB21" s="244"/>
+      <c r="AC21" s="245"/>
     </row>
-    <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7479,14 +7833,14 @@
       <c r="Q22" s="49"/>
       <c r="R22" s="49"/>
       <c r="S22" s="49"/>
-      <c r="X22" s="252"/>
-      <c r="Y22" s="253"/>
-      <c r="Z22" s="253"/>
-      <c r="AA22" s="253"/>
-      <c r="AB22" s="253"/>
-      <c r="AC22" s="254"/>
+      <c r="X22" s="243"/>
+      <c r="Y22" s="244"/>
+      <c r="Z22" s="244"/>
+      <c r="AA22" s="244"/>
+      <c r="AB22" s="244"/>
+      <c r="AC22" s="245"/>
     </row>
-    <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -7527,14 +7881,14 @@
       <c r="Q23" s="49"/>
       <c r="R23" s="49"/>
       <c r="S23" s="49"/>
-      <c r="X23" s="255"/>
-      <c r="Y23" s="256"/>
-      <c r="Z23" s="256"/>
-      <c r="AA23" s="256"/>
-      <c r="AB23" s="256"/>
-      <c r="AC23" s="257"/>
+      <c r="X23" s="246"/>
+      <c r="Y23" s="247"/>
+      <c r="Z23" s="247"/>
+      <c r="AA23" s="247"/>
+      <c r="AB23" s="247"/>
+      <c r="AC23" s="248"/>
     </row>
-    <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -7550,7 +7904,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
     </row>
-    <row r="25" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
@@ -7573,7 +7927,7 @@
       <c r="S25" s="42"/>
       <c r="T25" s="43"/>
     </row>
-    <row r="26" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B26" s="44" t="s">
         <v>21</v>
       </c>
@@ -7597,7 +7951,7 @@
       <c r="T26" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="btIobjZ7u8l9IPSN0sy6+lWUQ/33EWGFMJHZ//Cz9AY68zwg8Nbh4stnTsSyCN6/2xjkUleG/IlMGxQX2lwm+g==" saltValue="RgEZh/wR8LYmaTmqcUk8DQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="fIi+k+lZSlZlCe8Mpm4Q1EVKURkOiLcEuXVMi8MDxFodCOJp3+nhf9lRp9zx64FA07N4JqFSApH0RVJMu61xxw==" saltValue="evwvXr8s1QUaE0EwvEhnfA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="X15:AC23"/>
   </mergeCells>
@@ -7618,22 +7972,28 @@
     </dataValidation>
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4 X5:Z7" xr:uid="{6A031A24-5A5F-4B42-99F6-700F8AD4C680}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{F986BA72-0D76-4699-9051-CF4AA1B9A1ED}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5297D6F5-6C1E-488B-8FB8-D42B93695DA4}">
   <dimension ref="A1:AC26"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="29" width="4.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="29" width="4.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
@@ -7665,7 +8025,7 @@
       <c r="AB1" s="19"/>
       <c r="AC1" s="19"/>
     </row>
-    <row r="2" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -7694,7 +8054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -7716,7 +8076,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
         <v>8</v>
       </c>
@@ -7757,7 +8117,7 @@
       <c r="Z4" s="16"/>
       <c r="AA4" s="16"/>
     </row>
-    <row r="5" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -7811,7 +8171,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <f t="shared" ref="B6:I13" si="1">L6</f>
         <v>1</v>
@@ -7886,7 +8246,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -7961,7 +8321,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8034,7 +8394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8109,7 +8469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8175,7 +8535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8241,7 +8601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8307,7 +8667,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -8373,7 +8733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="K14" s="20">
         <f>(K13+L14)/2</f>
         <v>1</v>
@@ -8423,23 +8783,23 @@
       <c r="AB14" s="39"/>
       <c r="AC14" s="40"/>
     </row>
-    <row r="15" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="249" t="s">
+      <c r="X15" s="240" t="s">
         <v>23</v>
       </c>
-      <c r="Y15" s="250"/>
-      <c r="Z15" s="250"/>
-      <c r="AA15" s="250"/>
-      <c r="AB15" s="250"/>
-      <c r="AC15" s="251"/>
+      <c r="Y15" s="241"/>
+      <c r="Z15" s="241"/>
+      <c r="AA15" s="241"/>
+      <c r="AB15" s="241"/>
+      <c r="AC15" s="242"/>
     </row>
-    <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
         <f t="shared" ref="B16:I23" si="5">L16</f>
         <v>1</v>
@@ -8504,14 +8864,14 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="X16" s="252"/>
-      <c r="Y16" s="253"/>
-      <c r="Z16" s="253"/>
-      <c r="AA16" s="253"/>
-      <c r="AB16" s="253"/>
-      <c r="AC16" s="254"/>
+      <c r="X16" s="243"/>
+      <c r="Y16" s="244"/>
+      <c r="Z16" s="244"/>
+      <c r="AA16" s="244"/>
+      <c r="AB16" s="244"/>
+      <c r="AC16" s="245"/>
     </row>
-    <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -8576,14 +8936,14 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="X17" s="252"/>
-      <c r="Y17" s="253"/>
-      <c r="Z17" s="253"/>
-      <c r="AA17" s="253"/>
-      <c r="AB17" s="253"/>
-      <c r="AC17" s="254"/>
+      <c r="X17" s="243"/>
+      <c r="Y17" s="244"/>
+      <c r="Z17" s="244"/>
+      <c r="AA17" s="244"/>
+      <c r="AB17" s="244"/>
+      <c r="AC17" s="245"/>
     </row>
-    <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -8648,14 +9008,14 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="X18" s="252"/>
-      <c r="Y18" s="253"/>
-      <c r="Z18" s="253"/>
-      <c r="AA18" s="253"/>
-      <c r="AB18" s="253"/>
-      <c r="AC18" s="254"/>
+      <c r="X18" s="243"/>
+      <c r="Y18" s="244"/>
+      <c r="Z18" s="244"/>
+      <c r="AA18" s="244"/>
+      <c r="AB18" s="244"/>
+      <c r="AC18" s="245"/>
     </row>
-    <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -8720,14 +9080,14 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="X19" s="252"/>
-      <c r="Y19" s="253"/>
-      <c r="Z19" s="253"/>
-      <c r="AA19" s="253"/>
-      <c r="AB19" s="253"/>
-      <c r="AC19" s="254"/>
+      <c r="X19" s="243"/>
+      <c r="Y19" s="244"/>
+      <c r="Z19" s="244"/>
+      <c r="AA19" s="244"/>
+      <c r="AB19" s="244"/>
+      <c r="AC19" s="245"/>
     </row>
-    <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -8792,14 +9152,14 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="X20" s="252"/>
-      <c r="Y20" s="253"/>
-      <c r="Z20" s="253"/>
-      <c r="AA20" s="253"/>
-      <c r="AB20" s="253"/>
-      <c r="AC20" s="254"/>
+      <c r="X20" s="243"/>
+      <c r="Y20" s="244"/>
+      <c r="Z20" s="244"/>
+      <c r="AA20" s="244"/>
+      <c r="AB20" s="244"/>
+      <c r="AC20" s="245"/>
     </row>
-    <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -8864,14 +9224,14 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="X21" s="252"/>
-      <c r="Y21" s="253"/>
-      <c r="Z21" s="253"/>
-      <c r="AA21" s="253"/>
-      <c r="AB21" s="253"/>
-      <c r="AC21" s="254"/>
+      <c r="X21" s="243"/>
+      <c r="Y21" s="244"/>
+      <c r="Z21" s="244"/>
+      <c r="AA21" s="244"/>
+      <c r="AB21" s="244"/>
+      <c r="AC21" s="245"/>
     </row>
-    <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -8936,14 +9296,14 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="X22" s="252"/>
-      <c r="Y22" s="253"/>
-      <c r="Z22" s="253"/>
-      <c r="AA22" s="253"/>
-      <c r="AB22" s="253"/>
-      <c r="AC22" s="254"/>
+      <c r="X22" s="243"/>
+      <c r="Y22" s="244"/>
+      <c r="Z22" s="244"/>
+      <c r="AA22" s="244"/>
+      <c r="AB22" s="244"/>
+      <c r="AC22" s="245"/>
     </row>
-    <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -9008,14 +9368,14 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="X23" s="255"/>
-      <c r="Y23" s="256"/>
-      <c r="Z23" s="256"/>
-      <c r="AA23" s="256"/>
-      <c r="AB23" s="256"/>
-      <c r="AC23" s="257"/>
+      <c r="X23" s="246"/>
+      <c r="Y23" s="247"/>
+      <c r="Z23" s="247"/>
+      <c r="AA23" s="247"/>
+      <c r="AB23" s="247"/>
+      <c r="AC23" s="248"/>
     </row>
-    <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
@@ -9031,7 +9391,7 @@
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
     </row>
-    <row r="25" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="41" t="s">
         <v>20</v>
       </c>
@@ -9054,7 +9414,7 @@
       <c r="S25" s="42"/>
       <c r="T25" s="43"/>
     </row>
-    <row r="26" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B26" s="44" t="s">
         <v>21</v>
       </c>
@@ -9078,7 +9438,7 @@
       <c r="T26" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="OsbN3ooLKwYi5NIHg3NE24wNpcXnBAhpoCZ7jpsh9kB0t3vnmHOJyCB+Zfa0fqrexl9wivU3KwaCOmk0jDb79g==" saltValue="4Xyy5UKVCCinhO7CbyiG8g==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="VXMW/twfHXicmEDIUix0D6fJ0gg6vg+N/TjfvpzAMWPVPr2ueyKFuai5Vp+EkqDiF2ocvNBAscZaPDmYbW6AaA==" saltValue="7yumMwkox+k8ZKk7NTzNuA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="X15:AC23"/>
   </mergeCells>
@@ -9099,23 +9459,29 @@
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{65477C5D-5CC2-4E38-84F4-C2C9DFDE1204}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5D03243-5B3F-4FDF-873F-4B17BDA33052}">
   <dimension ref="A1:AU55"/>
-  <sheetFormatPr defaultColWidth="4.33203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="42" max="42" width="8.33203125" customWidth="1"/>
-    <col min="44" max="47" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.375" customWidth="1"/>
+    <col min="44" max="47" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
         <v>73</v>
       </c>
@@ -9151,7 +9517,7 @@
       <c r="AF1" s="19"/>
       <c r="AG1" s="19"/>
     </row>
-    <row r="2" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -9173,7 +9539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -9184,7 +9550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="28" t="s">
         <v>8</v>
       </c>
@@ -9218,7 +9584,7 @@
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
     </row>
-    <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -9233,7 +9599,7 @@
       <c r="S5" s="20"/>
       <c r="T5" s="20"/>
     </row>
-    <row r="6" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B6" s="1">
         <f t="shared" ref="B6:I13" si="0">L6</f>
         <v>1</v>
@@ -9293,7 +9659,7 @@
       </c>
       <c r="T6" s="20"/>
     </row>
-    <row r="7" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -9353,7 +9719,7 @@
       </c>
       <c r="T7" s="20"/>
     </row>
-    <row r="8" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -9419,7 +9785,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -9478,27 +9844,27 @@
         <v>1</v>
       </c>
       <c r="T9" s="20"/>
-      <c r="X9" s="242" t="s">
+      <c r="X9" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
-      <c r="AA9" s="244"/>
-      <c r="AF9" s="242" t="s">
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
+      <c r="AA9" s="254"/>
+      <c r="AF9" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="243"/>
-      <c r="AH9" s="243"/>
-      <c r="AI9" s="244"/>
-      <c r="AL9" s="258" t="s">
+      <c r="AG9" s="253"/>
+      <c r="AH9" s="253"/>
+      <c r="AI9" s="254"/>
+      <c r="AL9" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="259"/>
-      <c r="AN9" s="259"/>
-      <c r="AO9" s="259"/>
-      <c r="AP9" s="260"/>
+      <c r="AM9" s="256"/>
+      <c r="AN9" s="256"/>
+      <c r="AO9" s="256"/>
+      <c r="AP9" s="257"/>
     </row>
-    <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -9581,16 +9947,16 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="261"/>
-      <c r="AM10" s="262"/>
-      <c r="AN10" s="262"/>
-      <c r="AO10" s="262"/>
-      <c r="AP10" s="263"/>
+      <c r="AL10" s="258"/>
+      <c r="AM10" s="259"/>
+      <c r="AN10" s="259"/>
+      <c r="AO10" s="259"/>
+      <c r="AP10" s="260"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <f t="shared" si="0"/>
         <v>1</v>
@@ -9649,7 +10015,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="20"/>
-      <c r="V11" s="245" t="s">
+      <c r="V11" s="249" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -9671,7 +10037,7 @@
         <f>SUM(AC17:AI24)</f>
         <v>1</v>
       </c>
-      <c r="AD11" s="245" t="s">
+      <c r="AD11" s="249" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -9720,7 +10086,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -9779,7 +10145,7 @@
         <v>3</v>
       </c>
       <c r="T12" s="20"/>
-      <c r="V12" s="246"/>
+      <c r="V12" s="250"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -9799,7 +10165,7 @@
         <f>SUM(AC27:AI34)</f>
         <v>4</v>
       </c>
-      <c r="AD12" s="246"/>
+      <c r="AD12" s="250"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -9846,7 +10212,7 @@
         <v>-0.27195392300411458</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -9905,7 +10271,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="20"/>
-      <c r="V13" s="246"/>
+      <c r="V13" s="250"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -9925,7 +10291,7 @@
         <f>SUM(AC37:AI44)</f>
         <v>1</v>
       </c>
-      <c r="AD13" s="246"/>
+      <c r="AD13" s="250"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -9972,7 +10338,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="K14" s="20"/>
       <c r="L14" s="20"/>
       <c r="M14" s="20"/>
@@ -9983,7 +10349,7 @@
       <c r="R14" s="20"/>
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
-      <c r="V14" s="247"/>
+      <c r="V14" s="251"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -10003,7 +10369,7 @@
         <f>SUM(AC47:AI54)</f>
         <v>1</v>
       </c>
-      <c r="AD14" s="247"/>
+      <c r="AD14" s="251"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -10050,7 +10416,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="82" t="s">
         <v>48</v>
       </c>
@@ -10090,7 +10456,7 @@
       <c r="AI15" s="82"/>
       <c r="AJ15" s="82"/>
     </row>
-    <row r="16" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="82">
         <v>1</v>
       </c>
@@ -10164,7 +10530,7 @@
       <c r="AI16" s="82"/>
       <c r="AJ16" s="82"/>
     </row>
-    <row r="17" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="82"/>
       <c r="B17" s="84">
         <f>IF(AND(L6=$A$16,M6=$C$16),1,0)</f>
@@ -10286,7 +10652,7 @@
       </c>
       <c r="AJ17" s="82"/>
     </row>
-    <row r="18" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="82"/>
       <c r="B18" s="87">
         <f t="shared" ref="B18:B24" si="7">IF(AND(L7=$A$16,M7=$C$16),1,0)</f>
@@ -10408,7 +10774,7 @@
       </c>
       <c r="AJ18" s="82"/>
     </row>
-    <row r="19" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="82"/>
       <c r="B19" s="86">
         <f t="shared" si="7"/>
@@ -10530,7 +10896,7 @@
       </c>
       <c r="AJ19" s="82"/>
     </row>
-    <row r="20" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="82"/>
       <c r="B20" s="86">
         <f t="shared" si="7"/>
@@ -10652,7 +11018,7 @@
       </c>
       <c r="AJ20" s="82"/>
     </row>
-    <row r="21" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="82"/>
       <c r="B21" s="86">
         <f t="shared" si="7"/>
@@ -10774,7 +11140,7 @@
       </c>
       <c r="AJ21" s="82"/>
     </row>
-    <row r="22" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="82"/>
       <c r="B22" s="86">
         <f t="shared" si="7"/>
@@ -10896,7 +11262,7 @@
       </c>
       <c r="AJ22" s="82"/>
     </row>
-    <row r="23" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="82"/>
       <c r="B23" s="86">
         <f t="shared" si="7"/>
@@ -11018,7 +11384,7 @@
       </c>
       <c r="AJ23" s="82"/>
     </row>
-    <row r="24" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="82"/>
       <c r="B24" s="86">
         <f t="shared" si="7"/>
@@ -11140,7 +11506,7 @@
       </c>
       <c r="AJ24" s="82"/>
     </row>
-    <row r="25" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="82"/>
       <c r="B25" s="82"/>
       <c r="C25" s="82"/>
@@ -11178,7 +11544,7 @@
       <c r="AI25" s="82"/>
       <c r="AJ25" s="82"/>
     </row>
-    <row r="26" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="82">
         <v>2</v>
       </c>
@@ -11252,7 +11618,7 @@
       <c r="AI26" s="82"/>
       <c r="AJ26" s="82"/>
     </row>
-    <row r="27" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="82"/>
       <c r="B27" s="84">
         <f t="shared" ref="B27:H34" si="21">IF(AND(B6=$A$26,C6=$C$26),1,0)</f>
@@ -11374,7 +11740,7 @@
       </c>
       <c r="AJ27" s="82"/>
     </row>
-    <row r="28" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="82"/>
       <c r="B28" s="87">
         <f t="shared" si="21"/>
@@ -11496,7 +11862,7 @@
       </c>
       <c r="AJ28" s="82"/>
     </row>
-    <row r="29" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="82"/>
       <c r="B29" s="86">
         <f t="shared" si="21"/>
@@ -11618,7 +11984,7 @@
       </c>
       <c r="AJ29" s="82"/>
     </row>
-    <row r="30" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="82"/>
       <c r="B30" s="86">
         <f t="shared" si="21"/>
@@ -11740,7 +12106,7 @@
       </c>
       <c r="AJ30" s="82"/>
     </row>
-    <row r="31" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="82"/>
       <c r="B31" s="86">
         <f t="shared" si="21"/>
@@ -11862,7 +12228,7 @@
       </c>
       <c r="AJ31" s="82"/>
     </row>
-    <row r="32" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="82"/>
       <c r="B32" s="86">
         <f t="shared" si="21"/>
@@ -11984,7 +12350,7 @@
       </c>
       <c r="AJ32" s="82"/>
     </row>
-    <row r="33" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="82"/>
       <c r="B33" s="86">
         <f t="shared" si="21"/>
@@ -12106,7 +12472,7 @@
       </c>
       <c r="AJ33" s="82"/>
     </row>
-    <row r="34" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="82"/>
       <c r="B34" s="86">
         <f t="shared" si="21"/>
@@ -12228,7 +12594,7 @@
       </c>
       <c r="AJ34" s="82"/>
     </row>
-    <row r="35" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="82"/>
       <c r="B35" s="82"/>
       <c r="C35" s="82"/>
@@ -12266,7 +12632,7 @@
       <c r="AI35" s="82"/>
       <c r="AJ35" s="82"/>
     </row>
-    <row r="36" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="82">
         <v>3</v>
       </c>
@@ -12340,7 +12706,7 @@
       <c r="AI36" s="82"/>
       <c r="AJ36" s="82"/>
     </row>
-    <row r="37" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="82"/>
       <c r="B37" s="84">
         <f t="shared" ref="B37:H44" si="25">IF(AND(B6=$A$36,C6=$C$36),1,0)</f>
@@ -12462,7 +12828,7 @@
       </c>
       <c r="AJ37" s="82"/>
     </row>
-    <row r="38" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="82"/>
       <c r="B38" s="87">
         <f t="shared" si="25"/>
@@ -12584,7 +12950,7 @@
       </c>
       <c r="AJ38" s="82"/>
     </row>
-    <row r="39" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="82"/>
       <c r="B39" s="86">
         <f t="shared" si="25"/>
@@ -12706,7 +13072,7 @@
       </c>
       <c r="AJ39" s="82"/>
     </row>
-    <row r="40" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="82"/>
       <c r="B40" s="86">
         <f t="shared" si="25"/>
@@ -12828,7 +13194,7 @@
       </c>
       <c r="AJ40" s="82"/>
     </row>
-    <row r="41" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="82"/>
       <c r="B41" s="86">
         <f t="shared" si="25"/>
@@ -12950,7 +13316,7 @@
       </c>
       <c r="AJ41" s="82"/>
     </row>
-    <row r="42" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="82"/>
       <c r="B42" s="86">
         <f t="shared" si="25"/>
@@ -13072,7 +13438,7 @@
       </c>
       <c r="AJ42" s="82"/>
     </row>
-    <row r="43" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="82"/>
       <c r="B43" s="86">
         <f t="shared" si="25"/>
@@ -13194,7 +13560,7 @@
       </c>
       <c r="AJ43" s="82"/>
     </row>
-    <row r="44" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="82"/>
       <c r="B44" s="86">
         <f t="shared" si="25"/>
@@ -13316,7 +13682,7 @@
       </c>
       <c r="AJ44" s="82"/>
     </row>
-    <row r="45" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="82"/>
       <c r="B45" s="82"/>
       <c r="C45" s="82"/>
@@ -13354,7 +13720,7 @@
       <c r="AI45" s="82"/>
       <c r="AJ45" s="82"/>
     </row>
-    <row r="46" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="82">
         <v>4</v>
       </c>
@@ -13428,7 +13794,7 @@
       <c r="AI46" s="82"/>
       <c r="AJ46" s="82"/>
     </row>
-    <row r="47" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:36" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="82"/>
       <c r="B47" s="84">
         <f t="shared" ref="B47:H54" si="29">IF(AND(B6=$A$46,C6=$C$46),1,0)</f>
@@ -13550,7 +13916,7 @@
       </c>
       <c r="AJ47" s="82"/>
     </row>
-    <row r="48" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="82"/>
       <c r="B48" s="87">
         <f t="shared" si="29"/>
@@ -13672,7 +14038,7 @@
       </c>
       <c r="AJ48" s="82"/>
     </row>
-    <row r="49" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="82"/>
       <c r="B49" s="86">
         <f t="shared" si="29"/>
@@ -13794,7 +14160,7 @@
       </c>
       <c r="AJ49" s="82"/>
     </row>
-    <row r="50" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="82"/>
       <c r="B50" s="86">
         <f t="shared" si="29"/>
@@ -13916,7 +14282,7 @@
       </c>
       <c r="AJ50" s="82"/>
     </row>
-    <row r="51" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="82"/>
       <c r="B51" s="86">
         <f t="shared" si="29"/>
@@ -14038,7 +14404,7 @@
       </c>
       <c r="AJ51" s="82"/>
     </row>
-    <row r="52" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="82"/>
       <c r="B52" s="86">
         <f t="shared" si="29"/>
@@ -14160,7 +14526,7 @@
       </c>
       <c r="AJ52" s="82"/>
     </row>
-    <row r="53" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="82"/>
       <c r="B53" s="86">
         <f t="shared" si="29"/>
@@ -14282,7 +14648,7 @@
       </c>
       <c r="AJ53" s="82"/>
     </row>
-    <row r="54" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="82"/>
       <c r="B54" s="86">
         <f t="shared" si="29"/>
@@ -14404,7 +14770,7 @@
       </c>
       <c r="AJ54" s="82"/>
     </row>
-    <row r="55" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:36" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="82"/>
       <c r="B55" s="82"/>
       <c r="C55" s="82"/>
@@ -14443,7 +14809,7 @@
       <c r="AJ55" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="g5DGrv2R0Svxz9gkgsW83wn/3Gvv8+jZGdgsR06T1tIWEWN25/PfKY8ropFZ6mtq5yadqowbjTlyUOos40EDhg==" saltValue="6EC212lt0/eeN1hDXwqyxQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="D3cnX6YsrsqICfmB3pnBjFV6yS/VcPrGLKoDYeUPS+JJqTlpltiMLbavojwuBdamDitXX+orRoGKC2iyOFI/Eg==" saltValue="N0qYW7kzVVGJppr6k1Fnyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="5">
     <mergeCell ref="V11:V14"/>
     <mergeCell ref="AD11:AD14"/>
@@ -14492,22 +14858,28 @@
     </dataValidation>
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4 Z3:Z4 AB3:AB4 AH3:AH4 AJ3:AJ4" xr:uid="{995BD10A-B62E-4A28-9BFA-BCA2ECCB985D}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{50CA87CD-2A4A-4B8C-ADEB-70F4715E58AB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE47ACE9-AAFB-4754-9C53-DE8F778ECA9A}">
   <dimension ref="A1:AU55"/>
-  <sheetFormatPr defaultColWidth="4.33203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="42" max="42" width="8.33203125" customWidth="1"/>
-    <col min="44" max="47" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.375" customWidth="1"/>
+    <col min="44" max="47" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
         <v>74</v>
       </c>
@@ -14545,7 +14917,7 @@
       <c r="AH1" s="19"/>
       <c r="AI1" s="19"/>
     </row>
-    <row r="2" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -14576,7 +14948,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -14607,16 +14979,16 @@
         <v>0</v>
       </c>
       <c r="Z3" s="211"/>
-      <c r="AA3" s="241" t="s">
+      <c r="AA3" s="262" t="s">
         <v>72</v>
       </c>
-      <c r="AB3" s="241"/>
-      <c r="AC3" s="241"/>
-      <c r="AD3" s="241"/>
-      <c r="AE3" s="241"/>
-      <c r="AF3" s="241"/>
+      <c r="AB3" s="262"/>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="262"/>
+      <c r="AE3" s="262"/>
+      <c r="AF3" s="262"/>
     </row>
-    <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
         <v>8</v>
       </c>
@@ -14664,26 +15036,26 @@
       <c r="Z4" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="AA4" s="240" t="s">
+      <c r="AA4" s="261" t="s">
         <v>70</v>
       </c>
-      <c r="AB4" s="240"/>
-      <c r="AC4" s="240"/>
-      <c r="AD4" s="240"/>
-      <c r="AE4" s="240"/>
-      <c r="AF4" s="240"/>
-      <c r="AG4" s="240"/>
-      <c r="AH4" s="240"/>
-      <c r="AI4" s="240"/>
-      <c r="AJ4" s="240"/>
-      <c r="AK4" s="240"/>
-      <c r="AL4" s="240"/>
-      <c r="AM4" s="240"/>
-      <c r="AN4" s="240"/>
-      <c r="AO4" s="240"/>
-      <c r="AP4" s="240"/>
+      <c r="AB4" s="261"/>
+      <c r="AC4" s="261"/>
+      <c r="AD4" s="261"/>
+      <c r="AE4" s="261"/>
+      <c r="AF4" s="261"/>
+      <c r="AG4" s="261"/>
+      <c r="AH4" s="261"/>
+      <c r="AI4" s="261"/>
+      <c r="AJ4" s="261"/>
+      <c r="AK4" s="261"/>
+      <c r="AL4" s="261"/>
+      <c r="AM4" s="261"/>
+      <c r="AN4" s="261"/>
+      <c r="AO4" s="261"/>
+      <c r="AP4" s="261"/>
     </row>
-    <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -14756,7 +15128,7 @@
       <c r="AO5" s="211"/>
       <c r="AP5" s="211"/>
     </row>
-    <row r="6" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <f t="shared" ref="B6:I13" si="1">L6</f>
         <v>1</v>
@@ -14831,7 +15203,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -14897,7 +15269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -14969,7 +15341,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15034,27 +15406,27 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="242" t="s">
+      <c r="X9" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
-      <c r="AA9" s="244"/>
-      <c r="AF9" s="242" t="s">
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
+      <c r="AA9" s="254"/>
+      <c r="AF9" s="252" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="243"/>
-      <c r="AH9" s="243"/>
-      <c r="AI9" s="244"/>
-      <c r="AL9" s="248" t="s">
+      <c r="AG9" s="253"/>
+      <c r="AH9" s="253"/>
+      <c r="AI9" s="254"/>
+      <c r="AL9" s="263" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="248"/>
-      <c r="AN9" s="248"/>
-      <c r="AO9" s="248"/>
-      <c r="AP9" s="248"/>
+      <c r="AM9" s="263"/>
+      <c r="AN9" s="263"/>
+      <c r="AO9" s="263"/>
+      <c r="AP9" s="263"/>
     </row>
-    <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15143,16 +15515,16 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="248"/>
-      <c r="AM10" s="248"/>
-      <c r="AN10" s="248"/>
-      <c r="AO10" s="248"/>
-      <c r="AP10" s="248"/>
+      <c r="AL10" s="263"/>
+      <c r="AM10" s="263"/>
+      <c r="AN10" s="263"/>
+      <c r="AO10" s="263"/>
+      <c r="AP10" s="263"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -15217,7 +15589,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="245" t="s">
+      <c r="V11" s="249" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -15239,7 +15611,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>4</v>
       </c>
-      <c r="AD11" s="245" t="s">
+      <c r="AD11" s="249" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -15288,7 +15660,7 @@
         <v>-0.17169124721634299</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -15353,7 +15725,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="246"/>
+      <c r="V12" s="250"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -15373,7 +15745,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>6</v>
       </c>
-      <c r="AD12" s="246"/>
+      <c r="AD12" s="250"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -15420,7 +15792,7 @@
         <v>-0.22619959400016687</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -15485,7 +15857,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="246"/>
+      <c r="V13" s="250"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -15505,7 +15877,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>2</v>
       </c>
-      <c r="AD13" s="246"/>
+      <c r="AD13" s="250"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -15552,7 +15924,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="K14" s="20">
         <f>(K13+L14)/2</f>
         <v>0</v>
@@ -15593,7 +15965,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="247"/>
+      <c r="V14" s="251"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -15613,7 +15985,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>2</v>
       </c>
-      <c r="AD14" s="247"/>
+      <c r="AD14" s="251"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -15660,7 +16032,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="82" t="s">
         <v>48</v>
       </c>
@@ -15701,7 +16073,7 @@
       <c r="AJ15" s="82"/>
       <c r="AK15" s="82"/>
     </row>
-    <row r="16" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="82">
         <v>1</v>
       </c>
@@ -15776,7 +16148,7 @@
       <c r="AJ16" s="82"/>
       <c r="AK16" s="82"/>
     </row>
-    <row r="17" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="82"/>
       <c r="B17" s="84">
         <f>IF($L$6=A16,IF($K$5*$W$3=C16,1,0)+IF($L$5*$X$3=C16,1,0)+IF($M$5*$Y$3=C16,1,0)+IF($K$6*$W$4=C16,1,0)+IF($M$6*$Y$4=C16,1,0)+IF($K$7*$W$5=C16,1,0)+IF($L$7*$X$5=C16,1,0)+IF($M$7*$Y$5=C16,1,0),0)</f>
@@ -15911,7 +16283,7 @@
       </c>
       <c r="AK17" s="82"/>
     </row>
-    <row r="18" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="82"/>
       <c r="B18" s="87">
         <f t="shared" ref="B18:B24" si="11">IF(L7=$A$16,IF(K6*$W$3=$C$16,1,0)+IF(L6*$X$3=$C$16,1,0)+IF(M6*$Y$3=$C$16,1,0)+IF(K7*$W$4=$C$16,1,0)+IF(M7*$Y$4=$C$16,1,0)+IF(K8*$W$5=$C$16,1,0)+IF(L8*$X$5=$C$16,1,0)+IF(M8*$Y$5=$C$16,1,0),0)</f>
@@ -16046,7 +16418,7 @@
       </c>
       <c r="AK18" s="82"/>
     </row>
-    <row r="19" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="82"/>
       <c r="B19" s="86">
         <f t="shared" si="11"/>
@@ -16181,7 +16553,7 @@
       </c>
       <c r="AK19" s="82"/>
     </row>
-    <row r="20" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="82"/>
       <c r="B20" s="86">
         <f t="shared" si="11"/>
@@ -16316,7 +16688,7 @@
       </c>
       <c r="AK20" s="82"/>
     </row>
-    <row r="21" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="82"/>
       <c r="B21" s="86">
         <f t="shared" si="11"/>
@@ -16451,7 +16823,7 @@
       </c>
       <c r="AK21" s="82"/>
     </row>
-    <row r="22" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="82"/>
       <c r="B22" s="86">
         <f t="shared" si="11"/>
@@ -16586,7 +16958,7 @@
       </c>
       <c r="AK22" s="82"/>
     </row>
-    <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="82"/>
       <c r="B23" s="86">
         <f t="shared" si="11"/>
@@ -16721,7 +17093,7 @@
       </c>
       <c r="AK23" s="82"/>
     </row>
-    <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="82"/>
       <c r="B24" s="86">
         <f t="shared" si="11"/>
@@ -16856,7 +17228,7 @@
       </c>
       <c r="AK24" s="82"/>
     </row>
-    <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="82"/>
       <c r="B25" s="82"/>
       <c r="C25" s="82"/>
@@ -16895,7 +17267,7 @@
       <c r="AJ25" s="82"/>
       <c r="AK25" s="82"/>
     </row>
-    <row r="26" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="82">
         <v>2</v>
       </c>
@@ -16970,7 +17342,7 @@
       <c r="AJ26" s="82"/>
       <c r="AK26" s="82"/>
     </row>
-    <row r="27" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="82"/>
       <c r="B27" s="84">
         <f t="shared" ref="B27:I34" si="14">IF(L6=$A$26,IF(K5*$W$3=$C$26,1,0)+IF(L5*$X$3=$C$26,1,0)+IF(M5*$Y$3=$C$26,1,0)+IF(K6*$W$4=$C$26,1,0)+IF(M6*$Y$4=$C$26,1,0)+IF(K7*$W$5=$C$26,1,0)+IF(L7*$X$5=$C$26,1,0)+IF(M7*$Y$5=$C$26,1,0),0)</f>
@@ -17105,7 +17477,7 @@
       </c>
       <c r="AK27" s="82"/>
     </row>
-    <row r="28" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="82"/>
       <c r="B28" s="87">
         <f t="shared" si="14"/>
@@ -17240,7 +17612,7 @@
       </c>
       <c r="AK28" s="82"/>
     </row>
-    <row r="29" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="82"/>
       <c r="B29" s="86">
         <f t="shared" si="14"/>
@@ -17375,7 +17747,7 @@
       </c>
       <c r="AK29" s="82"/>
     </row>
-    <row r="30" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="82"/>
       <c r="B30" s="86">
         <f t="shared" si="14"/>
@@ -17510,7 +17882,7 @@
       </c>
       <c r="AK30" s="82"/>
     </row>
-    <row r="31" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="82"/>
       <c r="B31" s="86">
         <f t="shared" si="14"/>
@@ -17645,7 +18017,7 @@
       </c>
       <c r="AK31" s="82"/>
     </row>
-    <row r="32" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="82"/>
       <c r="B32" s="86">
         <f t="shared" si="14"/>
@@ -17780,7 +18152,7 @@
       </c>
       <c r="AK32" s="82"/>
     </row>
-    <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="82"/>
       <c r="B33" s="86">
         <f t="shared" si="14"/>
@@ -17915,7 +18287,7 @@
       </c>
       <c r="AK33" s="82"/>
     </row>
-    <row r="34" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="82"/>
       <c r="B34" s="86">
         <f t="shared" si="14"/>
@@ -18050,7 +18422,7 @@
       </c>
       <c r="AK34" s="82"/>
     </row>
-    <row r="35" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="82"/>
       <c r="B35" s="82"/>
       <c r="C35" s="82"/>
@@ -18089,7 +18461,7 @@
       <c r="AJ35" s="82"/>
       <c r="AK35" s="82"/>
     </row>
-    <row r="36" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="82">
         <v>3</v>
       </c>
@@ -18164,7 +18536,7 @@
       <c r="AJ36" s="82"/>
       <c r="AK36" s="82"/>
     </row>
-    <row r="37" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="82"/>
       <c r="B37" s="84">
         <f t="shared" ref="B37:I44" si="18">IF(L6=$A$36,IF(K5*$W$3=$C$36,1,0)+IF(L5*$X$3=$C$36,1,0)+IF(M5*$Y$3=$C$36,1,0)+IF(K6*$W$4=$C$36,1,0)+IF(M6*$Y$4=$C$36,1,0)+IF(K7*$W$5=$C$36,1,0)+IF(L7*$X$5=$C$36,1,0)+IF(M7*$Y$5=$C$36,1,0),0)</f>
@@ -18299,7 +18671,7 @@
       </c>
       <c r="AK37" s="82"/>
     </row>
-    <row r="38" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="82"/>
       <c r="B38" s="87">
         <f t="shared" si="18"/>
@@ -18434,7 +18806,7 @@
       </c>
       <c r="AK38" s="82"/>
     </row>
-    <row r="39" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="82"/>
       <c r="B39" s="86">
         <f t="shared" si="18"/>
@@ -18569,7 +18941,7 @@
       </c>
       <c r="AK39" s="82"/>
     </row>
-    <row r="40" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="82"/>
       <c r="B40" s="86">
         <f t="shared" si="18"/>
@@ -18704,7 +19076,7 @@
       </c>
       <c r="AK40" s="82"/>
     </row>
-    <row r="41" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="82"/>
       <c r="B41" s="86">
         <f t="shared" si="18"/>
@@ -18839,7 +19211,7 @@
       </c>
       <c r="AK41" s="82"/>
     </row>
-    <row r="42" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="82"/>
       <c r="B42" s="86">
         <f t="shared" si="18"/>
@@ -18974,7 +19346,7 @@
       </c>
       <c r="AK42" s="82"/>
     </row>
-    <row r="43" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="82"/>
       <c r="B43" s="86">
         <f t="shared" si="18"/>
@@ -19109,7 +19481,7 @@
       </c>
       <c r="AK43" s="82"/>
     </row>
-    <row r="44" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="82"/>
       <c r="B44" s="86">
         <f t="shared" si="18"/>
@@ -19244,7 +19616,7 @@
       </c>
       <c r="AK44" s="82"/>
     </row>
-    <row r="45" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="82"/>
       <c r="B45" s="82"/>
       <c r="C45" s="82"/>
@@ -19283,7 +19655,7 @@
       <c r="AJ45" s="82"/>
       <c r="AK45" s="82"/>
     </row>
-    <row r="46" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="82">
         <v>4</v>
       </c>
@@ -19358,7 +19730,7 @@
       <c r="AJ46" s="82"/>
       <c r="AK46" s="82"/>
     </row>
-    <row r="47" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="82"/>
       <c r="B47" s="84">
         <f t="shared" ref="B47:I54" si="22">IF(L6=$A$46,IF(K5*$W$3=$C$46,1,0)+IF(L5*$X$3=$C$46,1,0)+IF(M5*$Y$3=$C$46,1,0)+IF(K6*$W$4=$C$46,1,0)+IF(M6*$Y$4=$C$46,1,0)+IF(K7*$W$5=$C$46,1,0)+IF(L7*$X$5=$C$46,1,0)+IF(M7*$Y$5=$C$46,1,0),0)</f>
@@ -19493,7 +19865,7 @@
       </c>
       <c r="AK47" s="82"/>
     </row>
-    <row r="48" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="82"/>
       <c r="B48" s="87">
         <f t="shared" si="22"/>
@@ -19628,7 +20000,7 @@
       </c>
       <c r="AK48" s="82"/>
     </row>
-    <row r="49" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="82"/>
       <c r="B49" s="86">
         <f t="shared" si="22"/>
@@ -19763,7 +20135,7 @@
       </c>
       <c r="AK49" s="82"/>
     </row>
-    <row r="50" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="82"/>
       <c r="B50" s="86">
         <f t="shared" si="22"/>
@@ -19898,7 +20270,7 @@
       </c>
       <c r="AK50" s="82"/>
     </row>
-    <row r="51" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="82"/>
       <c r="B51" s="86">
         <f t="shared" si="22"/>
@@ -20033,7 +20405,7 @@
       </c>
       <c r="AK51" s="82"/>
     </row>
-    <row r="52" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="82"/>
       <c r="B52" s="86">
         <f t="shared" si="22"/>
@@ -20168,7 +20540,7 @@
       </c>
       <c r="AK52" s="82"/>
     </row>
-    <row r="53" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="82"/>
       <c r="B53" s="86">
         <f t="shared" si="22"/>
@@ -20303,7 +20675,7 @@
       </c>
       <c r="AK53" s="82"/>
     </row>
-    <row r="54" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="82"/>
       <c r="B54" s="86">
         <f t="shared" si="22"/>
@@ -20438,7 +20810,7 @@
       </c>
       <c r="AK54" s="82"/>
     </row>
-    <row r="55" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="82"/>
       <c r="B55" s="82"/>
       <c r="C55" s="82"/>
@@ -20478,7 +20850,7 @@
       <c r="AK55" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="bhmu29asPrBeCQim1l4dkh2lrSndBupQ3jDHnTMjIl6a1m3OFCDSxvnEWsEHrXTSYi//YX5gsDu4/Y3TgFdYGA==" saltValue="bVLB04T+uBTzhNSLjguhlg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="RMlVZshFWv7HKfGAhZCt1p2M0xKSbiW+fJE5WMYFeTaQ5Vz7ZYwiaX/ZAv2tLirdBbIa7AM33H0ks+h42utCBg==" saltValue="QchpNVrJa6YNLOdgVo/VKg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="AA4:AP4"/>
     <mergeCell ref="AA3:AF3"/>
@@ -20534,23 +20906,29 @@
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{16E63979-D6EA-4719-95E7-99D2241FE87A}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8C1C15-F12A-44A5-A92E-7821686EC966}">
   <dimension ref="A1:AU55"/>
-  <sheetFormatPr defaultColWidth="4.33203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="4.375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="42" max="42" width="8.33203125" customWidth="1"/>
-    <col min="44" max="47" width="10.109375" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="8.375" customWidth="1"/>
+    <col min="44" max="47" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
         <v>75</v>
       </c>
@@ -20587,7 +20965,7 @@
       <c r="AG1" s="19"/>
       <c r="AH1" s="19"/>
     </row>
-    <row r="2" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -20634,7 +21012,7 @@
       <c r="AQ2" s="265"/>
       <c r="AR2" s="266"/>
     </row>
-    <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -20681,7 +21059,7 @@
       <c r="AQ3" s="265"/>
       <c r="AR3" s="266"/>
     </row>
-    <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
         <v>8</v>
       </c>
@@ -20740,7 +21118,7 @@
       <c r="AQ4" s="268"/>
       <c r="AR4" s="269"/>
     </row>
-    <row r="5" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -20810,7 +21188,7 @@
       <c r="AQ5" s="265"/>
       <c r="AR5" s="266"/>
     </row>
-    <row r="6" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <f t="shared" ref="B6:I13" si="1">L6</f>
         <v>1</v>
@@ -20901,7 +21279,7 @@
       <c r="AQ6" s="268"/>
       <c r="AR6" s="269"/>
     </row>
-    <row r="7" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -20967,7 +21345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B8" s="1">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -21039,7 +21417,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -21116,15 +21494,15 @@
       <c r="AG9" s="271"/>
       <c r="AH9" s="271"/>
       <c r="AI9" s="272"/>
-      <c r="AL9" s="248" t="s">
+      <c r="AL9" s="263" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="248"/>
-      <c r="AN9" s="248"/>
-      <c r="AO9" s="248"/>
-      <c r="AP9" s="248"/>
+      <c r="AM9" s="263"/>
+      <c r="AN9" s="263"/>
+      <c r="AO9" s="263"/>
+      <c r="AP9" s="263"/>
     </row>
-    <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -21213,16 +21591,16 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="248"/>
-      <c r="AM10" s="248"/>
-      <c r="AN10" s="248"/>
-      <c r="AO10" s="248"/>
-      <c r="AP10" s="248"/>
+      <c r="AL10" s="263"/>
+      <c r="AM10" s="263"/>
+      <c r="AN10" s="263"/>
+      <c r="AO10" s="263"/>
+      <c r="AP10" s="263"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <f t="shared" si="1"/>
         <v>1</v>
@@ -21287,7 +21665,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="245" t="s">
+      <c r="V11" s="249" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -21309,7 +21687,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>13</v>
       </c>
-      <c r="AD11" s="245" t="s">
+      <c r="AD11" s="249" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -21358,7 +21736,7 @@
         <v>-0.15518922712815572</v>
       </c>
     </row>
-    <row r="12" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <f t="shared" si="1"/>
         <v>2</v>
@@ -21423,7 +21801,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="246"/>
+      <c r="V12" s="250"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -21443,7 +21821,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>20</v>
       </c>
-      <c r="AD12" s="246"/>
+      <c r="AD12" s="250"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -21490,7 +21868,7 @@
         <v>-0.20915797251327431</v>
       </c>
     </row>
-    <row r="13" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
@@ -21555,7 +21933,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="246"/>
+      <c r="V13" s="250"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -21575,7 +21953,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>7</v>
       </c>
-      <c r="AD13" s="246"/>
+      <c r="AD13" s="250"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -21622,7 +22000,7 @@
         <v>-9.8448176593475309E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="K14" s="20">
         <f>(K13+L14)/2</f>
         <v>0</v>
@@ -21663,7 +22041,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="247"/>
+      <c r="V14" s="251"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -21683,7 +22061,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>10</v>
       </c>
-      <c r="AD14" s="247"/>
+      <c r="AD14" s="251"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -21730,7 +22108,7 @@
         <v>-0.12838851006616095</v>
       </c>
     </row>
-    <row r="15" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="82" t="s">
         <v>48</v>
       </c>
@@ -21771,7 +22149,7 @@
       <c r="AJ15" s="82"/>
       <c r="AK15" s="82"/>
     </row>
-    <row r="16" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A16" s="82">
         <v>1</v>
       </c>
@@ -21846,7 +22224,7 @@
       <c r="AJ16" s="82"/>
       <c r="AK16" s="82"/>
     </row>
-    <row r="17" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A17" s="82"/>
       <c r="B17" s="84">
         <f>IF(L6=$A$16,COUNTIF(K5:M7,$C$16)-IF(L6=$C$16,1,0),0)</f>
@@ -21981,7 +22359,7 @@
       </c>
       <c r="AK17" s="82"/>
     </row>
-    <row r="18" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="82"/>
       <c r="B18" s="86">
         <f t="shared" ref="B18:B24" si="15">IF(L7=$A$16,COUNTIF(K6:M8,$C$16)-IF(L7=$C$16,1,0),0)</f>
@@ -22116,7 +22494,7 @@
       </c>
       <c r="AK18" s="82"/>
     </row>
-    <row r="19" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="82"/>
       <c r="B19" s="86">
         <f t="shared" si="15"/>
@@ -22251,7 +22629,7 @@
       </c>
       <c r="AK19" s="82"/>
     </row>
-    <row r="20" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="82"/>
       <c r="B20" s="86">
         <f t="shared" si="15"/>
@@ -22386,7 +22764,7 @@
       </c>
       <c r="AK20" s="82"/>
     </row>
-    <row r="21" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="82"/>
       <c r="B21" s="86">
         <f t="shared" si="15"/>
@@ -22521,7 +22899,7 @@
       </c>
       <c r="AK21" s="82"/>
     </row>
-    <row r="22" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="82"/>
       <c r="B22" s="86">
         <f t="shared" si="15"/>
@@ -22656,7 +23034,7 @@
       </c>
       <c r="AK22" s="82"/>
     </row>
-    <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="82"/>
       <c r="B23" s="86">
         <f t="shared" si="15"/>
@@ -22791,7 +23169,7 @@
       </c>
       <c r="AK23" s="82"/>
     </row>
-    <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="82"/>
       <c r="B24" s="86">
         <f t="shared" si="15"/>
@@ -22926,7 +23304,7 @@
       </c>
       <c r="AK24" s="82"/>
     </row>
-    <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="82"/>
       <c r="B25" s="82"/>
       <c r="C25" s="82"/>
@@ -22965,7 +23343,7 @@
       <c r="AJ25" s="82"/>
       <c r="AK25" s="82"/>
     </row>
-    <row r="26" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A26" s="82">
         <v>2</v>
       </c>
@@ -23040,7 +23418,7 @@
       <c r="AJ26" s="82"/>
       <c r="AK26" s="82"/>
     </row>
-    <row r="27" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A27" s="82"/>
       <c r="B27" s="84">
         <f>IF(L6=$A$26,COUNTIF(K5:M7,$C$26)-IF(L6=$C$26,1,0),0)</f>
@@ -23175,7 +23553,7 @@
       </c>
       <c r="AK27" s="82"/>
     </row>
-    <row r="28" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="82"/>
       <c r="B28" s="87">
         <f t="shared" ref="B28:B34" si="22">IF(L7=$A$26,COUNTIF(K6:M8,$C$26)-IF(L7=$C$26,1,0),0)</f>
@@ -23310,7 +23688,7 @@
       </c>
       <c r="AK28" s="82"/>
     </row>
-    <row r="29" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="82"/>
       <c r="B29" s="86">
         <f t="shared" si="22"/>
@@ -23445,7 +23823,7 @@
       </c>
       <c r="AK29" s="82"/>
     </row>
-    <row r="30" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="82"/>
       <c r="B30" s="86">
         <f t="shared" si="22"/>
@@ -23580,7 +23958,7 @@
       </c>
       <c r="AK30" s="82"/>
     </row>
-    <row r="31" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="82"/>
       <c r="B31" s="86">
         <f t="shared" si="22"/>
@@ -23715,7 +24093,7 @@
       </c>
       <c r="AK31" s="82"/>
     </row>
-    <row r="32" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="82"/>
       <c r="B32" s="86">
         <f t="shared" si="22"/>
@@ -23850,7 +24228,7 @@
       </c>
       <c r="AK32" s="82"/>
     </row>
-    <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="82"/>
       <c r="B33" s="86">
         <f t="shared" si="22"/>
@@ -23985,7 +24363,7 @@
       </c>
       <c r="AK33" s="82"/>
     </row>
-    <row r="34" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="82"/>
       <c r="B34" s="86">
         <f t="shared" si="22"/>
@@ -24120,7 +24498,7 @@
       </c>
       <c r="AK34" s="82"/>
     </row>
-    <row r="35" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="82"/>
       <c r="B35" s="82"/>
       <c r="C35" s="82"/>
@@ -24159,7 +24537,7 @@
       <c r="AJ35" s="82"/>
       <c r="AK35" s="82"/>
     </row>
-    <row r="36" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A36" s="82">
         <v>3</v>
       </c>
@@ -24234,7 +24612,7 @@
       <c r="AJ36" s="82"/>
       <c r="AK36" s="82"/>
     </row>
-    <row r="37" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A37" s="82"/>
       <c r="B37" s="84">
         <f>IF(L6=$A$36,COUNTIF(K5:M7,$C$36)-IF(L6=$C$36,1,0),0)</f>
@@ -24369,7 +24747,7 @@
       </c>
       <c r="AK37" s="82"/>
     </row>
-    <row r="38" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="82"/>
       <c r="B38" s="87">
         <f t="shared" ref="B38:B44" si="30">IF(L7=$A$36,COUNTIF(K6:M8,$C$36)-IF(L7=$C$36,1,0),0)</f>
@@ -24504,7 +24882,7 @@
       </c>
       <c r="AK38" s="82"/>
     </row>
-    <row r="39" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="82"/>
       <c r="B39" s="86">
         <f t="shared" si="30"/>
@@ -24639,7 +25017,7 @@
       </c>
       <c r="AK39" s="82"/>
     </row>
-    <row r="40" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="82"/>
       <c r="B40" s="86">
         <f t="shared" si="30"/>
@@ -24774,7 +25152,7 @@
       </c>
       <c r="AK40" s="82"/>
     </row>
-    <row r="41" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="82"/>
       <c r="B41" s="86">
         <f t="shared" si="30"/>
@@ -24909,7 +25287,7 @@
       </c>
       <c r="AK41" s="82"/>
     </row>
-    <row r="42" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="82"/>
       <c r="B42" s="86">
         <f t="shared" si="30"/>
@@ -25044,7 +25422,7 @@
       </c>
       <c r="AK42" s="82"/>
     </row>
-    <row r="43" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="82"/>
       <c r="B43" s="86">
         <f t="shared" si="30"/>
@@ -25179,7 +25557,7 @@
       </c>
       <c r="AK43" s="82"/>
     </row>
-    <row r="44" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="82"/>
       <c r="B44" s="86">
         <f t="shared" si="30"/>
@@ -25314,7 +25692,7 @@
       </c>
       <c r="AK44" s="82"/>
     </row>
-    <row r="45" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="82"/>
       <c r="B45" s="82"/>
       <c r="C45" s="82"/>
@@ -25353,7 +25731,7 @@
       <c r="AJ45" s="82"/>
       <c r="AK45" s="82"/>
     </row>
-    <row r="46" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A46" s="82">
         <v>4</v>
       </c>
@@ -25428,7 +25806,7 @@
       <c r="AJ46" s="82"/>
       <c r="AK46" s="82"/>
     </row>
-    <row r="47" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A47" s="82"/>
       <c r="B47" s="84">
         <f>IF(L6=$A$46,COUNTIF(K5:M7,$C$46)-IF(L6=$C$46,1,0),0)</f>
@@ -25563,7 +25941,7 @@
       </c>
       <c r="AK47" s="82"/>
     </row>
-    <row r="48" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="82"/>
       <c r="B48" s="87">
         <f t="shared" ref="B48:B54" si="38">IF(L7=$A$46,COUNTIF(K6:M8,$C$46)-IF(L7=$C$46,1,0),0)</f>
@@ -25698,7 +26076,7 @@
       </c>
       <c r="AK48" s="82"/>
     </row>
-    <row r="49" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="82"/>
       <c r="B49" s="86">
         <f t="shared" si="38"/>
@@ -25833,7 +26211,7 @@
       </c>
       <c r="AK49" s="82"/>
     </row>
-    <row r="50" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="82"/>
       <c r="B50" s="86">
         <f t="shared" si="38"/>
@@ -25968,7 +26346,7 @@
       </c>
       <c r="AK50" s="82"/>
     </row>
-    <row r="51" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="82"/>
       <c r="B51" s="86">
         <f t="shared" si="38"/>
@@ -26103,7 +26481,7 @@
       </c>
       <c r="AK51" s="82"/>
     </row>
-    <row r="52" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="82"/>
       <c r="B52" s="86">
         <f t="shared" si="38"/>
@@ -26238,7 +26616,7 @@
       </c>
       <c r="AK52" s="82"/>
     </row>
-    <row r="53" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="82"/>
       <c r="B53" s="86">
         <f t="shared" si="38"/>
@@ -26373,7 +26751,7 @@
       </c>
       <c r="AK53" s="82"/>
     </row>
-    <row r="54" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="82"/>
       <c r="B54" s="86">
         <f t="shared" si="38"/>
@@ -26508,7 +26886,7 @@
       </c>
       <c r="AK54" s="82"/>
     </row>
-    <row r="55" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="82"/>
       <c r="B55" s="82"/>
       <c r="C55" s="82"/>
@@ -26548,7 +26926,7 @@
       <c r="AK55" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ShpPEKQqlNFxplyWAB8Ft7i5ExMREghG4jH43D10zett18b/vTDmdNxMDw8n0x1Oh4YBZ9pxtEAEeHT+PRpr/Q==" saltValue="TY6FtBuPGbrH7A4R+kcGuA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="a7AHORGKHpMUjRkn5ERUm+ygSQ4XxlgmW0+c9l1HPGNWdceOfaHMTxam3gp7rwV50up4xOklDw6DgOSDy+jgQg==" saltValue="iSPclcrsv8KynPC2yADwnA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
     <mergeCell ref="AL9:AP10"/>
     <mergeCell ref="X9:AA9"/>
@@ -26602,36 +26980,41 @@
     </dataValidation>
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4" xr:uid="{A2F48F23-233F-48A9-98A5-1E3C3D47166C}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{0418C76F-B20A-44ED-BA79-F6CE0CE443C8}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9884B89F-F41E-46EF-87E9-F2DD32687A57}">
   <dimension ref="A1:AH29"/>
-  <sheetFormatPr defaultRowHeight="16.2" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="9" width="4.33203125" customWidth="1"/>
-    <col min="10" max="10" width="4.44140625" customWidth="1"/>
-    <col min="11" max="11" width="3.21875" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" customWidth="1"/>
-    <col min="13" max="16" width="5.109375" customWidth="1"/>
-    <col min="18" max="21" width="7.21875" customWidth="1"/>
-    <col min="23" max="23" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="11.109375" customWidth="1"/>
-    <col min="26" max="26" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="4.375" customWidth="1"/>
+    <col min="10" max="10" width="4.5" customWidth="1"/>
+    <col min="11" max="11" width="3.25" customWidth="1"/>
+    <col min="12" max="12" width="4.5" customWidth="1"/>
+    <col min="13" max="16" width="5.125" customWidth="1"/>
+    <col min="18" max="21" width="7.25" customWidth="1"/>
+    <col min="23" max="23" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="11.125" customWidth="1"/>
+    <col min="26" max="26" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="7.75" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
-    <col min="31" max="34" width="6.88671875" customWidth="1"/>
+    <col min="31" max="34" width="6.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -26657,7 +27040,7 @@
       <c r="X1" s="19"/>
       <c r="Y1" s="19"/>
     </row>
-    <row r="2" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="166" t="s">
         <v>83</v>
       </c>
@@ -26680,7 +27063,7 @@
       <c r="S2" s="212"/>
       <c r="T2" s="213"/>
     </row>
-    <row r="3" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="214" t="s">
         <v>79</v>
       </c>
@@ -26711,7 +27094,7 @@
       </c>
       <c r="Z3" s="275"/>
     </row>
-    <row r="4" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="217" t="s">
         <v>85</v>
       </c>
@@ -26743,7 +27126,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="218" t="s">
         <v>86</v>
       </c>
@@ -26792,7 +27175,7 @@
         <v>3.0952380952380953E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="166" t="s">
         <v>84</v>
       </c>
@@ -26841,7 +27224,7 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="217" t="s">
         <v>87</v>
       </c>
@@ -26890,7 +27273,7 @@
         <v>1.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="218" t="s">
         <v>88</v>
       </c>
@@ -26939,36 +27322,43 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="M9" s="259" t="s">
+    <row r="9" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M9" s="256" t="s">
         <v>94</v>
       </c>
-      <c r="N9" s="259"/>
-      <c r="O9" s="259"/>
-      <c r="P9" s="259"/>
+      <c r="N9" s="256"/>
+      <c r="O9" s="256"/>
+      <c r="P9" s="256"/>
       <c r="R9" s="275" t="s">
         <v>95</v>
       </c>
       <c r="S9" s="275"/>
       <c r="T9" s="275"/>
       <c r="U9" s="275"/>
-      <c r="X9" s="219"/>
-      <c r="Y9" s="219"/>
+      <c r="X9" s="219" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y9" s="219" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>97</v>
+      </c>
     </row>
-    <row r="10" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="J10" s="273" t="s">
         <v>82</v>
       </c>
       <c r="K10" s="273"/>
       <c r="L10" s="273"/>
-      <c r="M10" s="262"/>
-      <c r="N10" s="262"/>
-      <c r="O10" s="262"/>
-      <c r="P10" s="262"/>
-      <c r="R10" s="262"/>
-      <c r="S10" s="262"/>
-      <c r="T10" s="262"/>
-      <c r="U10" s="262"/>
+      <c r="M10" s="259"/>
+      <c r="N10" s="259"/>
+      <c r="O10" s="259"/>
+      <c r="P10" s="259"/>
+      <c r="R10" s="259"/>
+      <c r="S10" s="259"/>
+      <c r="T10" s="259"/>
+      <c r="U10" s="259"/>
       <c r="X10" s="219"/>
       <c r="Y10" s="219"/>
       <c r="Z10" s="274" t="s">
@@ -26978,7 +27368,7 @@
       <c r="AB10" s="274"/>
       <c r="AC10" s="274"/>
     </row>
-    <row r="11" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="J11" s="82">
         <v>0</v>
       </c>
@@ -27041,7 +27431,7 @@
         <v>-0.17169124721634299</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K12" s="216"/>
       <c r="M12" s="86">
         <v>14</v>
@@ -27095,7 +27485,7 @@
         <v>-0.22619959400016687</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K13" s="216"/>
       <c r="M13" s="86">
         <v>5</v>
@@ -27149,7 +27539,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K14" s="216"/>
       <c r="M14" s="86">
         <v>4</v>
@@ -27203,7 +27593,7 @@
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K15" s="216"/>
       <c r="R15" s="220"/>
       <c r="S15" s="220"/>
@@ -27216,7 +27606,7 @@
       <c r="AB15" s="220"/>
       <c r="AC15" s="220"/>
     </row>
-    <row r="16" spans="1:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" t="s">
         <v>92</v>
       </c>
@@ -27282,7 +27672,7 @@
         <v>-0.21901947700142071</v>
       </c>
     </row>
-    <row r="17" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>1</v>
       </c>
@@ -27360,7 +27750,7 @@
         <v>-0.18835550384143707</v>
       </c>
     </row>
-    <row r="18" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>1</v>
       </c>
@@ -27438,7 +27828,7 @@
         <v>-6.7497039225665398E-2</v>
       </c>
     </row>
-    <row r="19" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>2</v>
       </c>
@@ -27516,7 +27906,7 @@
         <v>-0.11458591518602466</v>
       </c>
     </row>
-    <row r="20" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>1</v>
       </c>
@@ -27556,7 +27946,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="21" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>1</v>
       </c>
@@ -27655,7 +28045,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>1</v>
       </c>
@@ -27745,7 +28135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>2</v>
       </c>
@@ -27835,7 +28225,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="24" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>3</v>
       </c>
@@ -27925,7 +28315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K25" s="216"/>
       <c r="R25" s="220"/>
       <c r="S25" s="220"/>
@@ -27938,7 +28328,7 @@
       <c r="AB25" s="220"/>
       <c r="AC25" s="220"/>
     </row>
-    <row r="26" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="J26" s="228">
         <v>135</v>
       </c>
@@ -28001,7 +28391,7 @@
         <v>-0.11458591518602466</v>
       </c>
     </row>
-    <row r="27" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="M27" s="230">
         <v>12</v>
       </c>
@@ -28054,7 +28444,7 @@
         <v>-0.15397185745083833</v>
       </c>
     </row>
-    <row r="28" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="M28" s="230">
         <v>6</v>
       </c>
@@ -28107,7 +28497,7 @@
         <v>-0.15397185745083833</v>
       </c>
     </row>
-    <row r="29" spans="2:34" ht="16.2" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="M29" s="230">
         <v>2</v>
       </c>
@@ -28161,7 +28551,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Jd1bTubjHTgmHO4LM9iY21eQmpt4wzvP2SXCwXun0Ic4wzEEGjlBxEpQplaemXa1FIdEQcZ0QTH6V2YnR9d7gQ==" saltValue="unuRP6lzojoY4gbk8EOatw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WdDGh6/abOzYiUeW2mf3dBTGAVJ6atb3oUvKw10xnqNQhNuald2cJzB5MBcmrlH0ew6+9pa1rMVnCLujFHBPkQ==" saltValue="sOKXLDV9J+cwY+4USa+aSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="J10:L10"/>
     <mergeCell ref="W3:X3"/>
@@ -28177,23 +28567,27 @@
     <hyperlink ref="B5" r:id="rId2" xr:uid="{EA50A9D2-75D3-4B81-ACC3-0522675DC24C}"/>
     <hyperlink ref="B7" r:id="rId3" xr:uid="{C8C5C4AA-98E9-4A40-9127-FEDCA006F1CC}"/>
     <hyperlink ref="B8" r:id="rId4" xr:uid="{53B6EFD0-4201-4794-B5F6-6C5BC92FC4CD}"/>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{ADD3407C-F48E-4B24-927E-D7A0BDE66701}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBFE8DD6-D3E6-44BA-A1F5-2A4F67355FE9}">
   <dimension ref="A1:AM42"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="4.33203125" customWidth="1"/>
-    <col min="3" max="42" width="4.21875" customWidth="1"/>
+    <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.375" customWidth="1"/>
+    <col min="3" max="42" width="4.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
+    <row r="1" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="282" t="s">
+        <v>101</v>
+      </c>
       <c r="B1" s="19" t="s">
         <v>49</v>
       </c>
@@ -28225,7 +28619,7 @@
       <c r="AB1" s="19"/>
       <c r="AC1" s="19"/>
     </row>
-    <row r="2" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -28244,7 +28638,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>6</v>
       </c>
@@ -28255,7 +28649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="28" t="s">
         <v>8</v>
       </c>
@@ -28296,7 +28690,7 @@
       <c r="AA4" s="276"/>
       <c r="AB4" s="276"/>
     </row>
-    <row r="5" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -28325,7 +28719,7 @@
       <c r="AL5" s="91"/>
       <c r="AM5" s="92"/>
     </row>
-    <row r="6" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
         <f t="shared" ref="B6:I13" si="0">L6</f>
         <v>32</v>
@@ -28399,7 +28793,7 @@
       </c>
       <c r="AM6" s="94"/>
     </row>
-    <row r="7" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -28467,7 +28861,7 @@
       </c>
       <c r="AM7" s="94"/>
     </row>
-    <row r="8" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -28549,7 +28943,7 @@
       <c r="AL8" s="98"/>
       <c r="AM8" s="99"/>
     </row>
-    <row r="9" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -28631,7 +29025,7 @@
       <c r="AL9" s="19"/>
       <c r="AM9" s="102"/>
     </row>
-    <row r="10" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -28707,7 +29101,7 @@
       <c r="AL10" s="105"/>
       <c r="AM10" s="106"/>
     </row>
-    <row r="11" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -28777,7 +29171,7 @@
       <c r="AL11" s="109"/>
       <c r="AM11" s="110"/>
     </row>
-    <row r="12" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -28835,7 +29229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -28893,8 +29287,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" ht="24" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="15" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
         <v>50</v>
       </c>
@@ -28904,7 +29298,7 @@
       <c r="Y15" s="111"/>
       <c r="Z15" s="111"/>
     </row>
-    <row r="16" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="66">
         <f t="shared" ref="B16:I23" si="1">L16</f>
         <v>16</v>
@@ -28970,7 +29364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="73">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -29036,7 +29430,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="73">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -29102,7 +29496,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B19" s="59">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -29171,7 +29565,7 @@
       <c r="AB19" s="111"/>
       <c r="AC19" s="111"/>
     </row>
-    <row r="20" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B20" s="134">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -29256,7 +29650,7 @@
       <c r="AB20" s="111"/>
       <c r="AC20" s="111"/>
     </row>
-    <row r="21" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B21" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -29339,7 +29733,7 @@
       </c>
       <c r="AA21" s="111"/>
     </row>
-    <row r="22" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="73">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -29422,7 +29816,7 @@
       </c>
       <c r="AA22" s="111"/>
     </row>
-    <row r="23" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="59">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -29505,7 +29899,7 @@
       </c>
       <c r="AA23" s="111"/>
     </row>
-    <row r="24" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
         <v>53</v>
       </c>
@@ -29517,7 +29911,7 @@
       <c r="Z24" s="9"/>
       <c r="AA24" s="9"/>
     </row>
-    <row r="25" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B25" s="66">
         <f>L25</f>
         <v>16</v>
@@ -29583,7 +29977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B26" s="59">
         <f t="shared" ref="B26:B32" si="5">L26</f>
         <v>20</v>
@@ -29649,7 +30043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B27" s="134">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -29715,7 +30109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B28" s="59">
         <f t="shared" si="5"/>
         <v>4</v>
@@ -29781,7 +30175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="134">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -29847,7 +30241,7 @@
         <v>-16</v>
       </c>
     </row>
-    <row r="30" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B30" s="73">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -29913,7 +30307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="73">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -29987,7 +30381,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B32" s="59">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -30073,7 +30467,7 @@
       <c r="AJ32" s="279"/>
       <c r="AK32" s="279"/>
     </row>
-    <row r="33" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
         <v>55</v>
       </c>
@@ -30099,7 +30493,7 @@
       <c r="AJ33" s="277"/>
       <c r="AK33" s="277"/>
     </row>
-    <row r="34" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B34" s="167">
         <f>L34</f>
         <v>18</v>
@@ -30179,7 +30573,7 @@
       <c r="AJ34" s="185"/>
       <c r="AK34" s="184"/>
     </row>
-    <row r="35" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B35" s="170">
         <f t="shared" ref="B35:B41" si="26">L35</f>
         <v>0</v>
@@ -30257,7 +30651,7 @@
       <c r="AJ35" s="174"/>
       <c r="AK35" s="173"/>
     </row>
-    <row r="36" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="134">
         <f t="shared" si="26"/>
         <v>0</v>
@@ -30335,7 +30729,7 @@
       <c r="AJ36" s="174"/>
       <c r="AK36" s="173"/>
     </row>
-    <row r="37" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B37" s="59">
         <f t="shared" si="26"/>
         <v>4</v>
@@ -30411,7 +30805,7 @@
       <c r="AJ37" s="193"/>
       <c r="AK37" s="194"/>
     </row>
-    <row r="38" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="134">
         <f t="shared" si="26"/>
         <v>0</v>
@@ -30489,7 +30883,7 @@
       <c r="AJ38" s="196"/>
       <c r="AK38" s="198"/>
     </row>
-    <row r="39" spans="2:37" ht="23.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" ht="23.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="73">
         <f t="shared" si="26"/>
         <v>0</v>
@@ -30565,7 +30959,7 @@
       <c r="AJ39" s="174"/>
       <c r="AK39" s="173"/>
     </row>
-    <row r="40" spans="2:37" ht="23.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" ht="23.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="73">
         <f t="shared" si="26"/>
         <v>0</v>
@@ -30641,7 +31035,7 @@
       <c r="AJ40" s="174"/>
       <c r="AK40" s="173"/>
     </row>
-    <row r="41" spans="2:37" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:37" ht="23.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B41" s="59">
         <f t="shared" si="26"/>
         <v>0</v>
@@ -30717,9 +31111,9 @@
       <c r="AJ41" s="175"/>
       <c r="AK41" s="171"/>
     </row>
-    <row r="42" spans="2:37" ht="23.4" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="2:37" ht="23.45" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="LnOi3afxSK1Ja5SsPikum6gg+xAa1jt6tufBPa10bSrW069SaaxiDsZX1yFR34t4anmnLWAbHeJ/TmeCkf1RaQ==" saltValue="2Efl0pQZ8xaS7rB/OpfP5w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="mHT+oa+MFud6Vb/mTv/DYOir/zd2ZtJvFD1/IEZy7+L/rX5sYXEIIWQDaaTMyaU/UJK2shn0jI95HnEUCpnQLQ==" saltValue="4x3BLSnSV3JQzvpYzMwgBw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="X4:AB4"/>
     <mergeCell ref="AF33:AG33"/>
@@ -30756,6 +31150,9 @@
     </dataValidation>
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4 X8:Y8 AA8 AA5:AA6 X5:Y6" xr:uid="{DF5F91E0-C653-4F0E-B693-F7405715B82B}"/>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{C569BDA4-DF0A-4F08-8E1A-7B756F6E8F3E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/Convolution-Radiomics-Wavelet.xlsx
+++ b/Convolution-Radiomics-Wavelet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HN-Data-1\教育\講義\講義2年生-AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C85957D-9932-4E37-8636-05352A0549D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3F8346-F485-48DF-ADCD-B3116E1A735B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="11" r:id="rId1"/>
@@ -1249,41 +1249,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>上記手順での動作はJuliaで稼動する「Radiomics.jl」でも同じであることを確認した。</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウキ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テジュン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ドウサ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>カドウ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>オナ</t>
-    </rPh>
-    <rPh sb="43" eb="45">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://github.com/AIM-Harvard/pyradiomics</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://github.com/aujinen/pyradiomics_edu</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://www.radiomicsjl.org/</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>https://github.com/pzaffino/Radiomics.jl</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1521,6 +1487,73 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>得られるGLCM特徴量は、対象画像の異方性の影響を受けやすい。</t>
+    <rPh sb="0" eb="1">
+      <t>エ</t>
+    </rPh>
+    <rPh sb="8" eb="11">
+      <t>トクチョウリョウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="18" eb="21">
+      <t>イホウセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>エイキョウ</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>ウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://github.com/aujinen/pyradiomics_edu/blob/master/workspace/check_P_glcm.ipynb</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>`weightingNorm`を'no_weighting'に設定すれば、対象画像の異方性が平均化され相対的に弱まったGLCM特徴量を得る。</t>
+    <rPh sb="31" eb="33">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>タイショウ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ガゾウ</t>
+    </rPh>
+    <rPh sb="42" eb="45">
+      <t>イホウセイ</t>
+    </rPh>
+    <rPh sb="46" eb="49">
+      <t>ヘイキンカ</t>
+    </rPh>
+    <rPh sb="51" eb="54">
+      <t>ソウタイテキ</t>
+    </rPh>
+    <rPh sb="55" eb="56">
+      <t>ヨワ</t>
+    </rPh>
+    <rPh sb="63" eb="65">
+      <t>トクチョウ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
+      <t>リョウ</t>
+    </rPh>
+    <rPh sb="67" eb="68">
+      <t>エ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://github.com/aujinen/pyradiomics_edu/blob/master/workspace/radiomics_julia_2D.ipynb</t>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -1532,7 +1565,7 @@
     <numFmt numFmtId="178" formatCode="0.00000"/>
     <numFmt numFmtId="179" formatCode="0.0000_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1572,6 +1605,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="ＭＳ ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="ＭＳ ゴシック"/>
       <family val="2"/>
       <charset val="128"/>
@@ -2885,7 +2924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="283">
+  <cellXfs count="296">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3634,6 +3673,15 @@
     <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3706,6 +3754,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3723,15 +3780,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3757,11 +3805,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="63" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="64" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="41" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4565,13 +4643,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>259052</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>23829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>225635</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>59688</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4631,15 +4709,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>268940</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>11206</xdr:colOff>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>116540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>242046</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4655,8 +4733,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2617693" y="3415552"/>
-          <a:ext cx="797859" cy="448236"/>
+          <a:off x="3429000" y="3545540"/>
+          <a:ext cx="824752" cy="439272"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4699,15 +4777,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>268940</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>80682</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>259976</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>116542</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4723,8 +4801,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2617693" y="4410635"/>
-          <a:ext cx="815789" cy="448236"/>
+          <a:off x="3417794" y="4518211"/>
+          <a:ext cx="853888" cy="439272"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -4769,13 +4847,13 @@
     <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>8041</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>185194</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>270459</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>14866</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4838,12 +4916,12 @@
       <xdr:col>22</xdr:col>
       <xdr:colOff>914400</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>17929</xdr:rowOff>
+      <xdr:rowOff>44823</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>58271</xdr:colOff>
-      <xdr:row>28</xdr:row>
+      <xdr:row>29</xdr:row>
       <xdr:rowOff>179294</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4859,8 +4937,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="6990229" y="3659841"/>
-          <a:ext cx="4285130" cy="300318"/>
+          <a:off x="8436908" y="3627344"/>
+          <a:ext cx="4370295" cy="432548"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst>
@@ -4908,13 +4986,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>62754</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>62751</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>324972</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>170330</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -4987,13 +5065,13 @@
       <xdr:col>31</xdr:col>
       <xdr:colOff>178445</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>52552</xdr:rowOff>
+      <xdr:rowOff>22411</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>32</xdr:col>
       <xdr:colOff>354183</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>201705</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5008,8 +5086,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000">
-          <a:off x="15403722" y="2398098"/>
-          <a:ext cx="2166213" cy="702415"/>
+          <a:off x="14357711" y="2483880"/>
+          <a:ext cx="2398059" cy="702415"/>
         </a:xfrm>
         <a:prstGeom prst="rightArrow">
           <a:avLst/>
@@ -5121,14 +5199,14 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>652181</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:colOff>11207</xdr:colOff>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>142314</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>459441</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:colOff>459442</xdr:colOff>
+      <xdr:row>30</xdr:row>
       <xdr:rowOff>33617</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5144,8 +5222,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15242240" y="5588373"/>
-          <a:ext cx="2227730" cy="294715"/>
+          <a:off x="14287501" y="5790079"/>
+          <a:ext cx="2252382" cy="294714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5181,6 +5259,7 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
+          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
             <a:t>`weightingNorm` = 'no_weighting'</a:t>
@@ -5195,13 +5274,13 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>44824</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>48184</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>981634</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>78441</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5260,6 +5339,244 @@
             <a:t>`weightingNorm` = None</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>717176</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>67235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>268939</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>179295</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="吹き出し: 角を丸めた四角形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34EEB0DE-3150-4247-BDA8-12CA52C5C107}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12348882" y="1882588"/>
+          <a:ext cx="2420469" cy="918883"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -116474"/>
+            <a:gd name="adj2" fmla="val -39288"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>対象画像の異方性が残りやすい</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>GLCM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>特徴量</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>358588</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>123265</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>26893</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="吹き出し: 角を丸めた四角形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9F35B16D-54E2-47D9-8C75-8717D8F346FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11990294" y="3160058"/>
+          <a:ext cx="2409265" cy="900953"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 98391"/>
+            <a:gd name="adj2" fmla="val -50171"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>対象画像の</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>異方性</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>が平均化された</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>GLCM</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>特徴量</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6614,57 +6931,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="C4" s="281" t="s">
-        <v>103</v>
+      <c r="C4" s="241" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="C5" s="281" t="s">
-        <v>104</v>
+      <c r="C5" s="241" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
       <c r="B6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="C7" s="281" t="s">
-        <v>105</v>
+      <c r="C7" s="241" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="C8" s="281" t="s">
-        <v>106</v>
+      <c r="C8" s="241" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="C9" s="281" t="s">
-        <v>107</v>
+      <c r="C9" s="241" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="C10" s="281" t="s">
-        <v>108</v>
+      <c r="C10" s="241" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="281" t="s">
-        <v>109</v>
+      <c r="B11" s="241" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -6693,8 +7010,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -7492,14 +7809,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="240" t="s">
+      <c r="X15" s="243" t="s">
         <v>19</v>
       </c>
-      <c r="Y15" s="241"/>
-      <c r="Z15" s="241"/>
-      <c r="AA15" s="241"/>
-      <c r="AB15" s="241"/>
-      <c r="AC15" s="242"/>
+      <c r="Y15" s="244"/>
+      <c r="Z15" s="244"/>
+      <c r="AA15" s="244"/>
+      <c r="AB15" s="244"/>
+      <c r="AC15" s="245"/>
     </row>
     <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -7545,12 +7862,12 @@
       <c r="Q16" s="49"/>
       <c r="R16" s="49"/>
       <c r="S16" s="49"/>
-      <c r="X16" s="243"/>
-      <c r="Y16" s="244"/>
-      <c r="Z16" s="244"/>
-      <c r="AA16" s="244"/>
-      <c r="AB16" s="244"/>
-      <c r="AC16" s="245"/>
+      <c r="X16" s="246"/>
+      <c r="Y16" s="247"/>
+      <c r="Z16" s="247"/>
+      <c r="AA16" s="247"/>
+      <c r="AB16" s="247"/>
+      <c r="AC16" s="248"/>
     </row>
     <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -7593,12 +7910,12 @@
       <c r="Q17" s="49"/>
       <c r="R17" s="49"/>
       <c r="S17" s="49"/>
-      <c r="X17" s="243"/>
-      <c r="Y17" s="244"/>
-      <c r="Z17" s="244"/>
-      <c r="AA17" s="244"/>
-      <c r="AB17" s="244"/>
-      <c r="AC17" s="245"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="247"/>
+      <c r="Z17" s="247"/>
+      <c r="AA17" s="247"/>
+      <c r="AB17" s="247"/>
+      <c r="AC17" s="248"/>
     </row>
     <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
@@ -7641,12 +7958,12 @@
       <c r="Q18" s="49"/>
       <c r="R18" s="49"/>
       <c r="S18" s="49"/>
-      <c r="X18" s="243"/>
-      <c r="Y18" s="244"/>
-      <c r="Z18" s="244"/>
-      <c r="AA18" s="244"/>
-      <c r="AB18" s="244"/>
-      <c r="AC18" s="245"/>
+      <c r="X18" s="246"/>
+      <c r="Y18" s="247"/>
+      <c r="Z18" s="247"/>
+      <c r="AA18" s="247"/>
+      <c r="AB18" s="247"/>
+      <c r="AC18" s="248"/>
     </row>
     <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -7689,12 +8006,12 @@
       <c r="Q19" s="49"/>
       <c r="R19" s="49"/>
       <c r="S19" s="49"/>
-      <c r="X19" s="243"/>
-      <c r="Y19" s="244"/>
-      <c r="Z19" s="244"/>
-      <c r="AA19" s="244"/>
-      <c r="AB19" s="244"/>
-      <c r="AC19" s="245"/>
+      <c r="X19" s="246"/>
+      <c r="Y19" s="247"/>
+      <c r="Z19" s="247"/>
+      <c r="AA19" s="247"/>
+      <c r="AB19" s="247"/>
+      <c r="AC19" s="248"/>
     </row>
     <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
@@ -7737,12 +8054,12 @@
       <c r="Q20" s="49"/>
       <c r="R20" s="49"/>
       <c r="S20" s="49"/>
-      <c r="X20" s="243"/>
-      <c r="Y20" s="244"/>
-      <c r="Z20" s="244"/>
-      <c r="AA20" s="244"/>
-      <c r="AB20" s="244"/>
-      <c r="AC20" s="245"/>
+      <c r="X20" s="246"/>
+      <c r="Y20" s="247"/>
+      <c r="Z20" s="247"/>
+      <c r="AA20" s="247"/>
+      <c r="AB20" s="247"/>
+      <c r="AC20" s="248"/>
     </row>
     <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
@@ -7785,12 +8102,12 @@
       <c r="Q21" s="49"/>
       <c r="R21" s="49"/>
       <c r="S21" s="49"/>
-      <c r="X21" s="243"/>
-      <c r="Y21" s="244"/>
-      <c r="Z21" s="244"/>
-      <c r="AA21" s="244"/>
-      <c r="AB21" s="244"/>
-      <c r="AC21" s="245"/>
+      <c r="X21" s="246"/>
+      <c r="Y21" s="247"/>
+      <c r="Z21" s="247"/>
+      <c r="AA21" s="247"/>
+      <c r="AB21" s="247"/>
+      <c r="AC21" s="248"/>
     </row>
     <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -7833,12 +8150,12 @@
       <c r="Q22" s="49"/>
       <c r="R22" s="49"/>
       <c r="S22" s="49"/>
-      <c r="X22" s="243"/>
-      <c r="Y22" s="244"/>
-      <c r="Z22" s="244"/>
-      <c r="AA22" s="244"/>
-      <c r="AB22" s="244"/>
-      <c r="AC22" s="245"/>
+      <c r="X22" s="246"/>
+      <c r="Y22" s="247"/>
+      <c r="Z22" s="247"/>
+      <c r="AA22" s="247"/>
+      <c r="AB22" s="247"/>
+      <c r="AC22" s="248"/>
     </row>
     <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
@@ -7881,12 +8198,12 @@
       <c r="Q23" s="49"/>
       <c r="R23" s="49"/>
       <c r="S23" s="49"/>
-      <c r="X23" s="246"/>
-      <c r="Y23" s="247"/>
-      <c r="Z23" s="247"/>
-      <c r="AA23" s="247"/>
-      <c r="AB23" s="247"/>
-      <c r="AC23" s="248"/>
+      <c r="X23" s="249"/>
+      <c r="Y23" s="250"/>
+      <c r="Z23" s="250"/>
+      <c r="AA23" s="250"/>
+      <c r="AB23" s="250"/>
+      <c r="AC23" s="251"/>
     </row>
     <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
@@ -7991,8 +8308,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>0</v>
@@ -8790,14 +9107,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="240" t="s">
+      <c r="X15" s="243" t="s">
         <v>23</v>
       </c>
-      <c r="Y15" s="241"/>
-      <c r="Z15" s="241"/>
-      <c r="AA15" s="241"/>
-      <c r="AB15" s="241"/>
-      <c r="AC15" s="242"/>
+      <c r="Y15" s="244"/>
+      <c r="Z15" s="244"/>
+      <c r="AA15" s="244"/>
+      <c r="AB15" s="244"/>
+      <c r="AC15" s="245"/>
     </row>
     <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -8864,12 +9181,12 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="X16" s="243"/>
-      <c r="Y16" s="244"/>
-      <c r="Z16" s="244"/>
-      <c r="AA16" s="244"/>
-      <c r="AB16" s="244"/>
-      <c r="AC16" s="245"/>
+      <c r="X16" s="246"/>
+      <c r="Y16" s="247"/>
+      <c r="Z16" s="247"/>
+      <c r="AA16" s="247"/>
+      <c r="AB16" s="247"/>
+      <c r="AC16" s="248"/>
     </row>
     <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -8936,12 +9253,12 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="X17" s="243"/>
-      <c r="Y17" s="244"/>
-      <c r="Z17" s="244"/>
-      <c r="AA17" s="244"/>
-      <c r="AB17" s="244"/>
-      <c r="AC17" s="245"/>
+      <c r="X17" s="246"/>
+      <c r="Y17" s="247"/>
+      <c r="Z17" s="247"/>
+      <c r="AA17" s="247"/>
+      <c r="AB17" s="247"/>
+      <c r="AC17" s="248"/>
     </row>
     <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
@@ -9008,12 +9325,12 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="X18" s="243"/>
-      <c r="Y18" s="244"/>
-      <c r="Z18" s="244"/>
-      <c r="AA18" s="244"/>
-      <c r="AB18" s="244"/>
-      <c r="AC18" s="245"/>
+      <c r="X18" s="246"/>
+      <c r="Y18" s="247"/>
+      <c r="Z18" s="247"/>
+      <c r="AA18" s="247"/>
+      <c r="AB18" s="247"/>
+      <c r="AC18" s="248"/>
     </row>
     <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -9080,12 +9397,12 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="X19" s="243"/>
-      <c r="Y19" s="244"/>
-      <c r="Z19" s="244"/>
-      <c r="AA19" s="244"/>
-      <c r="AB19" s="244"/>
-      <c r="AC19" s="245"/>
+      <c r="X19" s="246"/>
+      <c r="Y19" s="247"/>
+      <c r="Z19" s="247"/>
+      <c r="AA19" s="247"/>
+      <c r="AB19" s="247"/>
+      <c r="AC19" s="248"/>
     </row>
     <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
@@ -9152,12 +9469,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="X20" s="243"/>
-      <c r="Y20" s="244"/>
-      <c r="Z20" s="244"/>
-      <c r="AA20" s="244"/>
-      <c r="AB20" s="244"/>
-      <c r="AC20" s="245"/>
+      <c r="X20" s="246"/>
+      <c r="Y20" s="247"/>
+      <c r="Z20" s="247"/>
+      <c r="AA20" s="247"/>
+      <c r="AB20" s="247"/>
+      <c r="AC20" s="248"/>
     </row>
     <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
@@ -9224,12 +9541,12 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="X21" s="243"/>
-      <c r="Y21" s="244"/>
-      <c r="Z21" s="244"/>
-      <c r="AA21" s="244"/>
-      <c r="AB21" s="244"/>
-      <c r="AC21" s="245"/>
+      <c r="X21" s="246"/>
+      <c r="Y21" s="247"/>
+      <c r="Z21" s="247"/>
+      <c r="AA21" s="247"/>
+      <c r="AB21" s="247"/>
+      <c r="AC21" s="248"/>
     </row>
     <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -9296,12 +9613,12 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="X22" s="243"/>
-      <c r="Y22" s="244"/>
-      <c r="Z22" s="244"/>
-      <c r="AA22" s="244"/>
-      <c r="AB22" s="244"/>
-      <c r="AC22" s="245"/>
+      <c r="X22" s="246"/>
+      <c r="Y22" s="247"/>
+      <c r="Z22" s="247"/>
+      <c r="AA22" s="247"/>
+      <c r="AB22" s="247"/>
+      <c r="AC22" s="248"/>
     </row>
     <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
@@ -9368,12 +9685,12 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="X23" s="246"/>
-      <c r="Y23" s="247"/>
-      <c r="Z23" s="247"/>
-      <c r="AA23" s="247"/>
-      <c r="AB23" s="247"/>
-      <c r="AC23" s="248"/>
+      <c r="X23" s="249"/>
+      <c r="Y23" s="250"/>
+      <c r="Z23" s="250"/>
+      <c r="AA23" s="250"/>
+      <c r="AB23" s="250"/>
+      <c r="AC23" s="251"/>
     </row>
     <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
@@ -9479,8 +9796,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>73</v>
@@ -9844,25 +10161,25 @@
         <v>1</v>
       </c>
       <c r="T9" s="20"/>
-      <c r="X9" s="252" t="s">
+      <c r="X9" s="255" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
-      <c r="AA9" s="254"/>
-      <c r="AF9" s="252" t="s">
+      <c r="Y9" s="256"/>
+      <c r="Z9" s="256"/>
+      <c r="AA9" s="257"/>
+      <c r="AF9" s="255" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="253"/>
-      <c r="AH9" s="253"/>
-      <c r="AI9" s="254"/>
-      <c r="AL9" s="255" t="s">
+      <c r="AG9" s="256"/>
+      <c r="AH9" s="256"/>
+      <c r="AI9" s="257"/>
+      <c r="AL9" s="258" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="256"/>
-      <c r="AN9" s="256"/>
-      <c r="AO9" s="256"/>
-      <c r="AP9" s="257"/>
+      <c r="AM9" s="259"/>
+      <c r="AN9" s="259"/>
+      <c r="AO9" s="259"/>
+      <c r="AP9" s="260"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -9947,11 +10264,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="258"/>
-      <c r="AM10" s="259"/>
-      <c r="AN10" s="259"/>
-      <c r="AO10" s="259"/>
-      <c r="AP10" s="260"/>
+      <c r="AL10" s="261"/>
+      <c r="AM10" s="262"/>
+      <c r="AN10" s="262"/>
+      <c r="AO10" s="262"/>
+      <c r="AP10" s="263"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -10015,7 +10332,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="20"/>
-      <c r="V11" s="249" t="s">
+      <c r="V11" s="252" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -10037,7 +10354,7 @@
         <f>SUM(AC17:AI24)</f>
         <v>1</v>
       </c>
-      <c r="AD11" s="249" t="s">
+      <c r="AD11" s="252" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -10145,7 +10462,7 @@
         <v>3</v>
       </c>
       <c r="T12" s="20"/>
-      <c r="V12" s="250"/>
+      <c r="V12" s="253"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -10165,7 +10482,7 @@
         <f>SUM(AC27:AI34)</f>
         <v>4</v>
       </c>
-      <c r="AD12" s="250"/>
+      <c r="AD12" s="253"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -10271,7 +10588,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="20"/>
-      <c r="V13" s="250"/>
+      <c r="V13" s="253"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -10291,7 +10608,7 @@
         <f>SUM(AC37:AI44)</f>
         <v>1</v>
       </c>
-      <c r="AD13" s="250"/>
+      <c r="AD13" s="253"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -10349,7 +10666,7 @@
       <c r="R14" s="20"/>
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
-      <c r="V14" s="251"/>
+      <c r="V14" s="254"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -10369,7 +10686,7 @@
         <f>SUM(AC47:AI54)</f>
         <v>1</v>
       </c>
-      <c r="AD14" s="251"/>
+      <c r="AD14" s="254"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -14877,8 +15194,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>74</v>
@@ -14979,14 +15296,14 @@
         <v>0</v>
       </c>
       <c r="Z3" s="211"/>
-      <c r="AA3" s="262" t="s">
+      <c r="AA3" s="265" t="s">
         <v>72</v>
       </c>
-      <c r="AB3" s="262"/>
-      <c r="AC3" s="262"/>
-      <c r="AD3" s="262"/>
-      <c r="AE3" s="262"/>
-      <c r="AF3" s="262"/>
+      <c r="AB3" s="265"/>
+      <c r="AC3" s="265"/>
+      <c r="AD3" s="265"/>
+      <c r="AE3" s="265"/>
+      <c r="AF3" s="265"/>
     </row>
     <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
@@ -15036,24 +15353,24 @@
       <c r="Z4" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="AA4" s="261" t="s">
+      <c r="AA4" s="264" t="s">
         <v>70</v>
       </c>
-      <c r="AB4" s="261"/>
-      <c r="AC4" s="261"/>
-      <c r="AD4" s="261"/>
-      <c r="AE4" s="261"/>
-      <c r="AF4" s="261"/>
-      <c r="AG4" s="261"/>
-      <c r="AH4" s="261"/>
-      <c r="AI4" s="261"/>
-      <c r="AJ4" s="261"/>
-      <c r="AK4" s="261"/>
-      <c r="AL4" s="261"/>
-      <c r="AM4" s="261"/>
-      <c r="AN4" s="261"/>
-      <c r="AO4" s="261"/>
-      <c r="AP4" s="261"/>
+      <c r="AB4" s="264"/>
+      <c r="AC4" s="264"/>
+      <c r="AD4" s="264"/>
+      <c r="AE4" s="264"/>
+      <c r="AF4" s="264"/>
+      <c r="AG4" s="264"/>
+      <c r="AH4" s="264"/>
+      <c r="AI4" s="264"/>
+      <c r="AJ4" s="264"/>
+      <c r="AK4" s="264"/>
+      <c r="AL4" s="264"/>
+      <c r="AM4" s="264"/>
+      <c r="AN4" s="264"/>
+      <c r="AO4" s="264"/>
+      <c r="AP4" s="264"/>
     </row>
     <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -15406,25 +15723,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="252" t="s">
+      <c r="X9" s="255" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="253"/>
-      <c r="Z9" s="253"/>
-      <c r="AA9" s="254"/>
-      <c r="AF9" s="252" t="s">
+      <c r="Y9" s="256"/>
+      <c r="Z9" s="256"/>
+      <c r="AA9" s="257"/>
+      <c r="AF9" s="255" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="253"/>
-      <c r="AH9" s="253"/>
-      <c r="AI9" s="254"/>
-      <c r="AL9" s="263" t="s">
+      <c r="AG9" s="256"/>
+      <c r="AH9" s="256"/>
+      <c r="AI9" s="257"/>
+      <c r="AL9" s="266" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="263"/>
-      <c r="AN9" s="263"/>
-      <c r="AO9" s="263"/>
-      <c r="AP9" s="263"/>
+      <c r="AM9" s="266"/>
+      <c r="AN9" s="266"/>
+      <c r="AO9" s="266"/>
+      <c r="AP9" s="266"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -15515,11 +15832,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="263"/>
-      <c r="AM10" s="263"/>
-      <c r="AN10" s="263"/>
-      <c r="AO10" s="263"/>
-      <c r="AP10" s="263"/>
+      <c r="AL10" s="266"/>
+      <c r="AM10" s="266"/>
+      <c r="AN10" s="266"/>
+      <c r="AO10" s="266"/>
+      <c r="AP10" s="266"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -15589,7 +15906,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="249" t="s">
+      <c r="V11" s="252" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -15611,7 +15928,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>4</v>
       </c>
-      <c r="AD11" s="249" t="s">
+      <c r="AD11" s="252" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -15725,7 +16042,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="250"/>
+      <c r="V12" s="253"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -15745,7 +16062,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>6</v>
       </c>
-      <c r="AD12" s="250"/>
+      <c r="AD12" s="253"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -15857,7 +16174,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="250"/>
+      <c r="V13" s="253"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -15877,7 +16194,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>2</v>
       </c>
-      <c r="AD13" s="250"/>
+      <c r="AD13" s="253"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -15965,7 +16282,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="251"/>
+      <c r="V14" s="254"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -15985,7 +16302,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>2</v>
       </c>
-      <c r="AD14" s="251"/>
+      <c r="AD14" s="254"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -20926,8 +21243,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>75</v>
@@ -20986,31 +21303,31 @@
       <c r="J2" t="s">
         <v>56</v>
       </c>
-      <c r="V2" s="264" t="s">
+      <c r="V2" s="270" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="265"/>
-      <c r="X2" s="265"/>
-      <c r="Y2" s="265"/>
-      <c r="Z2" s="265"/>
-      <c r="AA2" s="265"/>
-      <c r="AB2" s="265"/>
-      <c r="AC2" s="265"/>
-      <c r="AD2" s="265"/>
-      <c r="AE2" s="265"/>
-      <c r="AF2" s="265"/>
-      <c r="AG2" s="265"/>
-      <c r="AH2" s="265"/>
-      <c r="AI2" s="265"/>
-      <c r="AJ2" s="265"/>
-      <c r="AK2" s="265"/>
-      <c r="AL2" s="265"/>
-      <c r="AM2" s="265"/>
-      <c r="AN2" s="265"/>
-      <c r="AO2" s="265"/>
-      <c r="AP2" s="265"/>
-      <c r="AQ2" s="265"/>
-      <c r="AR2" s="266"/>
+      <c r="W2" s="271"/>
+      <c r="X2" s="271"/>
+      <c r="Y2" s="271"/>
+      <c r="Z2" s="271"/>
+      <c r="AA2" s="271"/>
+      <c r="AB2" s="271"/>
+      <c r="AC2" s="271"/>
+      <c r="AD2" s="271"/>
+      <c r="AE2" s="271"/>
+      <c r="AF2" s="271"/>
+      <c r="AG2" s="271"/>
+      <c r="AH2" s="271"/>
+      <c r="AI2" s="271"/>
+      <c r="AJ2" s="271"/>
+      <c r="AK2" s="271"/>
+      <c r="AL2" s="271"/>
+      <c r="AM2" s="271"/>
+      <c r="AN2" s="271"/>
+      <c r="AO2" s="271"/>
+      <c r="AP2" s="271"/>
+      <c r="AQ2" s="271"/>
+      <c r="AR2" s="272"/>
     </row>
     <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
@@ -21033,31 +21350,31 @@
       <c r="O3" t="s">
         <v>5</v>
       </c>
-      <c r="V3" s="264" t="s">
+      <c r="V3" s="270" t="s">
         <v>77</v>
       </c>
-      <c r="W3" s="265"/>
-      <c r="X3" s="265"/>
-      <c r="Y3" s="265"/>
-      <c r="Z3" s="265"/>
-      <c r="AA3" s="265"/>
-      <c r="AB3" s="265"/>
-      <c r="AC3" s="265"/>
-      <c r="AD3" s="265"/>
-      <c r="AE3" s="265"/>
-      <c r="AF3" s="265"/>
-      <c r="AG3" s="265"/>
-      <c r="AH3" s="265"/>
-      <c r="AI3" s="265"/>
-      <c r="AJ3" s="265"/>
-      <c r="AK3" s="265"/>
-      <c r="AL3" s="265"/>
-      <c r="AM3" s="265"/>
-      <c r="AN3" s="265"/>
-      <c r="AO3" s="265"/>
-      <c r="AP3" s="265"/>
-      <c r="AQ3" s="265"/>
-      <c r="AR3" s="266"/>
+      <c r="W3" s="271"/>
+      <c r="X3" s="271"/>
+      <c r="Y3" s="271"/>
+      <c r="Z3" s="271"/>
+      <c r="AA3" s="271"/>
+      <c r="AB3" s="271"/>
+      <c r="AC3" s="271"/>
+      <c r="AD3" s="271"/>
+      <c r="AE3" s="271"/>
+      <c r="AF3" s="271"/>
+      <c r="AG3" s="271"/>
+      <c r="AH3" s="271"/>
+      <c r="AI3" s="271"/>
+      <c r="AJ3" s="271"/>
+      <c r="AK3" s="271"/>
+      <c r="AL3" s="271"/>
+      <c r="AM3" s="271"/>
+      <c r="AN3" s="271"/>
+      <c r="AO3" s="271"/>
+      <c r="AP3" s="271"/>
+      <c r="AQ3" s="271"/>
+      <c r="AR3" s="272"/>
     </row>
     <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
@@ -21092,31 +21409,31 @@
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
-      <c r="V4" s="267" t="s">
+      <c r="V4" s="273" t="s">
         <v>78</v>
       </c>
-      <c r="W4" s="268"/>
-      <c r="X4" s="268"/>
-      <c r="Y4" s="268"/>
-      <c r="Z4" s="268"/>
-      <c r="AA4" s="268"/>
-      <c r="AB4" s="268"/>
-      <c r="AC4" s="268"/>
-      <c r="AD4" s="268"/>
-      <c r="AE4" s="268"/>
-      <c r="AF4" s="268"/>
-      <c r="AG4" s="268"/>
-      <c r="AH4" s="268"/>
-      <c r="AI4" s="268"/>
-      <c r="AJ4" s="268"/>
-      <c r="AK4" s="268"/>
-      <c r="AL4" s="268"/>
-      <c r="AM4" s="268"/>
-      <c r="AN4" s="268"/>
-      <c r="AO4" s="268"/>
-      <c r="AP4" s="268"/>
-      <c r="AQ4" s="268"/>
-      <c r="AR4" s="269"/>
+      <c r="W4" s="274"/>
+      <c r="X4" s="274"/>
+      <c r="Y4" s="274"/>
+      <c r="Z4" s="274"/>
+      <c r="AA4" s="274"/>
+      <c r="AB4" s="274"/>
+      <c r="AC4" s="274"/>
+      <c r="AD4" s="274"/>
+      <c r="AE4" s="274"/>
+      <c r="AF4" s="274"/>
+      <c r="AG4" s="274"/>
+      <c r="AH4" s="274"/>
+      <c r="AI4" s="274"/>
+      <c r="AJ4" s="274"/>
+      <c r="AK4" s="274"/>
+      <c r="AL4" s="274"/>
+      <c r="AM4" s="274"/>
+      <c r="AN4" s="274"/>
+      <c r="AO4" s="274"/>
+      <c r="AP4" s="274"/>
+      <c r="AQ4" s="274"/>
+      <c r="AR4" s="275"/>
     </row>
     <row r="5" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
@@ -21162,31 +21479,31 @@
         <f>(S5+T6)/2</f>
         <v>0</v>
       </c>
-      <c r="V5" s="264" t="s">
+      <c r="V5" s="270" t="s">
         <v>76</v>
       </c>
-      <c r="W5" s="265"/>
-      <c r="X5" s="265"/>
-      <c r="Y5" s="265"/>
-      <c r="Z5" s="265"/>
-      <c r="AA5" s="265"/>
-      <c r="AB5" s="265"/>
-      <c r="AC5" s="265"/>
-      <c r="AD5" s="265"/>
-      <c r="AE5" s="265"/>
-      <c r="AF5" s="265"/>
-      <c r="AG5" s="265"/>
-      <c r="AH5" s="265"/>
-      <c r="AI5" s="265"/>
-      <c r="AJ5" s="265"/>
-      <c r="AK5" s="265"/>
-      <c r="AL5" s="265"/>
-      <c r="AM5" s="265"/>
-      <c r="AN5" s="265"/>
-      <c r="AO5" s="265"/>
-      <c r="AP5" s="265"/>
-      <c r="AQ5" s="265"/>
-      <c r="AR5" s="266"/>
+      <c r="W5" s="271"/>
+      <c r="X5" s="271"/>
+      <c r="Y5" s="271"/>
+      <c r="Z5" s="271"/>
+      <c r="AA5" s="271"/>
+      <c r="AB5" s="271"/>
+      <c r="AC5" s="271"/>
+      <c r="AD5" s="271"/>
+      <c r="AE5" s="271"/>
+      <c r="AF5" s="271"/>
+      <c r="AG5" s="271"/>
+      <c r="AH5" s="271"/>
+      <c r="AI5" s="271"/>
+      <c r="AJ5" s="271"/>
+      <c r="AK5" s="271"/>
+      <c r="AL5" s="271"/>
+      <c r="AM5" s="271"/>
+      <c r="AN5" s="271"/>
+      <c r="AO5" s="271"/>
+      <c r="AP5" s="271"/>
+      <c r="AQ5" s="271"/>
+      <c r="AR5" s="272"/>
     </row>
     <row r="6" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
@@ -21253,31 +21570,31 @@
         <f>S6*$N$3</f>
         <v>0</v>
       </c>
-      <c r="V6" s="267" t="s">
+      <c r="V6" s="273" t="s">
         <v>79</v>
       </c>
-      <c r="W6" s="268"/>
-      <c r="X6" s="268"/>
-      <c r="Y6" s="268"/>
-      <c r="Z6" s="268"/>
-      <c r="AA6" s="268"/>
-      <c r="AB6" s="268"/>
-      <c r="AC6" s="268"/>
-      <c r="AD6" s="268"/>
-      <c r="AE6" s="268"/>
-      <c r="AF6" s="268"/>
-      <c r="AG6" s="268"/>
-      <c r="AH6" s="268"/>
-      <c r="AI6" s="268"/>
-      <c r="AJ6" s="268"/>
-      <c r="AK6" s="268"/>
-      <c r="AL6" s="268"/>
-      <c r="AM6" s="268"/>
-      <c r="AN6" s="268"/>
-      <c r="AO6" s="268"/>
-      <c r="AP6" s="268"/>
-      <c r="AQ6" s="268"/>
-      <c r="AR6" s="269"/>
+      <c r="W6" s="274"/>
+      <c r="X6" s="274"/>
+      <c r="Y6" s="274"/>
+      <c r="Z6" s="274"/>
+      <c r="AA6" s="274"/>
+      <c r="AB6" s="274"/>
+      <c r="AC6" s="274"/>
+      <c r="AD6" s="274"/>
+      <c r="AE6" s="274"/>
+      <c r="AF6" s="274"/>
+      <c r="AG6" s="274"/>
+      <c r="AH6" s="274"/>
+      <c r="AI6" s="274"/>
+      <c r="AJ6" s="274"/>
+      <c r="AK6" s="274"/>
+      <c r="AL6" s="274"/>
+      <c r="AM6" s="274"/>
+      <c r="AN6" s="274"/>
+      <c r="AO6" s="274"/>
+      <c r="AP6" s="274"/>
+      <c r="AQ6" s="274"/>
+      <c r="AR6" s="275"/>
     </row>
     <row r="7" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
@@ -21482,25 +21799,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="270" t="s">
+      <c r="X9" s="267" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="271"/>
-      <c r="Z9" s="271"/>
-      <c r="AA9" s="272"/>
-      <c r="AF9" s="270" t="s">
+      <c r="Y9" s="268"/>
+      <c r="Z9" s="268"/>
+      <c r="AA9" s="269"/>
+      <c r="AF9" s="267" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="271"/>
-      <c r="AH9" s="271"/>
-      <c r="AI9" s="272"/>
-      <c r="AL9" s="263" t="s">
+      <c r="AG9" s="268"/>
+      <c r="AH9" s="268"/>
+      <c r="AI9" s="269"/>
+      <c r="AL9" s="266" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="263"/>
-      <c r="AN9" s="263"/>
-      <c r="AO9" s="263"/>
-      <c r="AP9" s="263"/>
+      <c r="AM9" s="266"/>
+      <c r="AN9" s="266"/>
+      <c r="AO9" s="266"/>
+      <c r="AP9" s="266"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -21591,11 +21908,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="263"/>
-      <c r="AM10" s="263"/>
-      <c r="AN10" s="263"/>
-      <c r="AO10" s="263"/>
-      <c r="AP10" s="263"/>
+      <c r="AL10" s="266"/>
+      <c r="AM10" s="266"/>
+      <c r="AN10" s="266"/>
+      <c r="AO10" s="266"/>
+      <c r="AP10" s="266"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -21665,7 +21982,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="249" t="s">
+      <c r="V11" s="252" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -21687,7 +22004,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>13</v>
       </c>
-      <c r="AD11" s="249" t="s">
+      <c r="AD11" s="252" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -21801,7 +22118,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="250"/>
+      <c r="V12" s="253"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -21821,7 +22138,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>20</v>
       </c>
-      <c r="AD12" s="250"/>
+      <c r="AD12" s="253"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -21933,7 +22250,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="250"/>
+      <c r="V13" s="253"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -21953,7 +22270,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>7</v>
       </c>
-      <c r="AD13" s="250"/>
+      <c r="AD13" s="253"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -22041,7 +22358,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="251"/>
+      <c r="V14" s="254"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -22061,7 +22378,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>10</v>
       </c>
-      <c r="AD14" s="251"/>
+      <c r="AD14" s="254"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -26928,16 +27245,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="a7AHORGKHpMUjRkn5ERUm+ygSQ4XxlgmW0+c9l1HPGNWdceOfaHMTxam3gp7rwV50up4xOklDw6DgOSDy+jgQg==" saltValue="iSPclcrsv8KynPC2yADwnA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
+    <mergeCell ref="V2:AR2"/>
+    <mergeCell ref="V3:AR3"/>
+    <mergeCell ref="V4:AR4"/>
+    <mergeCell ref="V5:AR5"/>
+    <mergeCell ref="V6:AR6"/>
     <mergeCell ref="AL9:AP10"/>
     <mergeCell ref="X9:AA9"/>
     <mergeCell ref="AF9:AI9"/>
     <mergeCell ref="V11:V14"/>
     <mergeCell ref="AD11:AD14"/>
-    <mergeCell ref="V2:AR2"/>
-    <mergeCell ref="V3:AR3"/>
-    <mergeCell ref="V4:AR4"/>
-    <mergeCell ref="V5:AR5"/>
-    <mergeCell ref="V6:AR6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B6:I13">
@@ -26991,7 +27308,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9884B89F-F41E-46EF-87E9-F2DD32687A57}">
-  <dimension ref="A1:AH29"/>
+  <dimension ref="A1:AM30"/>
   <sheetFormatPr defaultRowHeight="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -27004,17 +27321,17 @@
     <col min="23" max="23" width="16.875" bestFit="1" customWidth="1"/>
     <col min="24" max="25" width="11.125" customWidth="1"/>
     <col min="26" max="26" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="28" max="30" width="3" customWidth="1"/>
     <col min="31" max="34" width="6.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+    <row r="1" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C1" s="19"/>
       <c r="D1" s="19"/>
@@ -27040,7 +27357,7 @@
       <c r="X1" s="19"/>
       <c r="Y1" s="19"/>
     </row>
-    <row r="2" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="166" t="s">
         <v>83</v>
       </c>
@@ -27061,9 +27378,10 @@
       <c r="Q2" s="212"/>
       <c r="R2" s="212"/>
       <c r="S2" s="212"/>
-      <c r="T2" s="213"/>
+      <c r="T2" s="212"/>
+      <c r="U2" s="213"/>
     </row>
-    <row r="3" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="214" t="s">
         <v>79</v>
       </c>
@@ -27084,75 +27402,78 @@
       <c r="Q3" s="28"/>
       <c r="R3" s="28"/>
       <c r="S3" s="28"/>
-      <c r="T3" s="215"/>
-      <c r="W3" s="273" t="s">
-        <v>90</v>
-      </c>
-      <c r="X3" s="273"/>
-      <c r="Y3" s="275" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z3" s="275"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="215"/>
+      <c r="W3" s="276" t="s">
+        <v>86</v>
+      </c>
+      <c r="X3" s="276"/>
+      <c r="Y3" s="278" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z3" s="278"/>
     </row>
-    <row r="4" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="217" t="s">
-        <v>85</v>
-      </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="215"/>
-      <c r="W4" s="274" t="s">
-        <v>91</v>
-      </c>
-      <c r="X4" s="274"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
+    <row r="4" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="284" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="287"/>
+      <c r="D4" s="287"/>
+      <c r="E4" s="287"/>
+      <c r="F4" s="287"/>
+      <c r="G4" s="287"/>
+      <c r="H4" s="287"/>
+      <c r="I4" s="287"/>
+      <c r="J4" s="287"/>
+      <c r="K4" s="287"/>
+      <c r="L4" s="287"/>
+      <c r="M4" s="287"/>
+      <c r="N4" s="287"/>
+      <c r="O4" s="287"/>
+      <c r="P4" s="287"/>
+      <c r="Q4" s="287"/>
+      <c r="R4" s="287"/>
+      <c r="S4" s="287"/>
+      <c r="T4" s="287"/>
+      <c r="U4" s="288"/>
+      <c r="W4" s="277" t="s">
+        <v>87</v>
+      </c>
+      <c r="X4" s="277"/>
+      <c r="Y4" s="278"/>
+      <c r="Z4" s="278"/>
       <c r="AE4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="218" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="109"/>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="109"/>
-      <c r="T5" s="110"/>
+    <row r="5" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="217" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="215"/>
       <c r="W5" s="88" t="s">
         <v>27</v>
       </c>
       <c r="X5" s="232">
-        <f>AVERAGE(X11,X16,X21,X26)</f>
+        <f>AVERAGE(X12,X17,X22,X27)</f>
         <v>0.18112244897959184</v>
       </c>
       <c r="Y5" s="233">
@@ -27175,33 +27496,34 @@
         <v>3.0952380952380953E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="166" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="212"/>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="212"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="212"/>
-      <c r="I6" s="212"/>
-      <c r="J6" s="212"/>
-      <c r="K6" s="212"/>
-      <c r="L6" s="212"/>
-      <c r="M6" s="212"/>
-      <c r="N6" s="212"/>
-      <c r="O6" s="212"/>
-      <c r="P6" s="212"/>
-      <c r="Q6" s="212"/>
-      <c r="R6" s="212"/>
-      <c r="S6" s="212"/>
-      <c r="T6" s="213"/>
+    <row r="6" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="218" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="109"/>
+      <c r="D6" s="109"/>
+      <c r="E6" s="109"/>
+      <c r="F6" s="109"/>
+      <c r="G6" s="109"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="109"/>
+      <c r="J6" s="109"/>
+      <c r="K6" s="109"/>
+      <c r="L6" s="109"/>
+      <c r="M6" s="109"/>
+      <c r="N6" s="109"/>
+      <c r="O6" s="109"/>
+      <c r="P6" s="109"/>
+      <c r="Q6" s="109"/>
+      <c r="R6" s="109"/>
+      <c r="S6" s="109"/>
+      <c r="T6" s="109"/>
+      <c r="U6" s="110"/>
       <c r="W6" s="88" t="s">
         <v>28</v>
       </c>
       <c r="X6" s="232">
-        <f>AVERAGE(X12,X17,X22,X27)</f>
+        <f>AVERAGE(X13,X18,X23,X28)</f>
         <v>2.0181760204081631</v>
       </c>
       <c r="Y6" s="233">
@@ -27224,33 +27546,34 @@
         <v>4.7619047619047616E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="217" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28"/>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28"/>
-      <c r="T7" s="215"/>
+    <row r="7" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="285" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="289"/>
+      <c r="D7" s="289"/>
+      <c r="E7" s="289"/>
+      <c r="F7" s="289"/>
+      <c r="G7" s="289"/>
+      <c r="H7" s="289"/>
+      <c r="I7" s="289"/>
+      <c r="J7" s="289"/>
+      <c r="K7" s="289"/>
+      <c r="L7" s="289"/>
+      <c r="M7" s="289"/>
+      <c r="N7" s="289"/>
+      <c r="O7" s="289"/>
+      <c r="P7" s="289"/>
+      <c r="Q7" s="289"/>
+      <c r="R7" s="289"/>
+      <c r="S7" s="289"/>
+      <c r="T7" s="289"/>
+      <c r="U7" s="290"/>
       <c r="W7" s="88" t="s">
         <v>30</v>
       </c>
       <c r="X7" s="232">
-        <f>AVERAGE(X13,X18,X23,X28)</f>
+        <f>AVERAGE(X14,X19,X24,X29)</f>
         <v>0.96322129776655552</v>
       </c>
       <c r="Y7" s="233">
@@ -27273,9 +27596,9 @@
         <v>1.6666666666666666E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="218" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
@@ -27294,12 +27617,13 @@
       <c r="Q8" s="109"/>
       <c r="R8" s="109"/>
       <c r="S8" s="109"/>
-      <c r="T8" s="110"/>
+      <c r="T8" s="109"/>
+      <c r="U8" s="110"/>
       <c r="W8" s="88" t="s">
         <v>31</v>
       </c>
       <c r="X8" s="232">
-        <f>AVERAGE(X14,X19,X24,X29)</f>
+        <f>AVERAGE(X15,X20,X25,X30)</f>
         <v>3.5361260841509909</v>
       </c>
       <c r="Y8" s="233">
@@ -27322,1255 +27646,1286 @@
         <v>2.3809523809523808E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="M9" s="256" t="s">
-        <v>94</v>
-      </c>
-      <c r="N9" s="256"/>
-      <c r="O9" s="256"/>
-      <c r="P9" s="256"/>
-      <c r="R9" s="275" t="s">
-        <v>95</v>
-      </c>
-      <c r="S9" s="275"/>
-      <c r="T9" s="275"/>
-      <c r="U9" s="275"/>
-      <c r="X9" s="219" t="s">
-        <v>96</v>
-      </c>
-      <c r="Y9" s="219" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z9" t="s">
-        <v>97</v>
-      </c>
+    <row r="9" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="291"/>
+      <c r="C9" s="292"/>
+      <c r="D9" s="292"/>
+      <c r="E9" s="292"/>
+      <c r="F9" s="292"/>
+      <c r="G9" s="292"/>
+      <c r="H9" s="292"/>
+      <c r="I9" s="292"/>
+      <c r="J9" s="292"/>
+      <c r="K9" s="292"/>
+      <c r="L9" s="292"/>
+      <c r="M9" s="292"/>
+      <c r="N9" s="292"/>
+      <c r="O9" s="292"/>
+      <c r="P9" s="292"/>
+      <c r="Q9" s="292"/>
+      <c r="R9" s="292"/>
+      <c r="S9" s="292"/>
+      <c r="T9" s="292"/>
+      <c r="U9" s="292"/>
+      <c r="V9" s="293"/>
+      <c r="W9" s="292"/>
+      <c r="X9" s="295" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y9" s="295" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z9" s="216" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA9" s="293"/>
+      <c r="AB9" s="293"/>
+      <c r="AC9" s="293"/>
+      <c r="AD9" s="293"/>
+      <c r="AE9" s="294"/>
+      <c r="AF9" s="294"/>
+      <c r="AG9" s="294"/>
+      <c r="AH9" s="294"/>
     </row>
-    <row r="10" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J10" s="273" t="s">
+    <row r="10" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M10" s="286" t="s">
+        <v>90</v>
+      </c>
+      <c r="N10" s="286"/>
+      <c r="O10" s="286"/>
+      <c r="P10" s="286"/>
+      <c r="R10" s="278" t="s">
+        <v>91</v>
+      </c>
+      <c r="S10" s="278"/>
+      <c r="T10" s="278"/>
+      <c r="U10" s="278"/>
+    </row>
+    <row r="11" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J11" s="276" t="s">
         <v>82</v>
       </c>
-      <c r="K10" s="273"/>
-      <c r="L10" s="273"/>
-      <c r="M10" s="259"/>
-      <c r="N10" s="259"/>
-      <c r="O10" s="259"/>
-      <c r="P10" s="259"/>
-      <c r="R10" s="259"/>
-      <c r="S10" s="259"/>
-      <c r="T10" s="259"/>
-      <c r="U10" s="259"/>
-      <c r="X10" s="219"/>
-      <c r="Y10" s="219"/>
-      <c r="Z10" s="274" t="s">
+      <c r="K11" s="276"/>
+      <c r="L11" s="276"/>
+      <c r="M11" s="262"/>
+      <c r="N11" s="262"/>
+      <c r="O11" s="262"/>
+      <c r="P11" s="262"/>
+      <c r="R11" s="262"/>
+      <c r="S11" s="262"/>
+      <c r="T11" s="262"/>
+      <c r="U11" s="262"/>
+      <c r="X11" s="219"/>
+      <c r="Y11" s="219"/>
+      <c r="AJ11" s="277" t="s">
         <v>81</v>
       </c>
-      <c r="AA10" s="274"/>
-      <c r="AB10" s="274"/>
-      <c r="AC10" s="274"/>
+      <c r="AK11" s="277"/>
+      <c r="AL11" s="277"/>
+      <c r="AM11" s="277"/>
     </row>
-    <row r="11" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J11" s="82">
-        <v>0</v>
-      </c>
-      <c r="K11" s="223" t="s">
-        <v>89</v>
-      </c>
-      <c r="L11" s="82">
-        <f>J11+180</f>
+    <row r="12" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J12" s="82">
+        <v>0</v>
+      </c>
+      <c r="K12" s="223" t="s">
+        <v>85</v>
+      </c>
+      <c r="L12" s="82">
+        <f>J12+180</f>
         <v>180</v>
       </c>
-      <c r="M11" s="86">
+      <c r="M12" s="86">
         <v>16</v>
       </c>
-      <c r="N11" s="86">
+      <c r="N12" s="86">
         <v>14</v>
       </c>
-      <c r="O11" s="86">
+      <c r="O12" s="86">
         <v>5</v>
       </c>
-      <c r="P11" s="86">
+      <c r="P12" s="86">
         <v>4</v>
       </c>
-      <c r="Q11">
-        <v>1</v>
-      </c>
-      <c r="R11" s="224">
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12" s="224">
         <v>0.14285714285714285</v>
       </c>
-      <c r="S11" s="224">
+      <c r="S12" s="224">
         <v>0.125</v>
       </c>
-      <c r="T11" s="224">
+      <c r="T12" s="224">
         <v>4.4642857142857144E-2</v>
       </c>
-      <c r="U11" s="224">
+      <c r="U12" s="224">
         <v>3.5714285714285712E-2</v>
       </c>
-      <c r="W11" s="74" t="s">
+      <c r="W12" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="X11" s="225">
-        <f>MAX(R11:U14)</f>
+      <c r="X12" s="225">
+        <f>MAX(R12:U15)</f>
         <v>0.19642857142857142</v>
       </c>
-      <c r="Y11" s="219"/>
-      <c r="Z11" s="224">
-        <f t="shared" ref="Z11:AC14" si="0">IF(R11=0,0,R11*LOG(R11,2))</f>
+      <c r="Y12" s="219"/>
+      <c r="AJ12" s="224">
+        <f>IF(R12=0,0,R12*LOG(R12,2))</f>
         <v>-0.40105070315108637</v>
       </c>
-      <c r="AA11" s="224">
-        <f t="shared" si="0"/>
+      <c r="AK12" s="224">
+        <f>IF(S12=0,0,S12*LOG(S12,2))</f>
         <v>-0.375</v>
       </c>
-      <c r="AB11" s="224">
-        <f t="shared" si="0"/>
+      <c r="AL12" s="224">
+        <f>IF(T12=0,0,T12*LOG(T12,2))</f>
         <v>-0.20024226907010009</v>
       </c>
-      <c r="AC11" s="224">
-        <f t="shared" si="0"/>
+      <c r="AM12" s="224">
+        <f>IF(U12=0,0,U12*LOG(U12,2))</f>
         <v>-0.17169124721634299</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K12" s="216"/>
-      <c r="M12" s="86">
-        <v>14</v>
-      </c>
-      <c r="N12" s="86">
-        <v>22</v>
-      </c>
-      <c r="O12" s="86">
-        <v>3</v>
-      </c>
-      <c r="P12" s="86">
-        <v>6</v>
-      </c>
-      <c r="Q12">
-        <v>2</v>
-      </c>
-      <c r="R12" s="224">
-        <v>0.125</v>
-      </c>
-      <c r="S12" s="224">
-        <v>0.19642857142857142</v>
-      </c>
-      <c r="T12" s="224">
-        <v>2.6785714285714284E-2</v>
-      </c>
-      <c r="U12" s="224">
-        <v>5.3571428571428568E-2</v>
-      </c>
-      <c r="W12" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="X12" s="225">
-        <f>Q11*SUM(R11:U11)+Q12*SUM(R12:U12)+Q13*SUM(R13:U13)+Q14*SUM(R14:U14)</f>
-        <v>2.026785714285714</v>
-      </c>
-      <c r="Y12" s="219"/>
-      <c r="Z12" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.375</v>
-      </c>
-      <c r="AA12" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.46119922031470312</v>
-      </c>
-      <c r="AB12" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.13988551128579771</v>
-      </c>
-      <c r="AC12" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.22619959400016687</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K13" s="216"/>
       <c r="M13" s="86">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="N13" s="86">
+        <v>22</v>
+      </c>
+      <c r="O13" s="86">
         <v>3</v>
       </c>
-      <c r="O13" s="86">
-        <v>4</v>
-      </c>
       <c r="P13" s="86">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" s="224">
-        <v>4.4642857142857144E-2</v>
+        <v>0.125</v>
       </c>
       <c r="S13" s="224">
+        <v>0.19642857142857142</v>
+      </c>
+      <c r="T13" s="224">
         <v>2.6785714285714284E-2</v>
       </c>
-      <c r="T13" s="224">
-        <v>3.5714285714285712E-2</v>
-      </c>
       <c r="U13" s="224">
-        <v>1.7857142857142856E-2</v>
+        <v>5.3571428571428568E-2</v>
       </c>
       <c r="W13" s="74" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="X13" s="225">
-        <f>(Q11-X12)^2*SUM(R11:U11)+(Q12-X12)^2*SUM(R12:U12)+(Q13-X12)^2*SUM(R13:U13)+(Q14-X12)^2*SUM(R14:U14)</f>
-        <v>0.97249681122448961</v>
+        <f>Q12*SUM(R12:U12)+Q13*SUM(R13:U13)+Q14*SUM(R14:U14)+Q15*SUM(R15:U15)</f>
+        <v>2.026785714285714</v>
       </c>
       <c r="Y13" s="219"/>
-      <c r="Z13" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.20024226907010009</v>
-      </c>
-      <c r="AA13" s="224">
-        <f t="shared" si="0"/>
+      <c r="AJ13" s="224">
+        <f>IF(R13=0,0,R13*LOG(R13,2))</f>
+        <v>-0.375</v>
+      </c>
+      <c r="AK13" s="224">
+        <f>IF(S13=0,0,S13*LOG(S13,2))</f>
+        <v>-0.46119922031470312</v>
+      </c>
+      <c r="AL13" s="224">
+        <f>IF(T13=0,0,T13*LOG(T13,2))</f>
         <v>-0.13988551128579771</v>
       </c>
-      <c r="AB13" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.17169124721634299</v>
-      </c>
-      <c r="AC13" s="224">
-        <f t="shared" si="0"/>
-        <v>-0.10370276646531436</v>
+      <c r="AM13" s="224">
+        <f>IF(U13=0,0,U13*LOG(U13,2))</f>
+        <v>-0.22619959400016687</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="K14" s="216"/>
       <c r="M14" s="86">
+        <v>5</v>
+      </c>
+      <c r="N14" s="86">
+        <v>3</v>
+      </c>
+      <c r="O14" s="86">
         <v>4</v>
       </c>
-      <c r="N14" s="86">
-        <v>6</v>
-      </c>
-      <c r="O14" s="86">
-        <v>2</v>
-      </c>
       <c r="P14" s="86">
         <v>2</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R14" s="224">
+        <v>4.4642857142857144E-2</v>
+      </c>
+      <c r="S14" s="224">
+        <v>2.6785714285714284E-2</v>
+      </c>
+      <c r="T14" s="224">
         <v>3.5714285714285712E-2</v>
-      </c>
-      <c r="S14" s="224">
-        <v>5.3571428571428568E-2</v>
-      </c>
-      <c r="T14" s="224">
-        <v>1.7857142857142856E-2</v>
       </c>
       <c r="U14" s="224">
         <v>1.7857142857142856E-2</v>
       </c>
       <c r="W14" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="X14" s="225">
+        <f>(Q12-X13)^2*SUM(R12:U12)+(Q13-X13)^2*SUM(R13:U13)+(Q14-X13)^2*SUM(R14:U14)+(Q15-X13)^2*SUM(R15:U15)</f>
+        <v>0.97249681122448961</v>
+      </c>
+      <c r="Y14" s="219"/>
+      <c r="AJ14" s="224">
+        <f>IF(R14=0,0,R14*LOG(R14,2))</f>
+        <v>-0.20024226907010009</v>
+      </c>
+      <c r="AK14" s="224">
+        <f>IF(S14=0,0,S14*LOG(S14,2))</f>
+        <v>-0.13988551128579771</v>
+      </c>
+      <c r="AL14" s="224">
+        <f>IF(T14=0,0,T14*LOG(T14,2))</f>
+        <v>-0.17169124721634299</v>
+      </c>
+      <c r="AM14" s="224">
+        <f>IF(U14=0,0,U14*LOG(U14,2))</f>
+        <v>-0.10370276646531436</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K15" s="216"/>
+      <c r="M15" s="86">
+        <v>4</v>
+      </c>
+      <c r="N15" s="86">
+        <v>6</v>
+      </c>
+      <c r="O15" s="86">
+        <v>2</v>
+      </c>
+      <c r="P15" s="86">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>4</v>
+      </c>
+      <c r="R15" s="224">
+        <v>3.5714285714285712E-2</v>
+      </c>
+      <c r="S15" s="224">
+        <v>5.3571428571428568E-2</v>
+      </c>
+      <c r="T15" s="224">
+        <v>1.7857142857142856E-2</v>
+      </c>
+      <c r="U15" s="224">
+        <v>1.7857142857142856E-2</v>
+      </c>
+      <c r="W15" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="X14" s="225">
-        <f>-SUM(Z11:AC14)</f>
+      <c r="X15" s="225">
+        <f>-SUM(AJ12:AM15)</f>
         <v>3.5710867132228916</v>
       </c>
-      <c r="Y14" s="219"/>
-      <c r="Z14" s="224">
-        <f t="shared" si="0"/>
+      <c r="Y15" s="219"/>
+      <c r="AJ15" s="224">
+        <f>IF(R15=0,0,R15*LOG(R15,2))</f>
         <v>-0.17169124721634299</v>
       </c>
-      <c r="AA14" s="224">
-        <f t="shared" si="0"/>
+      <c r="AK15" s="224">
+        <f>IF(S15=0,0,S15*LOG(S15,2))</f>
         <v>-0.22619959400016687</v>
       </c>
-      <c r="AB14" s="224">
-        <f t="shared" si="0"/>
+      <c r="AL15" s="224">
+        <f>IF(T15=0,0,T15*LOG(T15,2))</f>
         <v>-0.10370276646531436</v>
       </c>
-      <c r="AC14" s="224">
-        <f t="shared" si="0"/>
+      <c r="AM15" s="224">
+        <f>IF(U15=0,0,U15*LOG(U15,2))</f>
         <v>-0.10370276646531436</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K15" s="216"/>
-      <c r="R15" s="220"/>
-      <c r="S15" s="220"/>
-      <c r="T15" s="220"/>
-      <c r="U15" s="220"/>
-      <c r="X15" s="219"/>
-      <c r="Y15" s="219"/>
-      <c r="Z15" s="220"/>
-      <c r="AA15" s="220"/>
-      <c r="AB15" s="220"/>
-      <c r="AC15" s="220"/>
+    <row r="16" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K16" s="216"/>
+      <c r="R16" s="220"/>
+      <c r="S16" s="220"/>
+      <c r="T16" s="220"/>
+      <c r="U16" s="220"/>
+      <c r="X16" s="219"/>
+      <c r="Y16" s="219"/>
+      <c r="AJ16" s="220"/>
+      <c r="AK16" s="220"/>
+      <c r="AL16" s="220"/>
+      <c r="AM16" s="220"/>
     </row>
-    <row r="16" spans="1:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="J16" s="20">
+    <row r="17" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" s="20">
         <v>45</v>
       </c>
-      <c r="K16" s="226" t="s">
-        <v>89</v>
-      </c>
-      <c r="L16" s="20">
-        <f>J16+180</f>
+      <c r="K17" s="226" t="s">
+        <v>85</v>
+      </c>
+      <c r="L17" s="20">
+        <f>J17+180</f>
         <v>225</v>
       </c>
-      <c r="M16" s="95">
+      <c r="M17" s="95">
         <v>6</v>
       </c>
-      <c r="N16" s="95">
+      <c r="N17" s="95">
         <v>16</v>
       </c>
-      <c r="O16" s="95">
+      <c r="O17" s="95">
         <v>6</v>
       </c>
-      <c r="P16" s="95">
+      <c r="P17" s="95">
         <v>5</v>
       </c>
-      <c r="Q16">
-        <v>1</v>
-      </c>
-      <c r="R16" s="227">
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17" s="227">
         <v>6.1224489795918366E-2</v>
       </c>
-      <c r="S16" s="227">
+      <c r="S17" s="227">
         <v>0.16326530612244897</v>
       </c>
-      <c r="T16" s="227">
+      <c r="T17" s="227">
         <v>6.1224489795918366E-2</v>
       </c>
-      <c r="U16" s="227">
+      <c r="U17" s="227">
         <v>5.1020408163265307E-2</v>
       </c>
-      <c r="W16" s="74" t="s">
+      <c r="W17" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="X16" s="221">
-        <f>MAX(R16:U19)</f>
+      <c r="X17" s="221">
+        <f>MAX(R17:U20)</f>
         <v>0.16326530612244897</v>
       </c>
-      <c r="Y16" s="219"/>
-      <c r="Z16" s="227">
-        <f t="shared" ref="Z16:AC19" si="1">IF(R16=0,0,R16*LOG(R16,2))</f>
+      <c r="Y17" s="219"/>
+      <c r="AJ17" s="227">
+        <f>IF(R17=0,0,R17*LOG(R17,2))</f>
         <v>-0.24671922510575831</v>
       </c>
-      <c r="AA16" s="227">
-        <f t="shared" si="1"/>
+      <c r="AK17" s="227">
+        <f>IF(S17=0,0,S17*LOG(S17,2))</f>
         <v>-0.42689140312085033</v>
       </c>
-      <c r="AB16" s="227">
-        <f t="shared" si="1"/>
+      <c r="AL17" s="227">
+        <f>IF(T17=0,0,T17*LOG(T17,2))</f>
         <v>-0.24671922510575831</v>
       </c>
-      <c r="AC16" s="227">
-        <f t="shared" si="1"/>
+      <c r="AM17" s="227">
+        <f>IF(U17=0,0,U17*LOG(U17,2))</f>
         <v>-0.21901947700142071</v>
       </c>
     </row>
-    <row r="17" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="1">
-        <v>1</v>
-      </c>
-      <c r="C17" s="1">
-        <v>2</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>2</v>
-      </c>
-      <c r="H17" s="1">
-        <v>2</v>
-      </c>
-      <c r="I17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="216"/>
-      <c r="M17" s="95">
-        <v>16</v>
-      </c>
-      <c r="N17" s="95">
-        <v>12</v>
-      </c>
-      <c r="O17" s="95">
-        <v>7</v>
-      </c>
-      <c r="P17" s="95">
-        <v>4</v>
-      </c>
-      <c r="Q17">
-        <v>2</v>
-      </c>
-      <c r="R17" s="227">
-        <v>0.16326530612244897</v>
-      </c>
-      <c r="S17" s="227">
-        <v>0.12244897959183673</v>
-      </c>
-      <c r="T17" s="227">
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="U17" s="227">
-        <v>4.0816326530612242E-2</v>
-      </c>
-      <c r="W17" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="X17" s="221">
-        <f>Q16*SUM(R16:U16)+Q17*SUM(R17:U17)+Q18*SUM(R18:U18)+Q19*SUM(R19:U19)</f>
-        <v>2.0510204081632653</v>
-      </c>
-      <c r="Y17" s="219"/>
-      <c r="Z17" s="227">
-        <f t="shared" si="1"/>
-        <v>-0.42689140312085033</v>
-      </c>
-      <c r="AA17" s="227">
-        <f t="shared" si="1"/>
-        <v>-0.3709894706196798</v>
-      </c>
-      <c r="AB17" s="227">
-        <f t="shared" si="1"/>
-        <v>-0.27195392300411458</v>
-      </c>
-      <c r="AC17" s="227">
-        <f t="shared" si="1"/>
-        <v>-0.18835550384143707</v>
-      </c>
-    </row>
-    <row r="18" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="1">
-        <v>1</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1">
-        <v>3</v>
-      </c>
-      <c r="G18" s="1">
-        <v>1</v>
-      </c>
-      <c r="H18" s="1">
-        <v>2</v>
-      </c>
-      <c r="I18" s="1">
-        <v>2</v>
+    <row r="18" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="240">
+        <v>1</v>
+      </c>
+      <c r="C18" s="240">
+        <v>2</v>
+      </c>
+      <c r="D18" s="240">
+        <v>2</v>
+      </c>
+      <c r="E18" s="240">
+        <v>2</v>
+      </c>
+      <c r="F18" s="240">
+        <v>1</v>
+      </c>
+      <c r="G18" s="240">
+        <v>2</v>
+      </c>
+      <c r="H18" s="240">
+        <v>2</v>
+      </c>
+      <c r="I18" s="240">
+        <v>1</v>
       </c>
       <c r="K18" s="216"/>
       <c r="M18" s="95">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="N18" s="95">
+        <v>12</v>
+      </c>
+      <c r="O18" s="95">
         <v>7</v>
       </c>
-      <c r="O18" s="95">
-        <v>0</v>
-      </c>
       <c r="P18" s="95">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q18">
+        <v>2</v>
+      </c>
+      <c r="R18" s="227">
+        <v>0.16326530612244897</v>
+      </c>
+      <c r="S18" s="227">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="T18" s="227">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="U18" s="227">
+        <v>4.0816326530612242E-2</v>
+      </c>
+      <c r="W18" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="X18" s="221">
+        <f>Q17*SUM(R17:U17)+Q18*SUM(R18:U18)+Q19*SUM(R19:U19)+Q20*SUM(R20:U20)</f>
+        <v>2.0510204081632653</v>
+      </c>
+      <c r="Y18" s="219"/>
+      <c r="AJ18" s="227">
+        <f>IF(R18=0,0,R18*LOG(R18,2))</f>
+        <v>-0.42689140312085033</v>
+      </c>
+      <c r="AK18" s="227">
+        <f>IF(S18=0,0,S18*LOG(S18,2))</f>
+        <v>-0.3709894706196798</v>
+      </c>
+      <c r="AL18" s="227">
+        <f>IF(T18=0,0,T18*LOG(T18,2))</f>
+        <v>-0.27195392300411458</v>
+      </c>
+      <c r="AM18" s="227">
+        <f>IF(U18=0,0,U18*LOG(U18,2))</f>
+        <v>-0.18835550384143707</v>
+      </c>
+    </row>
+    <row r="19" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="240">
+        <v>1</v>
+      </c>
+      <c r="C19" s="240">
+        <v>1</v>
+      </c>
+      <c r="D19" s="240">
         <v>3</v>
       </c>
-      <c r="R18" s="227">
-        <v>6.1224489795918366E-2</v>
-      </c>
-      <c r="S18" s="227">
-        <v>7.1428571428571425E-2</v>
-      </c>
-      <c r="T18" s="227">
-        <v>0</v>
-      </c>
-      <c r="U18" s="227">
-        <v>1.020408163265306E-2</v>
-      </c>
-      <c r="W18" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="X18" s="221">
-        <f>(Q16-X17)^2*SUM(R16:U16)+(Q17-X17)^2*SUM(R17:U17)+(Q18-X17)^2*SUM(R18:U18)+(Q19-X17)^2*SUM(R19:U19)</f>
-        <v>0.96678467305289462</v>
-      </c>
-      <c r="Y18" s="219"/>
-      <c r="Z18" s="227">
-        <f t="shared" si="1"/>
-        <v>-0.24671922510575831</v>
-      </c>
-      <c r="AA18" s="227">
-        <f t="shared" si="1"/>
-        <v>-0.27195392300411458</v>
-      </c>
-      <c r="AB18" s="227">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="AC18" s="227">
-        <f t="shared" si="1"/>
-        <v>-6.7497039225665398E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="1">
-        <v>2</v>
-      </c>
-      <c r="C19" s="1">
-        <v>2</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="E19" s="240">
         <v>4</v>
       </c>
-      <c r="E19" s="1">
-        <v>2</v>
-      </c>
-      <c r="F19" s="1">
-        <v>2</v>
-      </c>
-      <c r="G19" s="1">
-        <v>4</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1</v>
-      </c>
-      <c r="I19" s="1">
-        <v>1</v>
+      <c r="F19" s="240">
+        <v>3</v>
+      </c>
+      <c r="G19" s="240">
+        <v>1</v>
+      </c>
+      <c r="H19" s="240">
+        <v>2</v>
+      </c>
+      <c r="I19" s="240">
+        <v>2</v>
       </c>
       <c r="K19" s="216"/>
       <c r="M19" s="95">
+        <v>6</v>
+      </c>
+      <c r="N19" s="95">
+        <v>7</v>
+      </c>
+      <c r="O19" s="95">
+        <v>0</v>
+      </c>
+      <c r="P19" s="95">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>3</v>
+      </c>
+      <c r="R19" s="227">
+        <v>6.1224489795918366E-2</v>
+      </c>
+      <c r="S19" s="227">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="T19" s="227">
+        <v>0</v>
+      </c>
+      <c r="U19" s="227">
+        <v>1.020408163265306E-2</v>
+      </c>
+      <c r="W19" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="X19" s="221">
+        <f>(Q17-X18)^2*SUM(R17:U17)+(Q18-X18)^2*SUM(R18:U18)+(Q19-X18)^2*SUM(R19:U19)+(Q20-X18)^2*SUM(R20:U20)</f>
+        <v>0.96678467305289462</v>
+      </c>
+      <c r="Y19" s="219"/>
+      <c r="AJ19" s="227">
+        <f>IF(R19=0,0,R19*LOG(R19,2))</f>
+        <v>-0.24671922510575831</v>
+      </c>
+      <c r="AK19" s="227">
+        <f>IF(S19=0,0,S19*LOG(S19,2))</f>
+        <v>-0.27195392300411458</v>
+      </c>
+      <c r="AL19" s="227">
+        <f>IF(T19=0,0,T19*LOG(T19,2))</f>
+        <v>0</v>
+      </c>
+      <c r="AM19" s="227">
+        <f>IF(U19=0,0,U19*LOG(U19,2))</f>
+        <v>-6.7497039225665398E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="240">
+        <v>2</v>
+      </c>
+      <c r="C20" s="240">
+        <v>2</v>
+      </c>
+      <c r="D20" s="240">
+        <v>4</v>
+      </c>
+      <c r="E20" s="240">
+        <v>2</v>
+      </c>
+      <c r="F20" s="240">
+        <v>2</v>
+      </c>
+      <c r="G20" s="240">
+        <v>4</v>
+      </c>
+      <c r="H20" s="240">
+        <v>1</v>
+      </c>
+      <c r="I20" s="240">
+        <v>1</v>
+      </c>
+      <c r="K20" s="216"/>
+      <c r="M20" s="95">
         <v>5</v>
       </c>
-      <c r="N19" s="95">
+      <c r="N20" s="95">
         <v>4</v>
       </c>
-      <c r="O19" s="95">
-        <v>1</v>
-      </c>
-      <c r="P19" s="95">
-        <v>2</v>
-      </c>
-      <c r="Q19">
+      <c r="O20" s="95">
+        <v>1</v>
+      </c>
+      <c r="P20" s="95">
+        <v>2</v>
+      </c>
+      <c r="Q20">
         <v>4</v>
       </c>
-      <c r="R19" s="227">
+      <c r="R20" s="227">
         <v>5.1020408163265307E-2</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S20" s="227">
         <v>4.0816326530612242E-2</v>
       </c>
-      <c r="T19" s="227">
+      <c r="T20" s="227">
         <v>1.020408163265306E-2</v>
       </c>
-      <c r="U19" s="227">
+      <c r="U20" s="227">
         <v>2.0408163265306121E-2</v>
       </c>
-      <c r="W19" s="74" t="s">
+      <c r="W20" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="X19" s="221">
-        <f>-SUM(Z16:AC19)</f>
+      <c r="X20" s="221">
+        <f>-SUM(AJ17:AM20)</f>
         <v>3.573167753509956</v>
       </c>
-      <c r="Y19" s="219"/>
-      <c r="Z19" s="227">
-        <f t="shared" si="1"/>
+      <c r="Y20" s="219"/>
+      <c r="AJ20" s="227">
+        <f>IF(R20=0,0,R20*LOG(R20,2))</f>
         <v>-0.21901947700142071</v>
       </c>
-      <c r="AA19" s="227">
-        <f t="shared" si="1"/>
+      <c r="AK20" s="227">
+        <f>IF(S20=0,0,S20*LOG(S20,2))</f>
         <v>-0.18835550384143707</v>
       </c>
-      <c r="AB19" s="227">
-        <f t="shared" si="1"/>
+      <c r="AL20" s="227">
+        <f>IF(T20=0,0,T20*LOG(T20,2))</f>
         <v>-6.7497039225665398E-2</v>
       </c>
-      <c r="AC19" s="227">
-        <f t="shared" si="1"/>
+      <c r="AM20" s="227">
+        <f>IF(U20=0,0,U20*LOG(U20,2))</f>
         <v>-0.11458591518602466</v>
       </c>
     </row>
-    <row r="20" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="1">
-        <v>1</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-      <c r="D20" s="1">
-        <v>2</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1">
-        <v>2</v>
-      </c>
-      <c r="H20" s="1">
+    <row r="21" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="240">
+        <v>1</v>
+      </c>
+      <c r="C21" s="240">
+        <v>1</v>
+      </c>
+      <c r="D21" s="240">
+        <v>2</v>
+      </c>
+      <c r="E21" s="240">
+        <v>1</v>
+      </c>
+      <c r="F21" s="240">
+        <v>1</v>
+      </c>
+      <c r="G21" s="240">
+        <v>2</v>
+      </c>
+      <c r="H21" s="240">
         <v>3</v>
       </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="216"/>
-      <c r="R20" s="220"/>
-      <c r="S20" s="220"/>
-      <c r="T20" s="220"/>
-      <c r="U20" s="220"/>
-      <c r="X20" s="219"/>
-      <c r="Y20" s="219"/>
-      <c r="Z20" s="220"/>
-      <c r="AA20" s="220"/>
-      <c r="AB20" s="220"/>
-      <c r="AC20" s="220"/>
-      <c r="AE20" t="s">
+      <c r="I21" s="240">
+        <v>1</v>
+      </c>
+      <c r="K21" s="216"/>
+      <c r="R21" s="220"/>
+      <c r="S21" s="220"/>
+      <c r="T21" s="220"/>
+      <c r="U21" s="220"/>
+      <c r="X21" s="219"/>
+      <c r="Y21" s="219"/>
+      <c r="AE21" t="s">
         <v>68</v>
       </c>
+      <c r="AJ21" s="220"/>
+      <c r="AK21" s="220"/>
+      <c r="AL21" s="220"/>
+      <c r="AM21" s="220"/>
     </row>
-    <row r="21" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="1">
-        <v>1</v>
-      </c>
-      <c r="C21" s="1">
+    <row r="22" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="240">
+        <v>1</v>
+      </c>
+      <c r="C22" s="240">
         <v>3</v>
       </c>
-      <c r="D21" s="1">
-        <v>2</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1">
-        <v>2</v>
-      </c>
-      <c r="H21" s="1">
-        <v>2</v>
-      </c>
-      <c r="I21" s="1">
-        <v>1</v>
-      </c>
-      <c r="J21" s="19">
+      <c r="D22" s="240">
+        <v>2</v>
+      </c>
+      <c r="E22" s="240">
+        <v>2</v>
+      </c>
+      <c r="F22" s="240">
+        <v>1</v>
+      </c>
+      <c r="G22" s="240">
+        <v>2</v>
+      </c>
+      <c r="H22" s="240">
+        <v>2</v>
+      </c>
+      <c r="I22" s="240">
+        <v>1</v>
+      </c>
+      <c r="J22" s="19">
         <v>90</v>
       </c>
-      <c r="K21" s="235" t="s">
-        <v>89</v>
-      </c>
-      <c r="L21" s="19">
-        <f>J21+180</f>
+      <c r="K22" s="235" t="s">
+        <v>85</v>
+      </c>
+      <c r="L22" s="19">
+        <f>J22+180</f>
         <v>270</v>
       </c>
-      <c r="M21" s="89">
+      <c r="M22" s="89">
         <v>14</v>
       </c>
-      <c r="N21" s="89">
+      <c r="N22" s="89">
         <v>18</v>
       </c>
-      <c r="O21" s="89">
+      <c r="O22" s="89">
         <v>9</v>
       </c>
-      <c r="P21" s="89">
-        <v>2</v>
-      </c>
-      <c r="Q21">
-        <v>1</v>
-      </c>
-      <c r="R21" s="236">
+      <c r="P22" s="89">
+        <v>2</v>
+      </c>
+      <c r="Q22">
+        <v>1</v>
+      </c>
+      <c r="R22" s="236">
         <v>0.125</v>
       </c>
-      <c r="S21" s="236">
+      <c r="S22" s="236">
         <v>0.16071428571428573</v>
       </c>
-      <c r="T21" s="236">
+      <c r="T22" s="236">
         <v>8.0357142857142863E-2</v>
       </c>
-      <c r="U21" s="236">
+      <c r="U22" s="236">
         <v>1.7857142857142856E-2</v>
       </c>
-      <c r="W21" s="74" t="s">
+      <c r="W22" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="X21" s="237">
-        <f>MAX(R21:U24)</f>
+      <c r="X22" s="237">
+        <f>MAX(R22:U25)</f>
         <v>0.16071428571428573</v>
       </c>
-      <c r="Y21" s="219"/>
-      <c r="Z21" s="236">
-        <f t="shared" ref="Z21:AC24" si="2">IF(R21=0,0,R21*LOG(R21,2))</f>
+      <c r="Y22" s="219"/>
+      <c r="AE22" s="239">
+        <v>50</v>
+      </c>
+      <c r="AF22" s="239">
+        <v>60</v>
+      </c>
+      <c r="AG22" s="239">
+        <v>26</v>
+      </c>
+      <c r="AH22" s="239">
+        <v>13</v>
+      </c>
+      <c r="AJ22" s="236">
+        <f>IF(R22=0,0,R22*LOG(R22,2))</f>
         <v>-0.375</v>
       </c>
-      <c r="AA21" s="236">
-        <f t="shared" si="2"/>
+      <c r="AK22" s="236">
+        <f>IF(S22=0,0,S22*LOG(S22,2))</f>
         <v>-0.42387266581317196</v>
       </c>
-      <c r="AB21" s="236">
-        <f t="shared" si="2"/>
+      <c r="AL22" s="236">
+        <f>IF(T22=0,0,T22*LOG(T22,2))</f>
         <v>-0.29229347576372883</v>
       </c>
-      <c r="AC21" s="236">
-        <f t="shared" si="2"/>
+      <c r="AM22" s="236">
+        <f>IF(U22=0,0,U22*LOG(U22,2))</f>
         <v>-0.10370276646531436</v>
       </c>
-      <c r="AE21" s="239">
-        <v>50</v>
-      </c>
-      <c r="AF21" s="239">
-        <v>60</v>
-      </c>
-      <c r="AG21" s="239">
-        <v>26</v>
-      </c>
-      <c r="AH21" s="239">
-        <v>13</v>
-      </c>
     </row>
-    <row r="22" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="1">
-        <v>1</v>
-      </c>
-      <c r="C22" s="1">
-        <v>2</v>
-      </c>
-      <c r="D22" s="1">
+    <row r="23" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="240">
+        <v>1</v>
+      </c>
+      <c r="C23" s="240">
+        <v>2</v>
+      </c>
+      <c r="D23" s="240">
         <v>4</v>
       </c>
-      <c r="E22" s="1">
-        <v>2</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2</v>
-      </c>
-      <c r="G22" s="1">
-        <v>1</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1</v>
-      </c>
-      <c r="K22" s="216"/>
-      <c r="M22" s="89">
-        <v>18</v>
-      </c>
-      <c r="N22" s="89">
-        <v>12</v>
-      </c>
-      <c r="O22" s="89">
-        <v>5</v>
-      </c>
-      <c r="P22" s="89">
-        <v>7</v>
-      </c>
-      <c r="Q22">
-        <v>2</v>
-      </c>
-      <c r="R22" s="236">
-        <v>0.16071428571428573</v>
-      </c>
-      <c r="S22" s="236">
-        <v>0.10714285714285714</v>
-      </c>
-      <c r="T22" s="236">
-        <v>4.4642857142857144E-2</v>
-      </c>
-      <c r="U22" s="236">
-        <v>6.25E-2</v>
-      </c>
-      <c r="W22" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="X22" s="237">
-        <f>Q21*SUM(R21:U21)+Q22*SUM(R22:U22)+Q23*SUM(R23:U23)+Q24*SUM(R24:U24)</f>
-        <v>1.964285714285714</v>
-      </c>
-      <c r="Y22" s="219"/>
-      <c r="Z22" s="236">
-        <f t="shared" si="2"/>
-        <v>-0.42387266581317196</v>
-      </c>
-      <c r="AA22" s="236">
-        <f t="shared" si="2"/>
-        <v>-0.34525633085747659</v>
-      </c>
-      <c r="AB22" s="236">
-        <f t="shared" si="2"/>
-        <v>-0.20024226907010009</v>
-      </c>
-      <c r="AC22" s="236">
-        <f t="shared" si="2"/>
-        <v>-0.25</v>
-      </c>
-      <c r="AE22" s="239">
-        <v>60</v>
-      </c>
-      <c r="AF22" s="239">
-        <v>66</v>
-      </c>
-      <c r="AG22" s="239">
-        <v>19</v>
-      </c>
-      <c r="AH22" s="239">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>2</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1">
-        <v>4</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>3</v>
-      </c>
-      <c r="H23" s="1">
-        <v>3</v>
-      </c>
-      <c r="I23" s="1">
-        <v>3</v>
+      <c r="E23" s="240">
+        <v>2</v>
+      </c>
+      <c r="F23" s="240">
+        <v>2</v>
+      </c>
+      <c r="G23" s="240">
+        <v>1</v>
+      </c>
+      <c r="H23" s="240">
+        <v>1</v>
+      </c>
+      <c r="I23" s="240">
+        <v>1</v>
       </c>
       <c r="K23" s="216"/>
       <c r="M23" s="89">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="N23" s="89">
+        <v>12</v>
+      </c>
+      <c r="O23" s="89">
         <v>5</v>
       </c>
-      <c r="O23" s="89">
-        <v>0</v>
-      </c>
       <c r="P23" s="89">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
+        <v>2</v>
+      </c>
+      <c r="R23" s="236">
+        <v>0.16071428571428573</v>
+      </c>
+      <c r="S23" s="236">
+        <v>0.10714285714285714</v>
+      </c>
+      <c r="T23" s="236">
+        <v>4.4642857142857144E-2</v>
+      </c>
+      <c r="U23" s="236">
+        <v>6.25E-2</v>
+      </c>
+      <c r="W23" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="X23" s="237">
+        <f>Q22*SUM(R22:U22)+Q23*SUM(R23:U23)+Q24*SUM(R24:U24)+Q25*SUM(R25:U25)</f>
+        <v>1.964285714285714</v>
+      </c>
+      <c r="Y23" s="219"/>
+      <c r="AE23" s="239">
+        <v>60</v>
+      </c>
+      <c r="AF23" s="239">
+        <v>66</v>
+      </c>
+      <c r="AG23" s="239">
+        <v>19</v>
+      </c>
+      <c r="AH23" s="239">
+        <v>20</v>
+      </c>
+      <c r="AJ23" s="236">
+        <f>IF(R23=0,0,R23*LOG(R23,2))</f>
+        <v>-0.42387266581317196</v>
+      </c>
+      <c r="AK23" s="236">
+        <f>IF(S23=0,0,S23*LOG(S23,2))</f>
+        <v>-0.34525633085747659</v>
+      </c>
+      <c r="AL23" s="236">
+        <f>IF(T23=0,0,T23*LOG(T23,2))</f>
+        <v>-0.20024226907010009</v>
+      </c>
+      <c r="AM23" s="236">
+        <f>IF(U23=0,0,U23*LOG(U23,2))</f>
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="240">
+        <v>2</v>
+      </c>
+      <c r="C24" s="240">
+        <v>2</v>
+      </c>
+      <c r="D24" s="240">
+        <v>2</v>
+      </c>
+      <c r="E24" s="240">
+        <v>4</v>
+      </c>
+      <c r="F24" s="240">
+        <v>1</v>
+      </c>
+      <c r="G24" s="240">
         <v>3</v>
       </c>
-      <c r="R23" s="236">
-        <v>8.0357142857142863E-2</v>
-      </c>
-      <c r="S23" s="236">
-        <v>4.4642857142857144E-2</v>
-      </c>
-      <c r="T23" s="236">
-        <v>0</v>
-      </c>
-      <c r="U23" s="236">
-        <v>8.9285714285714281E-3</v>
-      </c>
-      <c r="W23" s="74" t="s">
-        <v>30</v>
-      </c>
-      <c r="X23" s="237">
-        <f>(Q21-X22)^2*SUM(R21:U21)+(Q22-X22)^2*SUM(R22:U22)+(Q23-X22)^2*SUM(R23:U23)+(Q24-X22)^2*SUM(R24:U24)</f>
-        <v>0.94515306122448961</v>
-      </c>
-      <c r="Y23" s="219"/>
-      <c r="Z23" s="236">
-        <f t="shared" si="2"/>
-        <v>-0.29229347576372883</v>
-      </c>
-      <c r="AA23" s="236">
-        <f t="shared" si="2"/>
-        <v>-0.20024226907010009</v>
-      </c>
-      <c r="AB23" s="236">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="AC23" s="236">
-        <f t="shared" si="2"/>
-        <v>-6.0779954661228604E-2</v>
-      </c>
-      <c r="AE23" s="239">
-        <v>26</v>
-      </c>
-      <c r="AF23" s="239">
-        <v>19</v>
-      </c>
-      <c r="AG23" s="239">
-        <v>4</v>
-      </c>
-      <c r="AH23" s="239">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="1">
+      <c r="H24" s="240">
         <v>3</v>
       </c>
-      <c r="C24" s="1">
-        <v>2</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
-        <v>4</v>
-      </c>
-      <c r="F24" s="1">
-        <v>4</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
+      <c r="I24" s="240">
+        <v>3</v>
       </c>
       <c r="K24" s="216"/>
       <c r="M24" s="89">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="N24" s="89">
+        <v>5</v>
+      </c>
+      <c r="O24" s="89">
+        <v>0</v>
+      </c>
+      <c r="P24" s="89">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>3</v>
+      </c>
+      <c r="R24" s="236">
+        <v>8.0357142857142863E-2</v>
+      </c>
+      <c r="S24" s="236">
+        <v>4.4642857142857144E-2</v>
+      </c>
+      <c r="T24" s="236">
+        <v>0</v>
+      </c>
+      <c r="U24" s="236">
+        <v>8.9285714285714281E-3</v>
+      </c>
+      <c r="W24" s="74" t="s">
+        <v>30</v>
+      </c>
+      <c r="X24" s="237">
+        <f>(Q22-X23)^2*SUM(R22:U22)+(Q23-X23)^2*SUM(R23:U23)+(Q24-X23)^2*SUM(R24:U24)+(Q25-X23)^2*SUM(R25:U25)</f>
+        <v>0.94515306122448961</v>
+      </c>
+      <c r="Y24" s="219"/>
+      <c r="AE24" s="239">
+        <v>26</v>
+      </c>
+      <c r="AF24" s="239">
+        <v>19</v>
+      </c>
+      <c r="AG24" s="239">
+        <v>4</v>
+      </c>
+      <c r="AH24" s="239">
         <v>7</v>
       </c>
-      <c r="O24" s="89">
-        <v>1</v>
-      </c>
-      <c r="P24" s="89">
-        <v>2</v>
-      </c>
-      <c r="Q24">
+      <c r="AJ24" s="236">
+        <f>IF(R24=0,0,R24*LOG(R24,2))</f>
+        <v>-0.29229347576372883</v>
+      </c>
+      <c r="AK24" s="236">
+        <f>IF(S24=0,0,S24*LOG(S24,2))</f>
+        <v>-0.20024226907010009</v>
+      </c>
+      <c r="AL24" s="236">
+        <f>IF(T24=0,0,T24*LOG(T24,2))</f>
+        <v>0</v>
+      </c>
+      <c r="AM24" s="236">
+        <f>IF(U24=0,0,U24*LOG(U24,2))</f>
+        <v>-6.0779954661228604E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="240">
+        <v>3</v>
+      </c>
+      <c r="C25" s="240">
+        <v>2</v>
+      </c>
+      <c r="D25" s="240">
+        <v>1</v>
+      </c>
+      <c r="E25" s="240">
         <v>4</v>
       </c>
-      <c r="R24" s="236">
+      <c r="F25" s="240">
+        <v>4</v>
+      </c>
+      <c r="G25" s="240">
+        <v>1</v>
+      </c>
+      <c r="H25" s="240">
+        <v>1</v>
+      </c>
+      <c r="I25" s="240">
+        <v>1</v>
+      </c>
+      <c r="K25" s="216"/>
+      <c r="M25" s="89">
+        <v>2</v>
+      </c>
+      <c r="N25" s="89">
+        <v>7</v>
+      </c>
+      <c r="O25" s="89">
+        <v>1</v>
+      </c>
+      <c r="P25" s="89">
+        <v>2</v>
+      </c>
+      <c r="Q25">
+        <v>4</v>
+      </c>
+      <c r="R25" s="236">
         <v>1.7857142857142856E-2</v>
       </c>
-      <c r="S24" s="236">
+      <c r="S25" s="236">
         <v>6.25E-2</v>
       </c>
-      <c r="T24" s="236">
+      <c r="T25" s="236">
         <v>8.9285714285714281E-3</v>
       </c>
-      <c r="U24" s="236">
+      <c r="U25" s="236">
         <v>1.7857142857142856E-2</v>
       </c>
-      <c r="W24" s="74" t="s">
+      <c r="W25" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="X24" s="237">
-        <f>-SUM(Z21:AC24)</f>
+      <c r="X25" s="237">
+        <f>-SUM(AJ22:AM25)</f>
         <v>3.4857413608698784</v>
       </c>
-      <c r="Y24" s="219"/>
-      <c r="Z24" s="236">
-        <f t="shared" si="2"/>
+      <c r="Y25" s="219"/>
+      <c r="AE25" s="239">
+        <v>13</v>
+      </c>
+      <c r="AF25" s="239">
+        <v>20</v>
+      </c>
+      <c r="AG25" s="239">
+        <v>7</v>
+      </c>
+      <c r="AH25" s="239">
+        <v>10</v>
+      </c>
+      <c r="AJ25" s="236">
+        <f>IF(R25=0,0,R25*LOG(R25,2))</f>
         <v>-0.10370276646531436</v>
       </c>
-      <c r="AA24" s="236">
-        <f t="shared" si="2"/>
+      <c r="AK25" s="236">
+        <f>IF(S25=0,0,S25*LOG(S25,2))</f>
         <v>-0.25</v>
       </c>
-      <c r="AB24" s="236">
-        <f t="shared" si="2"/>
+      <c r="AL25" s="236">
+        <f>IF(T25=0,0,T25*LOG(T25,2))</f>
         <v>-6.0779954661228604E-2</v>
       </c>
-      <c r="AC24" s="236">
-        <f t="shared" si="2"/>
+      <c r="AM25" s="236">
+        <f>IF(U25=0,0,U25*LOG(U25,2))</f>
         <v>-0.10370276646531436</v>
       </c>
-      <c r="AE24" s="239">
-        <v>13</v>
-      </c>
-      <c r="AF24" s="239">
+    </row>
+    <row r="26" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K26" s="216"/>
+      <c r="R26" s="220"/>
+      <c r="S26" s="220"/>
+      <c r="T26" s="220"/>
+      <c r="U26" s="220"/>
+      <c r="X26" s="219"/>
+      <c r="Y26" s="219"/>
+      <c r="AJ26" s="220"/>
+      <c r="AK26" s="220"/>
+      <c r="AL26" s="220"/>
+      <c r="AM26" s="220"/>
+    </row>
+    <row r="27" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J27" s="228">
+        <v>135</v>
+      </c>
+      <c r="K27" s="229" t="s">
+        <v>85</v>
+      </c>
+      <c r="L27" s="228">
+        <f>J27+180</f>
+        <v>315</v>
+      </c>
+      <c r="M27" s="230">
+        <v>14</v>
+      </c>
+      <c r="N27" s="230">
+        <v>12</v>
+      </c>
+      <c r="O27" s="230">
+        <v>6</v>
+      </c>
+      <c r="P27" s="230">
+        <v>2</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27" s="231">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="S27" s="231">
+        <v>0.12244897959183673</v>
+      </c>
+      <c r="T27" s="231">
+        <v>6.1224489795918366E-2</v>
+      </c>
+      <c r="U27" s="231">
+        <v>2.0408163265306121E-2</v>
+      </c>
+      <c r="W27" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="X27" s="222">
+        <f>MAX(R27:U30)</f>
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="Y27" s="219"/>
+      <c r="AJ27" s="231">
+        <f>IF(R27=0,0,R27*LOG(R27,2))</f>
+        <v>-0.40105070315108637</v>
+      </c>
+      <c r="AK27" s="231">
+        <f>IF(S27=0,0,S27*LOG(S27,2))</f>
+        <v>-0.3709894706196798</v>
+      </c>
+      <c r="AL27" s="231">
+        <f>IF(T27=0,0,T27*LOG(T27,2))</f>
+        <v>-0.24671922510575831</v>
+      </c>
+      <c r="AM27" s="231">
+        <f>IF(U27=0,0,U27*LOG(U27,2))</f>
+        <v>-0.11458591518602466</v>
+      </c>
+    </row>
+    <row r="28" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M28" s="230">
+        <v>12</v>
+      </c>
+      <c r="N28" s="230">
         <v>20</v>
       </c>
-      <c r="AG24" s="239">
-        <v>7</v>
-      </c>
-      <c r="AH24" s="239">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="K25" s="216"/>
-      <c r="R25" s="220"/>
-      <c r="S25" s="220"/>
-      <c r="T25" s="220"/>
-      <c r="U25" s="220"/>
-      <c r="X25" s="219"/>
-      <c r="Y25" s="219"/>
-      <c r="Z25" s="220"/>
-      <c r="AA25" s="220"/>
-      <c r="AB25" s="220"/>
-      <c r="AC25" s="220"/>
-    </row>
-    <row r="26" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J26" s="228">
-        <v>135</v>
-      </c>
-      <c r="K26" s="229" t="s">
-        <v>89</v>
-      </c>
-      <c r="L26" s="228">
-        <f>J26+180</f>
-        <v>315</v>
-      </c>
-      <c r="M26" s="230">
-        <v>14</v>
-      </c>
-      <c r="N26" s="230">
-        <v>12</v>
-      </c>
-      <c r="O26" s="230">
-        <v>6</v>
-      </c>
-      <c r="P26" s="230">
-        <v>2</v>
-      </c>
-      <c r="Q26">
-        <v>1</v>
-      </c>
-      <c r="R26" s="231">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="S26" s="231">
-        <v>0.12244897959183673</v>
-      </c>
-      <c r="T26" s="231">
-        <v>6.1224489795918366E-2</v>
-      </c>
-      <c r="U26" s="231">
-        <v>2.0408163265306121E-2</v>
-      </c>
-      <c r="W26" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="X26" s="222">
-        <f>MAX(R26:U29)</f>
-        <v>0.20408163265306123</v>
-      </c>
-      <c r="Y26" s="219"/>
-      <c r="Z26" s="231">
-        <f t="shared" ref="Z26:AC29" si="3">IF(R26=0,0,R26*LOG(R26,2))</f>
-        <v>-0.40105070315108637</v>
-      </c>
-      <c r="AA26" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.3709894706196798</v>
-      </c>
-      <c r="AB26" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.24671922510575831</v>
-      </c>
-      <c r="AC26" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.11458591518602466</v>
-      </c>
-    </row>
-    <row r="27" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="M27" s="230">
-        <v>12</v>
-      </c>
-      <c r="N27" s="230">
-        <v>20</v>
-      </c>
-      <c r="O27" s="230">
+      <c r="O28" s="230">
         <v>4</v>
-      </c>
-      <c r="P27" s="230">
-        <v>3</v>
-      </c>
-      <c r="Q27">
-        <v>2</v>
-      </c>
-      <c r="R27" s="231">
-        <v>0.12244897959183673</v>
-      </c>
-      <c r="S27" s="231">
-        <v>0.20408163265306123</v>
-      </c>
-      <c r="T27" s="231">
-        <v>4.0816326530612242E-2</v>
-      </c>
-      <c r="U27" s="231">
-        <v>3.0612244897959183E-2</v>
-      </c>
-      <c r="W27" s="74" t="s">
-        <v>28</v>
-      </c>
-      <c r="X27" s="222">
-        <f>Q26*SUM(R26:U26)+Q27*SUM(R27:U27)+Q28*SUM(R28:U28)+Q29*SUM(R29:U29)</f>
-        <v>2.0306122448979593</v>
-      </c>
-      <c r="Y27" s="219"/>
-      <c r="Z27" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.3709894706196798</v>
-      </c>
-      <c r="AA27" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.46791464269956046</v>
-      </c>
-      <c r="AB27" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.18835550384143707</v>
-      </c>
-      <c r="AC27" s="231">
-        <f t="shared" si="3"/>
-        <v>-0.15397185745083833</v>
-      </c>
-    </row>
-    <row r="28" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="M28" s="230">
-        <v>6</v>
-      </c>
-      <c r="N28" s="230">
-        <v>4</v>
-      </c>
-      <c r="O28" s="230">
-        <v>0</v>
       </c>
       <c r="P28" s="230">
         <v>3</v>
       </c>
       <c r="Q28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R28" s="231">
-        <v>6.1224489795918366E-2</v>
+        <v>0.12244897959183673</v>
       </c>
       <c r="S28" s="231">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="T28" s="231">
         <v>4.0816326530612242E-2</v>
-      </c>
-      <c r="T28" s="231">
-        <v>0</v>
       </c>
       <c r="U28" s="231">
         <v>3.0612244897959183E-2</v>
       </c>
       <c r="W28" s="74" t="s">
+        <v>28</v>
+      </c>
+      <c r="X28" s="222">
+        <f>Q27*SUM(R27:U27)+Q28*SUM(R28:U28)+Q29*SUM(R29:U29)+Q30*SUM(R30:U30)</f>
+        <v>2.0306122448979593</v>
+      </c>
+      <c r="Y28" s="219"/>
+      <c r="AJ28" s="231">
+        <f>IF(R28=0,0,R28*LOG(R28,2))</f>
+        <v>-0.3709894706196798</v>
+      </c>
+      <c r="AK28" s="231">
+        <f>IF(S28=0,0,S28*LOG(S28,2))</f>
+        <v>-0.46791464269956046</v>
+      </c>
+      <c r="AL28" s="231">
+        <f>IF(T28=0,0,T28*LOG(T28,2))</f>
+        <v>-0.18835550384143707</v>
+      </c>
+      <c r="AM28" s="231">
+        <f>IF(U28=0,0,U28*LOG(U28,2))</f>
+        <v>-0.15397185745083833</v>
+      </c>
+    </row>
+    <row r="29" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M29" s="230">
+        <v>6</v>
+      </c>
+      <c r="N29" s="230">
+        <v>4</v>
+      </c>
+      <c r="O29" s="230">
+        <v>0</v>
+      </c>
+      <c r="P29" s="230">
+        <v>3</v>
+      </c>
+      <c r="Q29">
+        <v>3</v>
+      </c>
+      <c r="R29" s="231">
+        <v>6.1224489795918366E-2</v>
+      </c>
+      <c r="S29" s="231">
+        <v>4.0816326530612242E-2</v>
+      </c>
+      <c r="T29" s="231">
+        <v>0</v>
+      </c>
+      <c r="U29" s="231">
+        <v>3.0612244897959183E-2</v>
+      </c>
+      <c r="W29" s="74" t="s">
         <v>30</v>
       </c>
-      <c r="X28" s="222">
-        <f>(Q26-X27)^2*SUM(R26:U26)+(Q27-X27)^2*SUM(R27:U27)+(Q28-X27)^2*SUM(R28:U28)+(Q29-X27)^2*SUM(R29:U29)</f>
+      <c r="X29" s="222">
+        <f>(Q27-X28)^2*SUM(R27:U27)+(Q28-X28)^2*SUM(R28:U28)+(Q29-X28)^2*SUM(R29:U29)+(Q30-X28)^2*SUM(R30:U30)</f>
         <v>0.96845064556434823</v>
       </c>
-      <c r="Y28" s="219"/>
-      <c r="Z28" s="231">
-        <f t="shared" si="3"/>
+      <c r="Y29" s="219"/>
+      <c r="AJ29" s="231">
+        <f>IF(R29=0,0,R29*LOG(R29,2))</f>
         <v>-0.24671922510575831</v>
       </c>
-      <c r="AA28" s="231">
-        <f t="shared" si="3"/>
+      <c r="AK29" s="231">
+        <f>IF(S29=0,0,S29*LOG(S29,2))</f>
         <v>-0.18835550384143707</v>
       </c>
-      <c r="AB28" s="231">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AC28" s="231">
-        <f t="shared" si="3"/>
+      <c r="AL29" s="231">
+        <f>IF(T29=0,0,T29*LOG(T29,2))</f>
+        <v>0</v>
+      </c>
+      <c r="AM29" s="231">
+        <f>IF(U29=0,0,U29*LOG(U29,2))</f>
         <v>-0.15397185745083833</v>
       </c>
     </row>
-    <row r="29" spans="2:34" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="M29" s="230">
-        <v>2</v>
-      </c>
-      <c r="N29" s="230">
+    <row r="30" spans="2:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M30" s="230">
+        <v>2</v>
+      </c>
+      <c r="N30" s="230">
         <v>3</v>
       </c>
-      <c r="O29" s="230">
+      <c r="O30" s="230">
         <v>3</v>
       </c>
-      <c r="P29" s="230">
+      <c r="P30" s="230">
         <v>4</v>
       </c>
-      <c r="Q29">
+      <c r="Q30">
         <v>4</v>
       </c>
-      <c r="R29" s="231">
+      <c r="R30" s="231">
         <v>2.0408163265306121E-2</v>
       </c>
-      <c r="S29" s="231">
+      <c r="S30" s="231">
         <v>3.0612244897959183E-2</v>
       </c>
-      <c r="T29" s="231">
+      <c r="T30" s="231">
         <v>3.0612244897959183E-2</v>
       </c>
-      <c r="U29" s="231">
+      <c r="U30" s="231">
         <v>4.0816326530612242E-2</v>
       </c>
-      <c r="W29" s="74" t="s">
+      <c r="W30" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="X29" s="222">
-        <f>-SUM(Z26:AC29)</f>
+      <c r="X30" s="222">
+        <f>-SUM(AJ27:AM30)</f>
         <v>3.5145085090012365</v>
       </c>
-      <c r="Y29" s="219"/>
-      <c r="Z29" s="231">
-        <f t="shared" si="3"/>
+      <c r="Y30" s="219"/>
+      <c r="AJ30" s="231">
+        <f>IF(R30=0,0,R30*LOG(R30,2))</f>
         <v>-0.11458591518602466</v>
       </c>
-      <c r="AA29" s="231">
-        <f t="shared" si="3"/>
+      <c r="AK30" s="231">
+        <f>IF(S30=0,0,S30*LOG(S30,2))</f>
         <v>-0.15397185745083833</v>
       </c>
-      <c r="AB29" s="231">
-        <f t="shared" si="3"/>
+      <c r="AL30" s="231">
+        <f>IF(T30=0,0,T30*LOG(T30,2))</f>
         <v>-0.15397185745083833</v>
       </c>
-      <c r="AC29" s="231">
-        <f t="shared" si="3"/>
+      <c r="AM30" s="231">
+        <f>IF(U30=0,0,U30*LOG(U30,2))</f>
         <v>-0.18835550384143707</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="WdDGh6/abOzYiUeW2mf3dBTGAVJ6atb3oUvKw10xnqNQhNuald2cJzB5MBcmrlH0ew6+9pa1rMVnCLujFHBPkQ==" saltValue="sOKXLDV9J+cwY+4USa+aSw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="oA3Ug/9KfCFFrluaq9yww6YJp2pz1n+dPILndlP8AdPhVJ80NCrLDMxWTXyatNUo4xnnw0nFdMZ/i7RVucmlgw==" saltValue="LqPx3UPsolM2bW3uxHWqDw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
-    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="W3:X3"/>
     <mergeCell ref="W4:X4"/>
-    <mergeCell ref="Z10:AC10"/>
+    <mergeCell ref="AJ11:AM11"/>
     <mergeCell ref="Y3:Z4"/>
-    <mergeCell ref="M9:P10"/>
-    <mergeCell ref="R9:U10"/>
+    <mergeCell ref="M10:P11"/>
+    <mergeCell ref="R10:U11"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="B4" r:id="rId1" xr:uid="{DAE58F5A-E59C-48E7-8567-91DF9C83DAAF}"/>
-    <hyperlink ref="B5" r:id="rId2" xr:uid="{EA50A9D2-75D3-4B81-ACC3-0522675DC24C}"/>
-    <hyperlink ref="B7" r:id="rId3" xr:uid="{C8C5C4AA-98E9-4A40-9127-FEDCA006F1CC}"/>
-    <hyperlink ref="B8" r:id="rId4" xr:uid="{53B6EFD0-4201-4794-B5F6-6C5BC92FC4CD}"/>
     <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{ADD3407C-F48E-4B24-927E-D7A0BDE66701}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{936E9B21-1CA6-4114-BDC3-AD2DA0FD1494}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{15F0E12B-B65A-4566-8A17-8D60D2CA6517}"/>
+    <hyperlink ref="B8" r:id="rId3" xr:uid="{09E62C2C-A0B2-439D-A8CE-8683510470C9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -28585,8 +28940,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="282" t="s">
-        <v>101</v>
+      <c r="A1" s="242" t="s">
+        <v>97</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>49</v>
@@ -28682,13 +29037,13 @@
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
-      <c r="X4" s="276" t="s">
+      <c r="X4" s="279" t="s">
         <v>34</v>
       </c>
-      <c r="Y4" s="276"/>
-      <c r="Z4" s="276"/>
-      <c r="AA4" s="276"/>
-      <c r="AB4" s="276"/>
+      <c r="Y4" s="279"/>
+      <c r="Z4" s="279"/>
+      <c r="AA4" s="279"/>
+      <c r="AB4" s="279"/>
     </row>
     <row r="5" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -30456,16 +30811,16 @@
       </c>
       <c r="AB32" s="111"/>
       <c r="AC32" s="111"/>
-      <c r="AD32" s="279" t="s">
+      <c r="AD32" s="282" t="s">
         <v>45</v>
       </c>
-      <c r="AE32" s="279"/>
-      <c r="AF32" s="279"/>
-      <c r="AG32" s="279"/>
-      <c r="AH32" s="279"/>
-      <c r="AI32" s="279"/>
-      <c r="AJ32" s="279"/>
-      <c r="AK32" s="279"/>
+      <c r="AE32" s="282"/>
+      <c r="AF32" s="282"/>
+      <c r="AG32" s="282"/>
+      <c r="AH32" s="282"/>
+      <c r="AI32" s="282"/>
+      <c r="AJ32" s="282"/>
+      <c r="AK32" s="282"/>
     </row>
     <row r="33" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -30482,16 +30837,16 @@
       <c r="AE33" s="182">
         <v>1</v>
       </c>
-      <c r="AF33" s="277">
-        <v>2</v>
-      </c>
-      <c r="AG33" s="277"/>
-      <c r="AH33" s="277">
+      <c r="AF33" s="280">
+        <v>2</v>
+      </c>
+      <c r="AG33" s="280"/>
+      <c r="AH33" s="280">
         <v>4</v>
       </c>
-      <c r="AI33" s="277"/>
-      <c r="AJ33" s="277"/>
-      <c r="AK33" s="277"/>
+      <c r="AI33" s="280"/>
+      <c r="AJ33" s="280"/>
+      <c r="AK33" s="280"/>
     </row>
     <row r="34" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B34" s="167">
@@ -30558,7 +30913,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="278" t="s">
+      <c r="AB34" s="281" t="s">
         <v>46</v>
       </c>
       <c r="AC34" s="181">
@@ -30638,7 +30993,7 @@
         <f t="shared" si="34"/>
         <v>16</v>
       </c>
-      <c r="AB35" s="278"/>
+      <c r="AB35" s="281"/>
       <c r="AC35" s="181">
         <v>1</v>
       </c>
@@ -30716,8 +31071,8 @@
         <f t="shared" si="36"/>
         <v>16</v>
       </c>
-      <c r="AB36" s="278"/>
-      <c r="AC36" s="280">
+      <c r="AB36" s="281"/>
+      <c r="AC36" s="283">
         <v>2</v>
       </c>
       <c r="AD36" s="186"/>
@@ -30794,8 +31149,8 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="278"/>
-      <c r="AC37" s="280"/>
+      <c r="AB37" s="281"/>
+      <c r="AC37" s="283"/>
       <c r="AD37" s="187"/>
       <c r="AE37" s="191"/>
       <c r="AF37" s="199"/>
@@ -30870,8 +31225,8 @@
         <f t="shared" si="40"/>
         <v>-16</v>
       </c>
-      <c r="AB38" s="278"/>
-      <c r="AC38" s="280">
+      <c r="AB38" s="281"/>
+      <c r="AC38" s="283">
         <v>4</v>
       </c>
       <c r="AD38" s="186"/>
@@ -30948,8 +31303,8 @@
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AB39" s="278"/>
-      <c r="AC39" s="280"/>
+      <c r="AB39" s="281"/>
+      <c r="AC39" s="283"/>
       <c r="AD39" s="188"/>
       <c r="AE39" s="174"/>
       <c r="AF39" s="174"/>
@@ -31024,8 +31379,8 @@
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="278"/>
-      <c r="AC40" s="280"/>
+      <c r="AB40" s="281"/>
+      <c r="AC40" s="283"/>
       <c r="AD40" s="188"/>
       <c r="AE40" s="174"/>
       <c r="AF40" s="174"/>
@@ -31100,8 +31455,8 @@
         <f t="shared" si="46"/>
         <v>16</v>
       </c>
-      <c r="AB41" s="278"/>
-      <c r="AC41" s="280"/>
+      <c r="AB41" s="281"/>
+      <c r="AC41" s="283"/>
       <c r="AD41" s="187"/>
       <c r="AE41" s="175"/>
       <c r="AF41" s="175"/>
@@ -31160,9 +31515,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31356,26 +31714,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E7E2A7-086F-4414-A818-C355190A2115}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2764B03-5387-4537-A949-7B2C7AF6C83E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="564c14fb-bfcd-4e52-83e8-2447e9c77f65"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31400,9 +31747,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2764B03-5387-4537-A949-7B2C7AF6C83E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E7E2A7-086F-4414-A818-C355190A2115}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="564c14fb-bfcd-4e52-83e8-2447e9c77f65"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Convolution-Radiomics-Wavelet.xlsx
+++ b/Convolution-Radiomics-Wavelet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HN-Data-1\教育\講義\講義2年生-AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3F8346-F485-48DF-ADCD-B3116E1A735B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E54CF36-1B8D-48A9-8E0D-CCB2C13C80A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="11" r:id="rId1"/>
@@ -2924,7 +2924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="296">
+  <cellXfs count="292">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3682,6 +3682,42 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="63" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="64" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="41" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3739,9 +3775,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3753,15 +3786,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3781,14 +3805,14 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3803,42 +3827,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="65" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="63" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="64" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="41" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5346,16 +5334,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>717176</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>67235</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>44824</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>145679</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
-      <xdr:colOff>268939</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>179295</xdr:rowOff>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>145678</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5370,13 +5358,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12348882" y="1882588"/>
-          <a:ext cx="2420469" cy="918883"/>
+          <a:off x="12528177" y="2767855"/>
+          <a:ext cx="2162735" cy="1210235"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -116474"/>
-            <a:gd name="adj2" fmla="val -39288"/>
+            <a:gd name="adj1" fmla="val -137341"/>
+            <a:gd name="adj2" fmla="val -18791"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -5414,7 +5402,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>対象画像の異方性が残りやすい</a:t>
+            <a:t>対象画像の異方性に準じた</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
@@ -5430,7 +5418,7 @@
                 <a:schemeClr val="tx1"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>特徴量</a:t>
+            <a:t>特徴量を算出後、平均化する。</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -5440,15 +5428,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>358588</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>134470</xdr:rowOff>
+      <xdr:colOff>89647</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>123265</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>26893</xdr:rowOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>100853</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>190501</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -5463,13 +5451,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11990294" y="3160058"/>
-          <a:ext cx="2409265" cy="900953"/>
+          <a:off x="11721353" y="5053853"/>
+          <a:ext cx="2207559" cy="1187824"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val 98391"/>
-            <a:gd name="adj2" fmla="val -50171"/>
+            <a:gd name="adj1" fmla="val 71717"/>
+            <a:gd name="adj2" fmla="val 25402"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -5545,7 +5533,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>が平均化された</a:t>
+            <a:t>を平均化した後、</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
@@ -5571,12 +5559,117 @@
             </a:rPr>
             <a:t>特徴量</a:t>
           </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>を算出する</a:t>
+          </a:r>
           <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="1800">
             <a:solidFill>
               <a:schemeClr val="tx1"/>
             </a:solidFill>
             <a:effectLst/>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>567018</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>56030</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>33618</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>56031</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="吹き出し: 角を丸めた四角形 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BF1366A-741A-438C-9160-D69EBF1CF3D2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13050371" y="1871383"/>
+          <a:ext cx="2010335" cy="806824"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -42375"/>
+            <a:gd name="adj2" fmla="val -87140"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>差分を見ると</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>entropy</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>への影響が大きい</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7809,14 +7902,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="243" t="s">
+      <c r="X15" s="255" t="s">
         <v>19</v>
       </c>
-      <c r="Y15" s="244"/>
-      <c r="Z15" s="244"/>
-      <c r="AA15" s="244"/>
-      <c r="AB15" s="244"/>
-      <c r="AC15" s="245"/>
+      <c r="Y15" s="256"/>
+      <c r="Z15" s="256"/>
+      <c r="AA15" s="256"/>
+      <c r="AB15" s="256"/>
+      <c r="AC15" s="257"/>
     </row>
     <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -7862,12 +7955,12 @@
       <c r="Q16" s="49"/>
       <c r="R16" s="49"/>
       <c r="S16" s="49"/>
-      <c r="X16" s="246"/>
-      <c r="Y16" s="247"/>
-      <c r="Z16" s="247"/>
-      <c r="AA16" s="247"/>
-      <c r="AB16" s="247"/>
-      <c r="AC16" s="248"/>
+      <c r="X16" s="258"/>
+      <c r="Y16" s="259"/>
+      <c r="Z16" s="259"/>
+      <c r="AA16" s="259"/>
+      <c r="AB16" s="259"/>
+      <c r="AC16" s="260"/>
     </row>
     <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -7910,12 +8003,12 @@
       <c r="Q17" s="49"/>
       <c r="R17" s="49"/>
       <c r="S17" s="49"/>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="247"/>
-      <c r="Z17" s="247"/>
-      <c r="AA17" s="247"/>
-      <c r="AB17" s="247"/>
-      <c r="AC17" s="248"/>
+      <c r="X17" s="258"/>
+      <c r="Y17" s="259"/>
+      <c r="Z17" s="259"/>
+      <c r="AA17" s="259"/>
+      <c r="AB17" s="259"/>
+      <c r="AC17" s="260"/>
     </row>
     <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
@@ -7958,12 +8051,12 @@
       <c r="Q18" s="49"/>
       <c r="R18" s="49"/>
       <c r="S18" s="49"/>
-      <c r="X18" s="246"/>
-      <c r="Y18" s="247"/>
-      <c r="Z18" s="247"/>
-      <c r="AA18" s="247"/>
-      <c r="AB18" s="247"/>
-      <c r="AC18" s="248"/>
+      <c r="X18" s="258"/>
+      <c r="Y18" s="259"/>
+      <c r="Z18" s="259"/>
+      <c r="AA18" s="259"/>
+      <c r="AB18" s="259"/>
+      <c r="AC18" s="260"/>
     </row>
     <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -8006,12 +8099,12 @@
       <c r="Q19" s="49"/>
       <c r="R19" s="49"/>
       <c r="S19" s="49"/>
-      <c r="X19" s="246"/>
-      <c r="Y19" s="247"/>
-      <c r="Z19" s="247"/>
-      <c r="AA19" s="247"/>
-      <c r="AB19" s="247"/>
-      <c r="AC19" s="248"/>
+      <c r="X19" s="258"/>
+      <c r="Y19" s="259"/>
+      <c r="Z19" s="259"/>
+      <c r="AA19" s="259"/>
+      <c r="AB19" s="259"/>
+      <c r="AC19" s="260"/>
     </row>
     <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
@@ -8054,12 +8147,12 @@
       <c r="Q20" s="49"/>
       <c r="R20" s="49"/>
       <c r="S20" s="49"/>
-      <c r="X20" s="246"/>
-      <c r="Y20" s="247"/>
-      <c r="Z20" s="247"/>
-      <c r="AA20" s="247"/>
-      <c r="AB20" s="247"/>
-      <c r="AC20" s="248"/>
+      <c r="X20" s="258"/>
+      <c r="Y20" s="259"/>
+      <c r="Z20" s="259"/>
+      <c r="AA20" s="259"/>
+      <c r="AB20" s="259"/>
+      <c r="AC20" s="260"/>
     </row>
     <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
@@ -8102,12 +8195,12 @@
       <c r="Q21" s="49"/>
       <c r="R21" s="49"/>
       <c r="S21" s="49"/>
-      <c r="X21" s="246"/>
-      <c r="Y21" s="247"/>
-      <c r="Z21" s="247"/>
-      <c r="AA21" s="247"/>
-      <c r="AB21" s="247"/>
-      <c r="AC21" s="248"/>
+      <c r="X21" s="258"/>
+      <c r="Y21" s="259"/>
+      <c r="Z21" s="259"/>
+      <c r="AA21" s="259"/>
+      <c r="AB21" s="259"/>
+      <c r="AC21" s="260"/>
     </row>
     <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -8150,12 +8243,12 @@
       <c r="Q22" s="49"/>
       <c r="R22" s="49"/>
       <c r="S22" s="49"/>
-      <c r="X22" s="246"/>
-      <c r="Y22" s="247"/>
-      <c r="Z22" s="247"/>
-      <c r="AA22" s="247"/>
-      <c r="AB22" s="247"/>
-      <c r="AC22" s="248"/>
+      <c r="X22" s="258"/>
+      <c r="Y22" s="259"/>
+      <c r="Z22" s="259"/>
+      <c r="AA22" s="259"/>
+      <c r="AB22" s="259"/>
+      <c r="AC22" s="260"/>
     </row>
     <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
@@ -8198,12 +8291,12 @@
       <c r="Q23" s="49"/>
       <c r="R23" s="49"/>
       <c r="S23" s="49"/>
-      <c r="X23" s="249"/>
-      <c r="Y23" s="250"/>
-      <c r="Z23" s="250"/>
-      <c r="AA23" s="250"/>
-      <c r="AB23" s="250"/>
-      <c r="AC23" s="251"/>
+      <c r="X23" s="261"/>
+      <c r="Y23" s="262"/>
+      <c r="Z23" s="262"/>
+      <c r="AA23" s="262"/>
+      <c r="AB23" s="262"/>
+      <c r="AC23" s="263"/>
     </row>
     <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
@@ -9107,14 +9200,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="243" t="s">
+      <c r="X15" s="255" t="s">
         <v>23</v>
       </c>
-      <c r="Y15" s="244"/>
-      <c r="Z15" s="244"/>
-      <c r="AA15" s="244"/>
-      <c r="AB15" s="244"/>
-      <c r="AC15" s="245"/>
+      <c r="Y15" s="256"/>
+      <c r="Z15" s="256"/>
+      <c r="AA15" s="256"/>
+      <c r="AB15" s="256"/>
+      <c r="AC15" s="257"/>
     </row>
     <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -9181,12 +9274,12 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="X16" s="246"/>
-      <c r="Y16" s="247"/>
-      <c r="Z16" s="247"/>
-      <c r="AA16" s="247"/>
-      <c r="AB16" s="247"/>
-      <c r="AC16" s="248"/>
+      <c r="X16" s="258"/>
+      <c r="Y16" s="259"/>
+      <c r="Z16" s="259"/>
+      <c r="AA16" s="259"/>
+      <c r="AB16" s="259"/>
+      <c r="AC16" s="260"/>
     </row>
     <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -9253,12 +9346,12 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="X17" s="246"/>
-      <c r="Y17" s="247"/>
-      <c r="Z17" s="247"/>
-      <c r="AA17" s="247"/>
-      <c r="AB17" s="247"/>
-      <c r="AC17" s="248"/>
+      <c r="X17" s="258"/>
+      <c r="Y17" s="259"/>
+      <c r="Z17" s="259"/>
+      <c r="AA17" s="259"/>
+      <c r="AB17" s="259"/>
+      <c r="AC17" s="260"/>
     </row>
     <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
@@ -9325,12 +9418,12 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="X18" s="246"/>
-      <c r="Y18" s="247"/>
-      <c r="Z18" s="247"/>
-      <c r="AA18" s="247"/>
-      <c r="AB18" s="247"/>
-      <c r="AC18" s="248"/>
+      <c r="X18" s="258"/>
+      <c r="Y18" s="259"/>
+      <c r="Z18" s="259"/>
+      <c r="AA18" s="259"/>
+      <c r="AB18" s="259"/>
+      <c r="AC18" s="260"/>
     </row>
     <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -9397,12 +9490,12 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="X19" s="246"/>
-      <c r="Y19" s="247"/>
-      <c r="Z19" s="247"/>
-      <c r="AA19" s="247"/>
-      <c r="AB19" s="247"/>
-      <c r="AC19" s="248"/>
+      <c r="X19" s="258"/>
+      <c r="Y19" s="259"/>
+      <c r="Z19" s="259"/>
+      <c r="AA19" s="259"/>
+      <c r="AB19" s="259"/>
+      <c r="AC19" s="260"/>
     </row>
     <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
@@ -9469,12 +9562,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="X20" s="246"/>
-      <c r="Y20" s="247"/>
-      <c r="Z20" s="247"/>
-      <c r="AA20" s="247"/>
-      <c r="AB20" s="247"/>
-      <c r="AC20" s="248"/>
+      <c r="X20" s="258"/>
+      <c r="Y20" s="259"/>
+      <c r="Z20" s="259"/>
+      <c r="AA20" s="259"/>
+      <c r="AB20" s="259"/>
+      <c r="AC20" s="260"/>
     </row>
     <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
@@ -9541,12 +9634,12 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="X21" s="246"/>
-      <c r="Y21" s="247"/>
-      <c r="Z21" s="247"/>
-      <c r="AA21" s="247"/>
-      <c r="AB21" s="247"/>
-      <c r="AC21" s="248"/>
+      <c r="X21" s="258"/>
+      <c r="Y21" s="259"/>
+      <c r="Z21" s="259"/>
+      <c r="AA21" s="259"/>
+      <c r="AB21" s="259"/>
+      <c r="AC21" s="260"/>
     </row>
     <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -9613,12 +9706,12 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="X22" s="246"/>
-      <c r="Y22" s="247"/>
-      <c r="Z22" s="247"/>
-      <c r="AA22" s="247"/>
-      <c r="AB22" s="247"/>
-      <c r="AC22" s="248"/>
+      <c r="X22" s="258"/>
+      <c r="Y22" s="259"/>
+      <c r="Z22" s="259"/>
+      <c r="AA22" s="259"/>
+      <c r="AB22" s="259"/>
+      <c r="AC22" s="260"/>
     </row>
     <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
@@ -9685,12 +9778,12 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="X23" s="249"/>
-      <c r="Y23" s="250"/>
-      <c r="Z23" s="250"/>
-      <c r="AA23" s="250"/>
-      <c r="AB23" s="250"/>
-      <c r="AC23" s="251"/>
+      <c r="X23" s="261"/>
+      <c r="Y23" s="262"/>
+      <c r="Z23" s="262"/>
+      <c r="AA23" s="262"/>
+      <c r="AB23" s="262"/>
+      <c r="AC23" s="263"/>
     </row>
     <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
@@ -10161,25 +10254,25 @@
         <v>1</v>
       </c>
       <c r="T9" s="20"/>
-      <c r="X9" s="255" t="s">
+      <c r="X9" s="267" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="256"/>
-      <c r="Z9" s="256"/>
-      <c r="AA9" s="257"/>
-      <c r="AF9" s="255" t="s">
+      <c r="Y9" s="268"/>
+      <c r="Z9" s="268"/>
+      <c r="AA9" s="269"/>
+      <c r="AF9" s="267" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="256"/>
-      <c r="AH9" s="256"/>
-      <c r="AI9" s="257"/>
-      <c r="AL9" s="258" t="s">
+      <c r="AG9" s="268"/>
+      <c r="AH9" s="268"/>
+      <c r="AI9" s="269"/>
+      <c r="AL9" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="259"/>
-      <c r="AN9" s="259"/>
-      <c r="AO9" s="259"/>
-      <c r="AP9" s="260"/>
+      <c r="AM9" s="271"/>
+      <c r="AN9" s="271"/>
+      <c r="AO9" s="271"/>
+      <c r="AP9" s="272"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -10264,11 +10357,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="261"/>
-      <c r="AM10" s="262"/>
-      <c r="AN10" s="262"/>
-      <c r="AO10" s="262"/>
-      <c r="AP10" s="263"/>
+      <c r="AL10" s="273"/>
+      <c r="AM10" s="254"/>
+      <c r="AN10" s="254"/>
+      <c r="AO10" s="254"/>
+      <c r="AP10" s="274"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -10332,7 +10425,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="20"/>
-      <c r="V11" s="252" t="s">
+      <c r="V11" s="264" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -10354,7 +10447,7 @@
         <f>SUM(AC17:AI24)</f>
         <v>1</v>
       </c>
-      <c r="AD11" s="252" t="s">
+      <c r="AD11" s="264" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -10462,7 +10555,7 @@
         <v>3</v>
       </c>
       <c r="T12" s="20"/>
-      <c r="V12" s="253"/>
+      <c r="V12" s="265"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -10482,7 +10575,7 @@
         <f>SUM(AC27:AI34)</f>
         <v>4</v>
       </c>
-      <c r="AD12" s="253"/>
+      <c r="AD12" s="265"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -10588,7 +10681,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="20"/>
-      <c r="V13" s="253"/>
+      <c r="V13" s="265"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -10608,7 +10701,7 @@
         <f>SUM(AC37:AI44)</f>
         <v>1</v>
       </c>
-      <c r="AD13" s="253"/>
+      <c r="AD13" s="265"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -10666,7 +10759,7 @@
       <c r="R14" s="20"/>
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
-      <c r="V14" s="254"/>
+      <c r="V14" s="266"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -10686,7 +10779,7 @@
         <f>SUM(AC47:AI54)</f>
         <v>1</v>
       </c>
-      <c r="AD14" s="254"/>
+      <c r="AD14" s="266"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -15296,14 +15389,14 @@
         <v>0</v>
       </c>
       <c r="Z3" s="211"/>
-      <c r="AA3" s="265" t="s">
+      <c r="AA3" s="276" t="s">
         <v>72</v>
       </c>
-      <c r="AB3" s="265"/>
-      <c r="AC3" s="265"/>
-      <c r="AD3" s="265"/>
-      <c r="AE3" s="265"/>
-      <c r="AF3" s="265"/>
+      <c r="AB3" s="276"/>
+      <c r="AC3" s="276"/>
+      <c r="AD3" s="276"/>
+      <c r="AE3" s="276"/>
+      <c r="AF3" s="276"/>
     </row>
     <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
@@ -15353,24 +15446,24 @@
       <c r="Z4" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="AA4" s="264" t="s">
+      <c r="AA4" s="275" t="s">
         <v>70</v>
       </c>
-      <c r="AB4" s="264"/>
-      <c r="AC4" s="264"/>
-      <c r="AD4" s="264"/>
-      <c r="AE4" s="264"/>
-      <c r="AF4" s="264"/>
-      <c r="AG4" s="264"/>
-      <c r="AH4" s="264"/>
-      <c r="AI4" s="264"/>
-      <c r="AJ4" s="264"/>
-      <c r="AK4" s="264"/>
-      <c r="AL4" s="264"/>
-      <c r="AM4" s="264"/>
-      <c r="AN4" s="264"/>
-      <c r="AO4" s="264"/>
-      <c r="AP4" s="264"/>
+      <c r="AB4" s="275"/>
+      <c r="AC4" s="275"/>
+      <c r="AD4" s="275"/>
+      <c r="AE4" s="275"/>
+      <c r="AF4" s="275"/>
+      <c r="AG4" s="275"/>
+      <c r="AH4" s="275"/>
+      <c r="AI4" s="275"/>
+      <c r="AJ4" s="275"/>
+      <c r="AK4" s="275"/>
+      <c r="AL4" s="275"/>
+      <c r="AM4" s="275"/>
+      <c r="AN4" s="275"/>
+      <c r="AO4" s="275"/>
+      <c r="AP4" s="275"/>
     </row>
     <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -15723,25 +15816,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="255" t="s">
+      <c r="X9" s="267" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="256"/>
-      <c r="Z9" s="256"/>
-      <c r="AA9" s="257"/>
-      <c r="AF9" s="255" t="s">
+      <c r="Y9" s="268"/>
+      <c r="Z9" s="268"/>
+      <c r="AA9" s="269"/>
+      <c r="AF9" s="267" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="256"/>
-      <c r="AH9" s="256"/>
-      <c r="AI9" s="257"/>
-      <c r="AL9" s="266" t="s">
+      <c r="AG9" s="268"/>
+      <c r="AH9" s="268"/>
+      <c r="AI9" s="269"/>
+      <c r="AL9" s="277" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="266"/>
-      <c r="AN9" s="266"/>
-      <c r="AO9" s="266"/>
-      <c r="AP9" s="266"/>
+      <c r="AM9" s="277"/>
+      <c r="AN9" s="277"/>
+      <c r="AO9" s="277"/>
+      <c r="AP9" s="277"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -15832,11 +15925,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="266"/>
-      <c r="AM10" s="266"/>
-      <c r="AN10" s="266"/>
-      <c r="AO10" s="266"/>
-      <c r="AP10" s="266"/>
+      <c r="AL10" s="277"/>
+      <c r="AM10" s="277"/>
+      <c r="AN10" s="277"/>
+      <c r="AO10" s="277"/>
+      <c r="AP10" s="277"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -15906,7 +15999,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="252" t="s">
+      <c r="V11" s="264" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -15928,7 +16021,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>4</v>
       </c>
-      <c r="AD11" s="252" t="s">
+      <c r="AD11" s="264" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -16042,7 +16135,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="253"/>
+      <c r="V12" s="265"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -16062,7 +16155,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>6</v>
       </c>
-      <c r="AD12" s="253"/>
+      <c r="AD12" s="265"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -16174,7 +16267,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="253"/>
+      <c r="V13" s="265"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -16194,7 +16287,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>2</v>
       </c>
-      <c r="AD13" s="253"/>
+      <c r="AD13" s="265"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -16282,7 +16375,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="254"/>
+      <c r="V14" s="266"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -16302,7 +16395,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>2</v>
       </c>
-      <c r="AD14" s="254"/>
+      <c r="AD14" s="266"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -21303,31 +21396,31 @@
       <c r="J2" t="s">
         <v>56</v>
       </c>
-      <c r="V2" s="270" t="s">
+      <c r="V2" s="278" t="s">
         <v>80</v>
       </c>
-      <c r="W2" s="271"/>
-      <c r="X2" s="271"/>
-      <c r="Y2" s="271"/>
-      <c r="Z2" s="271"/>
-      <c r="AA2" s="271"/>
-      <c r="AB2" s="271"/>
-      <c r="AC2" s="271"/>
-      <c r="AD2" s="271"/>
-      <c r="AE2" s="271"/>
-      <c r="AF2" s="271"/>
-      <c r="AG2" s="271"/>
-      <c r="AH2" s="271"/>
-      <c r="AI2" s="271"/>
-      <c r="AJ2" s="271"/>
-      <c r="AK2" s="271"/>
-      <c r="AL2" s="271"/>
-      <c r="AM2" s="271"/>
-      <c r="AN2" s="271"/>
-      <c r="AO2" s="271"/>
-      <c r="AP2" s="271"/>
-      <c r="AQ2" s="271"/>
-      <c r="AR2" s="272"/>
+      <c r="W2" s="279"/>
+      <c r="X2" s="279"/>
+      <c r="Y2" s="279"/>
+      <c r="Z2" s="279"/>
+      <c r="AA2" s="279"/>
+      <c r="AB2" s="279"/>
+      <c r="AC2" s="279"/>
+      <c r="AD2" s="279"/>
+      <c r="AE2" s="279"/>
+      <c r="AF2" s="279"/>
+      <c r="AG2" s="279"/>
+      <c r="AH2" s="279"/>
+      <c r="AI2" s="279"/>
+      <c r="AJ2" s="279"/>
+      <c r="AK2" s="279"/>
+      <c r="AL2" s="279"/>
+      <c r="AM2" s="279"/>
+      <c r="AN2" s="279"/>
+      <c r="AO2" s="279"/>
+      <c r="AP2" s="279"/>
+      <c r="AQ2" s="279"/>
+      <c r="AR2" s="280"/>
     </row>
     <row r="3" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
@@ -21350,31 +21443,31 @@
       <c r="O3" t="s">
         <v>5</v>
       </c>
-      <c r="V3" s="270" t="s">
+      <c r="V3" s="278" t="s">
         <v>77</v>
       </c>
-      <c r="W3" s="271"/>
-      <c r="X3" s="271"/>
-      <c r="Y3" s="271"/>
-      <c r="Z3" s="271"/>
-      <c r="AA3" s="271"/>
-      <c r="AB3" s="271"/>
-      <c r="AC3" s="271"/>
-      <c r="AD3" s="271"/>
-      <c r="AE3" s="271"/>
-      <c r="AF3" s="271"/>
-      <c r="AG3" s="271"/>
-      <c r="AH3" s="271"/>
-      <c r="AI3" s="271"/>
-      <c r="AJ3" s="271"/>
-      <c r="AK3" s="271"/>
-      <c r="AL3" s="271"/>
-      <c r="AM3" s="271"/>
-      <c r="AN3" s="271"/>
-      <c r="AO3" s="271"/>
-      <c r="AP3" s="271"/>
-      <c r="AQ3" s="271"/>
-      <c r="AR3" s="272"/>
+      <c r="W3" s="279"/>
+      <c r="X3" s="279"/>
+      <c r="Y3" s="279"/>
+      <c r="Z3" s="279"/>
+      <c r="AA3" s="279"/>
+      <c r="AB3" s="279"/>
+      <c r="AC3" s="279"/>
+      <c r="AD3" s="279"/>
+      <c r="AE3" s="279"/>
+      <c r="AF3" s="279"/>
+      <c r="AG3" s="279"/>
+      <c r="AH3" s="279"/>
+      <c r="AI3" s="279"/>
+      <c r="AJ3" s="279"/>
+      <c r="AK3" s="279"/>
+      <c r="AL3" s="279"/>
+      <c r="AM3" s="279"/>
+      <c r="AN3" s="279"/>
+      <c r="AO3" s="279"/>
+      <c r="AP3" s="279"/>
+      <c r="AQ3" s="279"/>
+      <c r="AR3" s="280"/>
     </row>
     <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
@@ -21409,31 +21502,31 @@
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
-      <c r="V4" s="273" t="s">
+      <c r="V4" s="281" t="s">
         <v>78</v>
       </c>
-      <c r="W4" s="274"/>
-      <c r="X4" s="274"/>
-      <c r="Y4" s="274"/>
-      <c r="Z4" s="274"/>
-      <c r="AA4" s="274"/>
-      <c r="AB4" s="274"/>
-      <c r="AC4" s="274"/>
-      <c r="AD4" s="274"/>
-      <c r="AE4" s="274"/>
-      <c r="AF4" s="274"/>
-      <c r="AG4" s="274"/>
-      <c r="AH4" s="274"/>
-      <c r="AI4" s="274"/>
-      <c r="AJ4" s="274"/>
-      <c r="AK4" s="274"/>
-      <c r="AL4" s="274"/>
-      <c r="AM4" s="274"/>
-      <c r="AN4" s="274"/>
-      <c r="AO4" s="274"/>
-      <c r="AP4" s="274"/>
-      <c r="AQ4" s="274"/>
-      <c r="AR4" s="275"/>
+      <c r="W4" s="282"/>
+      <c r="X4" s="282"/>
+      <c r="Y4" s="282"/>
+      <c r="Z4" s="282"/>
+      <c r="AA4" s="282"/>
+      <c r="AB4" s="282"/>
+      <c r="AC4" s="282"/>
+      <c r="AD4" s="282"/>
+      <c r="AE4" s="282"/>
+      <c r="AF4" s="282"/>
+      <c r="AG4" s="282"/>
+      <c r="AH4" s="282"/>
+      <c r="AI4" s="282"/>
+      <c r="AJ4" s="282"/>
+      <c r="AK4" s="282"/>
+      <c r="AL4" s="282"/>
+      <c r="AM4" s="282"/>
+      <c r="AN4" s="282"/>
+      <c r="AO4" s="282"/>
+      <c r="AP4" s="282"/>
+      <c r="AQ4" s="282"/>
+      <c r="AR4" s="283"/>
     </row>
     <row r="5" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" t="s">
@@ -21479,31 +21572,31 @@
         <f>(S5+T6)/2</f>
         <v>0</v>
       </c>
-      <c r="V5" s="270" t="s">
+      <c r="V5" s="278" t="s">
         <v>76</v>
       </c>
-      <c r="W5" s="271"/>
-      <c r="X5" s="271"/>
-      <c r="Y5" s="271"/>
-      <c r="Z5" s="271"/>
-      <c r="AA5" s="271"/>
-      <c r="AB5" s="271"/>
-      <c r="AC5" s="271"/>
-      <c r="AD5" s="271"/>
-      <c r="AE5" s="271"/>
-      <c r="AF5" s="271"/>
-      <c r="AG5" s="271"/>
-      <c r="AH5" s="271"/>
-      <c r="AI5" s="271"/>
-      <c r="AJ5" s="271"/>
-      <c r="AK5" s="271"/>
-      <c r="AL5" s="271"/>
-      <c r="AM5" s="271"/>
-      <c r="AN5" s="271"/>
-      <c r="AO5" s="271"/>
-      <c r="AP5" s="271"/>
-      <c r="AQ5" s="271"/>
-      <c r="AR5" s="272"/>
+      <c r="W5" s="279"/>
+      <c r="X5" s="279"/>
+      <c r="Y5" s="279"/>
+      <c r="Z5" s="279"/>
+      <c r="AA5" s="279"/>
+      <c r="AB5" s="279"/>
+      <c r="AC5" s="279"/>
+      <c r="AD5" s="279"/>
+      <c r="AE5" s="279"/>
+      <c r="AF5" s="279"/>
+      <c r="AG5" s="279"/>
+      <c r="AH5" s="279"/>
+      <c r="AI5" s="279"/>
+      <c r="AJ5" s="279"/>
+      <c r="AK5" s="279"/>
+      <c r="AL5" s="279"/>
+      <c r="AM5" s="279"/>
+      <c r="AN5" s="279"/>
+      <c r="AO5" s="279"/>
+      <c r="AP5" s="279"/>
+      <c r="AQ5" s="279"/>
+      <c r="AR5" s="280"/>
     </row>
     <row r="6" spans="1:47" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="1">
@@ -21570,31 +21663,31 @@
         <f>S6*$N$3</f>
         <v>0</v>
       </c>
-      <c r="V6" s="273" t="s">
+      <c r="V6" s="281" t="s">
         <v>79</v>
       </c>
-      <c r="W6" s="274"/>
-      <c r="X6" s="274"/>
-      <c r="Y6" s="274"/>
-      <c r="Z6" s="274"/>
-      <c r="AA6" s="274"/>
-      <c r="AB6" s="274"/>
-      <c r="AC6" s="274"/>
-      <c r="AD6" s="274"/>
-      <c r="AE6" s="274"/>
-      <c r="AF6" s="274"/>
-      <c r="AG6" s="274"/>
-      <c r="AH6" s="274"/>
-      <c r="AI6" s="274"/>
-      <c r="AJ6" s="274"/>
-      <c r="AK6" s="274"/>
-      <c r="AL6" s="274"/>
-      <c r="AM6" s="274"/>
-      <c r="AN6" s="274"/>
-      <c r="AO6" s="274"/>
-      <c r="AP6" s="274"/>
-      <c r="AQ6" s="274"/>
-      <c r="AR6" s="275"/>
+      <c r="W6" s="282"/>
+      <c r="X6" s="282"/>
+      <c r="Y6" s="282"/>
+      <c r="Z6" s="282"/>
+      <c r="AA6" s="282"/>
+      <c r="AB6" s="282"/>
+      <c r="AC6" s="282"/>
+      <c r="AD6" s="282"/>
+      <c r="AE6" s="282"/>
+      <c r="AF6" s="282"/>
+      <c r="AG6" s="282"/>
+      <c r="AH6" s="282"/>
+      <c r="AI6" s="282"/>
+      <c r="AJ6" s="282"/>
+      <c r="AK6" s="282"/>
+      <c r="AL6" s="282"/>
+      <c r="AM6" s="282"/>
+      <c r="AN6" s="282"/>
+      <c r="AO6" s="282"/>
+      <c r="AP6" s="282"/>
+      <c r="AQ6" s="282"/>
+      <c r="AR6" s="283"/>
     </row>
     <row r="7" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B7" s="1">
@@ -21799,25 +21892,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="267" t="s">
+      <c r="X9" s="284" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
-      <c r="AA9" s="269"/>
-      <c r="AF9" s="267" t="s">
+      <c r="Y9" s="285"/>
+      <c r="Z9" s="285"/>
+      <c r="AA9" s="286"/>
+      <c r="AF9" s="284" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="268"/>
-      <c r="AH9" s="268"/>
-      <c r="AI9" s="269"/>
-      <c r="AL9" s="266" t="s">
+      <c r="AG9" s="285"/>
+      <c r="AH9" s="285"/>
+      <c r="AI9" s="286"/>
+      <c r="AL9" s="277" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="266"/>
-      <c r="AN9" s="266"/>
-      <c r="AO9" s="266"/>
-      <c r="AP9" s="266"/>
+      <c r="AM9" s="277"/>
+      <c r="AN9" s="277"/>
+      <c r="AO9" s="277"/>
+      <c r="AP9" s="277"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -21908,11 +22001,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="266"/>
-      <c r="AM10" s="266"/>
-      <c r="AN10" s="266"/>
-      <c r="AO10" s="266"/>
-      <c r="AP10" s="266"/>
+      <c r="AL10" s="277"/>
+      <c r="AM10" s="277"/>
+      <c r="AN10" s="277"/>
+      <c r="AO10" s="277"/>
+      <c r="AP10" s="277"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -21982,7 +22075,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="252" t="s">
+      <c r="V11" s="264" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -22004,7 +22097,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>13</v>
       </c>
-      <c r="AD11" s="252" t="s">
+      <c r="AD11" s="264" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -22118,7 +22211,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="253"/>
+      <c r="V12" s="265"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -22138,7 +22231,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>20</v>
       </c>
-      <c r="AD12" s="253"/>
+      <c r="AD12" s="265"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -22250,7 +22343,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="253"/>
+      <c r="V13" s="265"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -22270,7 +22363,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>7</v>
       </c>
-      <c r="AD13" s="253"/>
+      <c r="AD13" s="265"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -22358,7 +22451,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="254"/>
+      <c r="V14" s="266"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -22378,7 +22471,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>10</v>
       </c>
-      <c r="AD14" s="254"/>
+      <c r="AD14" s="266"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -27245,16 +27338,16 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="a7AHORGKHpMUjRkn5ERUm+ygSQ4XxlgmW0+c9l1HPGNWdceOfaHMTxam3gp7rwV50up4xOklDw6DgOSDy+jgQg==" saltValue="iSPclcrsv8KynPC2yADwnA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
+    <mergeCell ref="AL9:AP10"/>
+    <mergeCell ref="X9:AA9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="V11:V14"/>
+    <mergeCell ref="AD11:AD14"/>
     <mergeCell ref="V2:AR2"/>
     <mergeCell ref="V3:AR3"/>
     <mergeCell ref="V4:AR4"/>
     <mergeCell ref="V5:AR5"/>
     <mergeCell ref="V6:AR6"/>
-    <mergeCell ref="AL9:AP10"/>
-    <mergeCell ref="X9:AA9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="V11:V14"/>
-    <mergeCell ref="AD11:AD14"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B6:I13">
@@ -27404,44 +27497,44 @@
       <c r="S3" s="28"/>
       <c r="T3" s="28"/>
       <c r="U3" s="215"/>
-      <c r="W3" s="276" t="s">
+      <c r="W3" s="251" t="s">
         <v>86</v>
       </c>
-      <c r="X3" s="276"/>
-      <c r="Y3" s="278" t="s">
+      <c r="X3" s="251"/>
+      <c r="Y3" s="253" t="s">
         <v>89</v>
       </c>
-      <c r="Z3" s="278"/>
+      <c r="Z3" s="253"/>
     </row>
     <row r="4" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="284" t="s">
+      <c r="B4" s="243" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="287"/>
-      <c r="D4" s="287"/>
-      <c r="E4" s="287"/>
-      <c r="F4" s="287"/>
-      <c r="G4" s="287"/>
-      <c r="H4" s="287"/>
-      <c r="I4" s="287"/>
-      <c r="J4" s="287"/>
-      <c r="K4" s="287"/>
-      <c r="L4" s="287"/>
-      <c r="M4" s="287"/>
-      <c r="N4" s="287"/>
-      <c r="O4" s="287"/>
-      <c r="P4" s="287"/>
-      <c r="Q4" s="287"/>
-      <c r="R4" s="287"/>
-      <c r="S4" s="287"/>
-      <c r="T4" s="287"/>
-      <c r="U4" s="288"/>
-      <c r="W4" s="277" t="s">
+      <c r="C4" s="245"/>
+      <c r="D4" s="245"/>
+      <c r="E4" s="245"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
+      <c r="H4" s="245"/>
+      <c r="I4" s="245"/>
+      <c r="J4" s="245"/>
+      <c r="K4" s="245"/>
+      <c r="L4" s="245"/>
+      <c r="M4" s="245"/>
+      <c r="N4" s="245"/>
+      <c r="O4" s="245"/>
+      <c r="P4" s="245"/>
+      <c r="Q4" s="245"/>
+      <c r="R4" s="245"/>
+      <c r="S4" s="245"/>
+      <c r="T4" s="245"/>
+      <c r="U4" s="246"/>
+      <c r="W4" s="252" t="s">
         <v>87</v>
       </c>
-      <c r="X4" s="277"/>
-      <c r="Y4" s="278"/>
-      <c r="Z4" s="278"/>
+      <c r="X4" s="252"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AE4" t="s">
         <v>69</v>
       </c>
@@ -27547,28 +27640,28 @@
       </c>
     </row>
     <row r="7" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="285" t="s">
+      <c r="B7" s="244" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="289"/>
-      <c r="D7" s="289"/>
-      <c r="E7" s="289"/>
-      <c r="F7" s="289"/>
-      <c r="G7" s="289"/>
-      <c r="H7" s="289"/>
-      <c r="I7" s="289"/>
-      <c r="J7" s="289"/>
-      <c r="K7" s="289"/>
-      <c r="L7" s="289"/>
-      <c r="M7" s="289"/>
-      <c r="N7" s="289"/>
-      <c r="O7" s="289"/>
-      <c r="P7" s="289"/>
-      <c r="Q7" s="289"/>
-      <c r="R7" s="289"/>
-      <c r="S7" s="289"/>
-      <c r="T7" s="289"/>
-      <c r="U7" s="290"/>
+      <c r="C7" s="247"/>
+      <c r="D7" s="247"/>
+      <c r="E7" s="247"/>
+      <c r="F7" s="247"/>
+      <c r="G7" s="247"/>
+      <c r="H7" s="247"/>
+      <c r="I7" s="247"/>
+      <c r="J7" s="247"/>
+      <c r="K7" s="247"/>
+      <c r="L7" s="247"/>
+      <c r="M7" s="247"/>
+      <c r="N7" s="247"/>
+      <c r="O7" s="247"/>
+      <c r="P7" s="247"/>
+      <c r="Q7" s="247"/>
+      <c r="R7" s="247"/>
+      <c r="S7" s="247"/>
+      <c r="T7" s="247"/>
+      <c r="U7" s="248"/>
       <c r="W7" s="88" t="s">
         <v>30</v>
       </c>
@@ -27647,82 +27740,57 @@
       </c>
     </row>
     <row r="9" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="291"/>
-      <c r="C9" s="292"/>
-      <c r="D9" s="292"/>
-      <c r="E9" s="292"/>
-      <c r="F9" s="292"/>
-      <c r="G9" s="292"/>
-      <c r="H9" s="292"/>
-      <c r="I9" s="292"/>
-      <c r="J9" s="292"/>
-      <c r="K9" s="292"/>
-      <c r="L9" s="292"/>
-      <c r="M9" s="292"/>
-      <c r="N9" s="292"/>
-      <c r="O9" s="292"/>
-      <c r="P9" s="292"/>
-      <c r="Q9" s="292"/>
-      <c r="R9" s="292"/>
-      <c r="S9" s="292"/>
-      <c r="T9" s="292"/>
-      <c r="U9" s="292"/>
-      <c r="V9" s="293"/>
-      <c r="W9" s="292"/>
-      <c r="X9" s="295" t="s">
+      <c r="B9" s="249"/>
+      <c r="X9" s="250" t="s">
         <v>92</v>
       </c>
-      <c r="Y9" s="295" t="s">
+      <c r="Y9" s="250" t="s">
         <v>92</v>
       </c>
       <c r="Z9" s="216" t="s">
         <v>93</v>
       </c>
-      <c r="AA9" s="293"/>
-      <c r="AB9" s="293"/>
-      <c r="AC9" s="293"/>
-      <c r="AD9" s="293"/>
-      <c r="AE9" s="294"/>
-      <c r="AF9" s="294"/>
-      <c r="AG9" s="294"/>
-      <c r="AH9" s="294"/>
+      <c r="AE9" s="220"/>
+      <c r="AF9" s="220"/>
+      <c r="AG9" s="220"/>
+      <c r="AH9" s="220"/>
     </row>
     <row r="10" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="M10" s="286" t="s">
+      <c r="M10" s="253" t="s">
         <v>90</v>
       </c>
-      <c r="N10" s="286"/>
-      <c r="O10" s="286"/>
-      <c r="P10" s="286"/>
-      <c r="R10" s="278" t="s">
+      <c r="N10" s="253"/>
+      <c r="O10" s="253"/>
+      <c r="P10" s="253"/>
+      <c r="R10" s="253" t="s">
         <v>91</v>
       </c>
-      <c r="S10" s="278"/>
-      <c r="T10" s="278"/>
-      <c r="U10" s="278"/>
+      <c r="S10" s="253"/>
+      <c r="T10" s="253"/>
+      <c r="U10" s="253"/>
     </row>
     <row r="11" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J11" s="276" t="s">
+      <c r="J11" s="251" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="276"/>
-      <c r="L11" s="276"/>
-      <c r="M11" s="262"/>
-      <c r="N11" s="262"/>
-      <c r="O11" s="262"/>
-      <c r="P11" s="262"/>
-      <c r="R11" s="262"/>
-      <c r="S11" s="262"/>
-      <c r="T11" s="262"/>
-      <c r="U11" s="262"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
+      <c r="M11" s="254"/>
+      <c r="N11" s="254"/>
+      <c r="O11" s="254"/>
+      <c r="P11" s="254"/>
+      <c r="R11" s="254"/>
+      <c r="S11" s="254"/>
+      <c r="T11" s="254"/>
+      <c r="U11" s="254"/>
       <c r="X11" s="219"/>
       <c r="Y11" s="219"/>
-      <c r="AJ11" s="277" t="s">
+      <c r="AJ11" s="252" t="s">
         <v>81</v>
       </c>
-      <c r="AK11" s="277"/>
-      <c r="AL11" s="277"/>
-      <c r="AM11" s="277"/>
+      <c r="AK11" s="252"/>
+      <c r="AL11" s="252"/>
+      <c r="AM11" s="252"/>
     </row>
     <row r="12" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="J12" s="82">
@@ -27771,19 +27839,19 @@
       </c>
       <c r="Y12" s="219"/>
       <c r="AJ12" s="224">
-        <f>IF(R12=0,0,R12*LOG(R12,2))</f>
+        <f t="shared" ref="AJ12:AM15" si="0">IF(R12=0,0,R12*LOG(R12,2))</f>
         <v>-0.40105070315108637</v>
       </c>
       <c r="AK12" s="224">
-        <f>IF(S12=0,0,S12*LOG(S12,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.375</v>
       </c>
       <c r="AL12" s="224">
-        <f>IF(T12=0,0,T12*LOG(T12,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.20024226907010009</v>
       </c>
       <c r="AM12" s="224">
-        <f>IF(U12=0,0,U12*LOG(U12,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.17169124721634299</v>
       </c>
     </row>
@@ -27825,19 +27893,19 @@
       </c>
       <c r="Y13" s="219"/>
       <c r="AJ13" s="224">
-        <f>IF(R13=0,0,R13*LOG(R13,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.375</v>
       </c>
       <c r="AK13" s="224">
-        <f>IF(S13=0,0,S13*LOG(S13,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.46119922031470312</v>
       </c>
       <c r="AL13" s="224">
-        <f>IF(T13=0,0,T13*LOG(T13,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.13988551128579771</v>
       </c>
       <c r="AM13" s="224">
-        <f>IF(U13=0,0,U13*LOG(U13,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.22619959400016687</v>
       </c>
     </row>
@@ -27879,19 +27947,19 @@
       </c>
       <c r="Y14" s="219"/>
       <c r="AJ14" s="224">
-        <f>IF(R14=0,0,R14*LOG(R14,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.20024226907010009</v>
       </c>
       <c r="AK14" s="224">
-        <f>IF(S14=0,0,S14*LOG(S14,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.13988551128579771</v>
       </c>
       <c r="AL14" s="224">
-        <f>IF(T14=0,0,T14*LOG(T14,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.17169124721634299</v>
       </c>
       <c r="AM14" s="224">
-        <f>IF(U14=0,0,U14*LOG(U14,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.10370276646531436</v>
       </c>
     </row>
@@ -27933,19 +28001,19 @@
       </c>
       <c r="Y15" s="219"/>
       <c r="AJ15" s="224">
-        <f>IF(R15=0,0,R15*LOG(R15,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.17169124721634299</v>
       </c>
       <c r="AK15" s="224">
-        <f>IF(S15=0,0,S15*LOG(S15,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.22619959400016687</v>
       </c>
       <c r="AL15" s="224">
-        <f>IF(T15=0,0,T15*LOG(T15,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.10370276646531436</v>
       </c>
       <c r="AM15" s="224">
-        <f>IF(U15=0,0,U15*LOG(U15,2))</f>
+        <f t="shared" si="0"/>
         <v>-0.10370276646531436</v>
       </c>
     </row>
@@ -28012,19 +28080,19 @@
       </c>
       <c r="Y17" s="219"/>
       <c r="AJ17" s="227">
-        <f>IF(R17=0,0,R17*LOG(R17,2))</f>
+        <f t="shared" ref="AJ17:AM20" si="1">IF(R17=0,0,R17*LOG(R17,2))</f>
         <v>-0.24671922510575831</v>
       </c>
       <c r="AK17" s="227">
-        <f>IF(S17=0,0,S17*LOG(S17,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.42689140312085033</v>
       </c>
       <c r="AL17" s="227">
-        <f>IF(T17=0,0,T17*LOG(T17,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.24671922510575831</v>
       </c>
       <c r="AM17" s="227">
-        <f>IF(U17=0,0,U17*LOG(U17,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.21901947700142071</v>
       </c>
     </row>
@@ -28090,19 +28158,19 @@
       </c>
       <c r="Y18" s="219"/>
       <c r="AJ18" s="227">
-        <f>IF(R18=0,0,R18*LOG(R18,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.42689140312085033</v>
       </c>
       <c r="AK18" s="227">
-        <f>IF(S18=0,0,S18*LOG(S18,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.3709894706196798</v>
       </c>
       <c r="AL18" s="227">
-        <f>IF(T18=0,0,T18*LOG(T18,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.27195392300411458</v>
       </c>
       <c r="AM18" s="227">
-        <f>IF(U18=0,0,U18*LOG(U18,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.18835550384143707</v>
       </c>
     </row>
@@ -28168,19 +28236,19 @@
       </c>
       <c r="Y19" s="219"/>
       <c r="AJ19" s="227">
-        <f>IF(R19=0,0,R19*LOG(R19,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.24671922510575831</v>
       </c>
       <c r="AK19" s="227">
-        <f>IF(S19=0,0,S19*LOG(S19,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.27195392300411458</v>
       </c>
       <c r="AL19" s="227">
-        <f>IF(T19=0,0,T19*LOG(T19,2))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AM19" s="227">
-        <f>IF(U19=0,0,U19*LOG(U19,2))</f>
+        <f t="shared" si="1"/>
         <v>-6.7497039225665398E-2</v>
       </c>
     </row>
@@ -28246,19 +28314,19 @@
       </c>
       <c r="Y20" s="219"/>
       <c r="AJ20" s="227">
-        <f>IF(R20=0,0,R20*LOG(R20,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.21901947700142071</v>
       </c>
       <c r="AK20" s="227">
-        <f>IF(S20=0,0,S20*LOG(S20,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.18835550384143707</v>
       </c>
       <c r="AL20" s="227">
-        <f>IF(T20=0,0,T20*LOG(T20,2))</f>
+        <f t="shared" si="1"/>
         <v>-6.7497039225665398E-2</v>
       </c>
       <c r="AM20" s="227">
-        <f>IF(U20=0,0,U20*LOG(U20,2))</f>
+        <f t="shared" si="1"/>
         <v>-0.11458591518602466</v>
       </c>
     </row>
@@ -28385,19 +28453,19 @@
         <v>13</v>
       </c>
       <c r="AJ22" s="236">
-        <f>IF(R22=0,0,R22*LOG(R22,2))</f>
+        <f t="shared" ref="AJ22:AM25" si="2">IF(R22=0,0,R22*LOG(R22,2))</f>
         <v>-0.375</v>
       </c>
       <c r="AK22" s="236">
-        <f>IF(S22=0,0,S22*LOG(S22,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.42387266581317196</v>
       </c>
       <c r="AL22" s="236">
-        <f>IF(T22=0,0,T22*LOG(T22,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.29229347576372883</v>
       </c>
       <c r="AM22" s="236">
-        <f>IF(U22=0,0,U22*LOG(U22,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.10370276646531436</v>
       </c>
     </row>
@@ -28475,19 +28543,19 @@
         <v>20</v>
       </c>
       <c r="AJ23" s="236">
-        <f>IF(R23=0,0,R23*LOG(R23,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.42387266581317196</v>
       </c>
       <c r="AK23" s="236">
-        <f>IF(S23=0,0,S23*LOG(S23,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.34525633085747659</v>
       </c>
       <c r="AL23" s="236">
-        <f>IF(T23=0,0,T23*LOG(T23,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.20024226907010009</v>
       </c>
       <c r="AM23" s="236">
-        <f>IF(U23=0,0,U23*LOG(U23,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
     </row>
@@ -28565,19 +28633,19 @@
         <v>7</v>
       </c>
       <c r="AJ24" s="236">
-        <f>IF(R24=0,0,R24*LOG(R24,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.29229347576372883</v>
       </c>
       <c r="AK24" s="236">
-        <f>IF(S24=0,0,S24*LOG(S24,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.20024226907010009</v>
       </c>
       <c r="AL24" s="236">
-        <f>IF(T24=0,0,T24*LOG(T24,2))</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AM24" s="236">
-        <f>IF(U24=0,0,U24*LOG(U24,2))</f>
+        <f t="shared" si="2"/>
         <v>-6.0779954661228604E-2</v>
       </c>
     </row>
@@ -28655,19 +28723,19 @@
         <v>10</v>
       </c>
       <c r="AJ25" s="236">
-        <f>IF(R25=0,0,R25*LOG(R25,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.10370276646531436</v>
       </c>
       <c r="AK25" s="236">
-        <f>IF(S25=0,0,S25*LOG(S25,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.25</v>
       </c>
       <c r="AL25" s="236">
-        <f>IF(T25=0,0,T25*LOG(T25,2))</f>
+        <f t="shared" si="2"/>
         <v>-6.0779954661228604E-2</v>
       </c>
       <c r="AM25" s="236">
-        <f>IF(U25=0,0,U25*LOG(U25,2))</f>
+        <f t="shared" si="2"/>
         <v>-0.10370276646531436</v>
       </c>
     </row>
@@ -28731,19 +28799,19 @@
       </c>
       <c r="Y27" s="219"/>
       <c r="AJ27" s="231">
-        <f>IF(R27=0,0,R27*LOG(R27,2))</f>
+        <f t="shared" ref="AJ27:AM30" si="3">IF(R27=0,0,R27*LOG(R27,2))</f>
         <v>-0.40105070315108637</v>
       </c>
       <c r="AK27" s="231">
-        <f>IF(S27=0,0,S27*LOG(S27,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.3709894706196798</v>
       </c>
       <c r="AL27" s="231">
-        <f>IF(T27=0,0,T27*LOG(T27,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.24671922510575831</v>
       </c>
       <c r="AM27" s="231">
-        <f>IF(U27=0,0,U27*LOG(U27,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.11458591518602466</v>
       </c>
     </row>
@@ -28784,19 +28852,19 @@
       </c>
       <c r="Y28" s="219"/>
       <c r="AJ28" s="231">
-        <f>IF(R28=0,0,R28*LOG(R28,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.3709894706196798</v>
       </c>
       <c r="AK28" s="231">
-        <f>IF(S28=0,0,S28*LOG(S28,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.46791464269956046</v>
       </c>
       <c r="AL28" s="231">
-        <f>IF(T28=0,0,T28*LOG(T28,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.18835550384143707</v>
       </c>
       <c r="AM28" s="231">
-        <f>IF(U28=0,0,U28*LOG(U28,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.15397185745083833</v>
       </c>
     </row>
@@ -28837,19 +28905,19 @@
       </c>
       <c r="Y29" s="219"/>
       <c r="AJ29" s="231">
-        <f>IF(R29=0,0,R29*LOG(R29,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.24671922510575831</v>
       </c>
       <c r="AK29" s="231">
-        <f>IF(S29=0,0,S29*LOG(S29,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.18835550384143707</v>
       </c>
       <c r="AL29" s="231">
-        <f>IF(T29=0,0,T29*LOG(T29,2))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="AM29" s="231">
-        <f>IF(U29=0,0,U29*LOG(U29,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.15397185745083833</v>
       </c>
     </row>
@@ -28890,24 +28958,24 @@
       </c>
       <c r="Y30" s="219"/>
       <c r="AJ30" s="231">
-        <f>IF(R30=0,0,R30*LOG(R30,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.11458591518602466</v>
       </c>
       <c r="AK30" s="231">
-        <f>IF(S30=0,0,S30*LOG(S30,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.15397185745083833</v>
       </c>
       <c r="AL30" s="231">
-        <f>IF(T30=0,0,T30*LOG(T30,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.15397185745083833</v>
       </c>
       <c r="AM30" s="231">
-        <f>IF(U30=0,0,U30*LOG(U30,2))</f>
+        <f t="shared" si="3"/>
         <v>-0.18835550384143707</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="oA3Ug/9KfCFFrluaq9yww6YJp2pz1n+dPILndlP8AdPhVJ80NCrLDMxWTXyatNUo4xnnw0nFdMZ/i7RVucmlgw==" saltValue="LqPx3UPsolM2bW3uxHWqDw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="eid3QjEvP9P3RAZ+HGyMrnh+frY0qO+PHPMapaSCn/D/UGasX9GQYlPv6mYncUsizlxe04N+cCnpzYe1E9yn3w==" saltValue="Qjoxmnv8NKNqkdBgATyUZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="W3:X3"/>
@@ -29037,13 +29105,13 @@
       <c r="R4" s="16"/>
       <c r="S4" s="16"/>
       <c r="T4" s="16"/>
-      <c r="X4" s="279" t="s">
+      <c r="X4" s="287" t="s">
         <v>34</v>
       </c>
-      <c r="Y4" s="279"/>
-      <c r="Z4" s="279"/>
-      <c r="AA4" s="279"/>
-      <c r="AB4" s="279"/>
+      <c r="Y4" s="287"/>
+      <c r="Z4" s="287"/>
+      <c r="AA4" s="287"/>
+      <c r="AB4" s="287"/>
     </row>
     <row r="5" spans="1:39" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -30811,16 +30879,16 @@
       </c>
       <c r="AB32" s="111"/>
       <c r="AC32" s="111"/>
-      <c r="AD32" s="282" t="s">
+      <c r="AD32" s="290" t="s">
         <v>45</v>
       </c>
-      <c r="AE32" s="282"/>
-      <c r="AF32" s="282"/>
-      <c r="AG32" s="282"/>
-      <c r="AH32" s="282"/>
-      <c r="AI32" s="282"/>
-      <c r="AJ32" s="282"/>
-      <c r="AK32" s="282"/>
+      <c r="AE32" s="290"/>
+      <c r="AF32" s="290"/>
+      <c r="AG32" s="290"/>
+      <c r="AH32" s="290"/>
+      <c r="AI32" s="290"/>
+      <c r="AJ32" s="290"/>
+      <c r="AK32" s="290"/>
     </row>
     <row r="33" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
@@ -30837,16 +30905,16 @@
       <c r="AE33" s="182">
         <v>1</v>
       </c>
-      <c r="AF33" s="280">
-        <v>2</v>
-      </c>
-      <c r="AG33" s="280"/>
-      <c r="AH33" s="280">
+      <c r="AF33" s="288">
+        <v>2</v>
+      </c>
+      <c r="AG33" s="288"/>
+      <c r="AH33" s="288">
         <v>4</v>
       </c>
-      <c r="AI33" s="280"/>
-      <c r="AJ33" s="280"/>
-      <c r="AK33" s="280"/>
+      <c r="AI33" s="288"/>
+      <c r="AJ33" s="288"/>
+      <c r="AK33" s="288"/>
     </row>
     <row r="34" spans="2:37" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B34" s="167">
@@ -30913,7 +30981,7 @@
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="AB34" s="281" t="s">
+      <c r="AB34" s="289" t="s">
         <v>46</v>
       </c>
       <c r="AC34" s="181">
@@ -30993,7 +31061,7 @@
         <f t="shared" si="34"/>
         <v>16</v>
       </c>
-      <c r="AB35" s="281"/>
+      <c r="AB35" s="289"/>
       <c r="AC35" s="181">
         <v>1</v>
       </c>
@@ -31071,8 +31139,8 @@
         <f t="shared" si="36"/>
         <v>16</v>
       </c>
-      <c r="AB36" s="281"/>
-      <c r="AC36" s="283">
+      <c r="AB36" s="289"/>
+      <c r="AC36" s="291">
         <v>2</v>
       </c>
       <c r="AD36" s="186"/>
@@ -31149,8 +31217,8 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AB37" s="281"/>
-      <c r="AC37" s="283"/>
+      <c r="AB37" s="289"/>
+      <c r="AC37" s="291"/>
       <c r="AD37" s="187"/>
       <c r="AE37" s="191"/>
       <c r="AF37" s="199"/>
@@ -31225,8 +31293,8 @@
         <f t="shared" si="40"/>
         <v>-16</v>
       </c>
-      <c r="AB38" s="281"/>
-      <c r="AC38" s="283">
+      <c r="AB38" s="289"/>
+      <c r="AC38" s="291">
         <v>4</v>
       </c>
       <c r="AD38" s="186"/>
@@ -31303,8 +31371,8 @@
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="AB39" s="281"/>
-      <c r="AC39" s="283"/>
+      <c r="AB39" s="289"/>
+      <c r="AC39" s="291"/>
       <c r="AD39" s="188"/>
       <c r="AE39" s="174"/>
       <c r="AF39" s="174"/>
@@ -31379,8 +31447,8 @@
         <f t="shared" si="44"/>
         <v>0</v>
       </c>
-      <c r="AB40" s="281"/>
-      <c r="AC40" s="283"/>
+      <c r="AB40" s="289"/>
+      <c r="AC40" s="291"/>
       <c r="AD40" s="188"/>
       <c r="AE40" s="174"/>
       <c r="AF40" s="174"/>
@@ -31455,8 +31523,8 @@
         <f t="shared" si="46"/>
         <v>16</v>
       </c>
-      <c r="AB41" s="281"/>
-      <c r="AC41" s="283"/>
+      <c r="AB41" s="289"/>
+      <c r="AC41" s="291"/>
       <c r="AD41" s="187"/>
       <c r="AE41" s="175"/>
       <c r="AF41" s="175"/>
@@ -31515,12 +31583,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -31714,15 +31779,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2764B03-5387-4537-A949-7B2C7AF6C83E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E7E2A7-086F-4414-A818-C355190A2115}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="564c14fb-bfcd-4e52-83e8-2447e9c77f65"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -31747,17 +31823,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E7E2A7-086F-4414-A818-C355190A2115}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2764B03-5387-4537-A949-7B2C7AF6C83E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="564c14fb-bfcd-4e52-83e8-2447e9c77f65"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/Convolution-Radiomics-Wavelet.xlsx
+++ b/Convolution-Radiomics-Wavelet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HN-Data-1\教育\講義\講義2年生-AI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E54CF36-1B8D-48A9-8E0D-CCB2C13C80A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5252050F-C7BB-4C43-AA81-81DD514B3251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
+    <workbookView xWindow="31050" yWindow="525" windowWidth="25560" windowHeight="12930" xr2:uid="{EB08A484-005D-4F71-B2D3-681DCA114F4E}"/>
   </bookViews>
   <sheets>
     <sheet name="目次" sheetId="11" r:id="rId1"/>
@@ -2924,7 +2924,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="292">
+  <cellXfs count="293">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3706,18 +3706,6 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3775,6 +3763,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3786,6 +3777,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="44" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3805,14 +3805,14 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3828,6 +3828,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7020,6 +7023,7 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="4" customWidth="1"/>
+    <col min="3" max="3" width="104.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.15">
@@ -7073,12 +7077,16 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="B11" s="241" t="s">
+      <c r="B11" s="292" t="s">
         <v>105</v>
       </c>
+      <c r="C11" s="292"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Oh/wyZBJM5QXqBYt/YMfLyL775haBs3z05CTY8EsL5+tBU3eVRuXMx35sIFjv+Ro+u7B8n+9aqyMZz5VtnOmng==" saltValue="tfBPuFgM89XraVHWdEg+jQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="hQDTGQKX1hMpGwJCNMRzggyhRh8k+RqU75oWEIqxM8C2T4T+zZlKuT9gNJSfLFD7+0IMhEsKJG85+1NFsjCGSA==" saltValue="VK8ieTWbVIa/Lg53Rb/yaA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="B11:C11"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="C4" location="演習・確認用!A1" display="演習・確認用" xr:uid="{05CA92A6-2BA4-4345-812D-B9966056781D}"/>
@@ -7902,14 +7910,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="255" t="s">
+      <c r="X15" s="251" t="s">
         <v>19</v>
       </c>
-      <c r="Y15" s="256"/>
-      <c r="Z15" s="256"/>
-      <c r="AA15" s="256"/>
-      <c r="AB15" s="256"/>
-      <c r="AC15" s="257"/>
+      <c r="Y15" s="252"/>
+      <c r="Z15" s="252"/>
+      <c r="AA15" s="252"/>
+      <c r="AB15" s="252"/>
+      <c r="AC15" s="253"/>
     </row>
     <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -7955,12 +7963,12 @@
       <c r="Q16" s="49"/>
       <c r="R16" s="49"/>
       <c r="S16" s="49"/>
-      <c r="X16" s="258"/>
-      <c r="Y16" s="259"/>
-      <c r="Z16" s="259"/>
-      <c r="AA16" s="259"/>
-      <c r="AB16" s="259"/>
-      <c r="AC16" s="260"/>
+      <c r="X16" s="254"/>
+      <c r="Y16" s="255"/>
+      <c r="Z16" s="255"/>
+      <c r="AA16" s="255"/>
+      <c r="AB16" s="255"/>
+      <c r="AC16" s="256"/>
     </row>
     <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -8003,12 +8011,12 @@
       <c r="Q17" s="49"/>
       <c r="R17" s="49"/>
       <c r="S17" s="49"/>
-      <c r="X17" s="258"/>
-      <c r="Y17" s="259"/>
-      <c r="Z17" s="259"/>
-      <c r="AA17" s="259"/>
-      <c r="AB17" s="259"/>
-      <c r="AC17" s="260"/>
+      <c r="X17" s="254"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
+      <c r="AA17" s="255"/>
+      <c r="AB17" s="255"/>
+      <c r="AC17" s="256"/>
     </row>
     <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
@@ -8051,12 +8059,12 @@
       <c r="Q18" s="49"/>
       <c r="R18" s="49"/>
       <c r="S18" s="49"/>
-      <c r="X18" s="258"/>
-      <c r="Y18" s="259"/>
-      <c r="Z18" s="259"/>
-      <c r="AA18" s="259"/>
-      <c r="AB18" s="259"/>
-      <c r="AC18" s="260"/>
+      <c r="X18" s="254"/>
+      <c r="Y18" s="255"/>
+      <c r="Z18" s="255"/>
+      <c r="AA18" s="255"/>
+      <c r="AB18" s="255"/>
+      <c r="AC18" s="256"/>
     </row>
     <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -8099,12 +8107,12 @@
       <c r="Q19" s="49"/>
       <c r="R19" s="49"/>
       <c r="S19" s="49"/>
-      <c r="X19" s="258"/>
-      <c r="Y19" s="259"/>
-      <c r="Z19" s="259"/>
-      <c r="AA19" s="259"/>
-      <c r="AB19" s="259"/>
-      <c r="AC19" s="260"/>
+      <c r="X19" s="254"/>
+      <c r="Y19" s="255"/>
+      <c r="Z19" s="255"/>
+      <c r="AA19" s="255"/>
+      <c r="AB19" s="255"/>
+      <c r="AC19" s="256"/>
     </row>
     <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
@@ -8147,12 +8155,12 @@
       <c r="Q20" s="49"/>
       <c r="R20" s="49"/>
       <c r="S20" s="49"/>
-      <c r="X20" s="258"/>
-      <c r="Y20" s="259"/>
-      <c r="Z20" s="259"/>
-      <c r="AA20" s="259"/>
-      <c r="AB20" s="259"/>
-      <c r="AC20" s="260"/>
+      <c r="X20" s="254"/>
+      <c r="Y20" s="255"/>
+      <c r="Z20" s="255"/>
+      <c r="AA20" s="255"/>
+      <c r="AB20" s="255"/>
+      <c r="AC20" s="256"/>
     </row>
     <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
@@ -8195,12 +8203,12 @@
       <c r="Q21" s="49"/>
       <c r="R21" s="49"/>
       <c r="S21" s="49"/>
-      <c r="X21" s="258"/>
-      <c r="Y21" s="259"/>
-      <c r="Z21" s="259"/>
-      <c r="AA21" s="259"/>
-      <c r="AB21" s="259"/>
-      <c r="AC21" s="260"/>
+      <c r="X21" s="254"/>
+      <c r="Y21" s="255"/>
+      <c r="Z21" s="255"/>
+      <c r="AA21" s="255"/>
+      <c r="AB21" s="255"/>
+      <c r="AC21" s="256"/>
     </row>
     <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -8243,12 +8251,12 @@
       <c r="Q22" s="49"/>
       <c r="R22" s="49"/>
       <c r="S22" s="49"/>
-      <c r="X22" s="258"/>
-      <c r="Y22" s="259"/>
-      <c r="Z22" s="259"/>
-      <c r="AA22" s="259"/>
-      <c r="AB22" s="259"/>
-      <c r="AC22" s="260"/>
+      <c r="X22" s="254"/>
+      <c r="Y22" s="255"/>
+      <c r="Z22" s="255"/>
+      <c r="AA22" s="255"/>
+      <c r="AB22" s="255"/>
+      <c r="AC22" s="256"/>
     </row>
     <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
@@ -8291,12 +8299,12 @@
       <c r="Q23" s="49"/>
       <c r="R23" s="49"/>
       <c r="S23" s="49"/>
-      <c r="X23" s="261"/>
-      <c r="Y23" s="262"/>
-      <c r="Z23" s="262"/>
-      <c r="AA23" s="262"/>
-      <c r="AB23" s="262"/>
-      <c r="AC23" s="263"/>
+      <c r="X23" s="257"/>
+      <c r="Y23" s="258"/>
+      <c r="Z23" s="258"/>
+      <c r="AA23" s="258"/>
+      <c r="AB23" s="258"/>
+      <c r="AC23" s="259"/>
     </row>
     <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
@@ -8361,7 +8369,7 @@
       <c r="T26" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="fIi+k+lZSlZlCe8Mpm4Q1EVKURkOiLcEuXVMi8MDxFodCOJp3+nhf9lRp9zx64FA07N4JqFSApH0RVJMu61xxw==" saltValue="evwvXr8s1QUaE0EwvEhnfA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="k4e76ZCuJbuFxu0m5oVz6hIOtjFbxCWa/44zc8j0zwb5y4iQFKAV3VP5mlsCE+/D1xT8Waocq6REFPprK8kQWg==" saltValue="54yeJly7NbeBhx9GXkAsZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="X15:AC23"/>
   </mergeCells>
@@ -8383,7 +8391,7 @@
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4 X5:Z7" xr:uid="{6A031A24-5A5F-4B42-99F6-700F8AD4C680}"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{F986BA72-0D76-4699-9051-CF4AA1B9A1ED}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{F986BA72-0D76-4699-9051-CF4AA1B9A1ED}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9200,14 +9208,14 @@
       <c r="K15" t="s">
         <v>18</v>
       </c>
-      <c r="X15" s="255" t="s">
+      <c r="X15" s="251" t="s">
         <v>23</v>
       </c>
-      <c r="Y15" s="256"/>
-      <c r="Z15" s="256"/>
-      <c r="AA15" s="256"/>
-      <c r="AB15" s="256"/>
-      <c r="AC15" s="257"/>
+      <c r="Y15" s="252"/>
+      <c r="Z15" s="252"/>
+      <c r="AA15" s="252"/>
+      <c r="AB15" s="252"/>
+      <c r="AC15" s="253"/>
     </row>
     <row r="16" spans="1:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1">
@@ -9274,12 +9282,12 @@
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="X16" s="258"/>
-      <c r="Y16" s="259"/>
-      <c r="Z16" s="259"/>
-      <c r="AA16" s="259"/>
-      <c r="AB16" s="259"/>
-      <c r="AC16" s="260"/>
+      <c r="X16" s="254"/>
+      <c r="Y16" s="255"/>
+      <c r="Z16" s="255"/>
+      <c r="AA16" s="255"/>
+      <c r="AB16" s="255"/>
+      <c r="AC16" s="256"/>
     </row>
     <row r="17" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
@@ -9346,12 +9354,12 @@
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="X17" s="258"/>
-      <c r="Y17" s="259"/>
-      <c r="Z17" s="259"/>
-      <c r="AA17" s="259"/>
-      <c r="AB17" s="259"/>
-      <c r="AC17" s="260"/>
+      <c r="X17" s="254"/>
+      <c r="Y17" s="255"/>
+      <c r="Z17" s="255"/>
+      <c r="AA17" s="255"/>
+      <c r="AB17" s="255"/>
+      <c r="AC17" s="256"/>
     </row>
     <row r="18" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
@@ -9418,12 +9426,12 @@
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="X18" s="258"/>
-      <c r="Y18" s="259"/>
-      <c r="Z18" s="259"/>
-      <c r="AA18" s="259"/>
-      <c r="AB18" s="259"/>
-      <c r="AC18" s="260"/>
+      <c r="X18" s="254"/>
+      <c r="Y18" s="255"/>
+      <c r="Z18" s="255"/>
+      <c r="AA18" s="255"/>
+      <c r="AB18" s="255"/>
+      <c r="AC18" s="256"/>
     </row>
     <row r="19" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
@@ -9490,12 +9498,12 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="X19" s="258"/>
-      <c r="Y19" s="259"/>
-      <c r="Z19" s="259"/>
-      <c r="AA19" s="259"/>
-      <c r="AB19" s="259"/>
-      <c r="AC19" s="260"/>
+      <c r="X19" s="254"/>
+      <c r="Y19" s="255"/>
+      <c r="Z19" s="255"/>
+      <c r="AA19" s="255"/>
+      <c r="AB19" s="255"/>
+      <c r="AC19" s="256"/>
     </row>
     <row r="20" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
@@ -9562,12 +9570,12 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="X20" s="258"/>
-      <c r="Y20" s="259"/>
-      <c r="Z20" s="259"/>
-      <c r="AA20" s="259"/>
-      <c r="AB20" s="259"/>
-      <c r="AC20" s="260"/>
+      <c r="X20" s="254"/>
+      <c r="Y20" s="255"/>
+      <c r="Z20" s="255"/>
+      <c r="AA20" s="255"/>
+      <c r="AB20" s="255"/>
+      <c r="AC20" s="256"/>
     </row>
     <row r="21" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
@@ -9634,12 +9642,12 @@
         <f t="shared" si="11"/>
         <v>1</v>
       </c>
-      <c r="X21" s="258"/>
-      <c r="Y21" s="259"/>
-      <c r="Z21" s="259"/>
-      <c r="AA21" s="259"/>
-      <c r="AB21" s="259"/>
-      <c r="AC21" s="260"/>
+      <c r="X21" s="254"/>
+      <c r="Y21" s="255"/>
+      <c r="Z21" s="255"/>
+      <c r="AA21" s="255"/>
+      <c r="AB21" s="255"/>
+      <c r="AC21" s="256"/>
     </row>
     <row r="22" spans="2:29" ht="24" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
@@ -9706,12 +9714,12 @@
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="X22" s="258"/>
-      <c r="Y22" s="259"/>
-      <c r="Z22" s="259"/>
-      <c r="AA22" s="259"/>
-      <c r="AB22" s="259"/>
-      <c r="AC22" s="260"/>
+      <c r="X22" s="254"/>
+      <c r="Y22" s="255"/>
+      <c r="Z22" s="255"/>
+      <c r="AA22" s="255"/>
+      <c r="AB22" s="255"/>
+      <c r="AC22" s="256"/>
     </row>
     <row r="23" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B23" s="1">
@@ -9778,12 +9786,12 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="X23" s="261"/>
-      <c r="Y23" s="262"/>
-      <c r="Z23" s="262"/>
-      <c r="AA23" s="262"/>
-      <c r="AB23" s="262"/>
-      <c r="AC23" s="263"/>
+      <c r="X23" s="257"/>
+      <c r="Y23" s="258"/>
+      <c r="Z23" s="258"/>
+      <c r="AA23" s="258"/>
+      <c r="AB23" s="258"/>
+      <c r="AC23" s="259"/>
     </row>
     <row r="24" spans="2:29" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="L24" s="8"/>
@@ -9848,7 +9856,7 @@
       <c r="T26" s="46"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="VXMW/twfHXicmEDIUix0D6fJ0gg6vg+N/TjfvpzAMWPVPr2ueyKFuai5Vp+EkqDiF2ocvNBAscZaPDmYbW6AaA==" saltValue="7yumMwkox+k8ZKk7NTzNuA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="HVUIO1V59FS3HXBioKlCopoaIeefzJON1b0yJRNQMDFnH/sJz2zG+O5B9MTW6CDY/JxMO4V0hRUxTvIUudxPSQ==" saltValue="OB4cRk+v/76M7QwZFvk3+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="X15:AC23"/>
   </mergeCells>
@@ -9870,7 +9878,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{65477C5D-5CC2-4E38-84F4-C2C9DFDE1204}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{21E31FC4-9453-47F1-8652-81F8A8DA7FF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -10254,25 +10262,25 @@
         <v>1</v>
       </c>
       <c r="T9" s="20"/>
-      <c r="X9" s="267" t="s">
+      <c r="X9" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
-      <c r="AA9" s="269"/>
-      <c r="AF9" s="267" t="s">
+      <c r="Y9" s="264"/>
+      <c r="Z9" s="264"/>
+      <c r="AA9" s="265"/>
+      <c r="AF9" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="268"/>
-      <c r="AH9" s="268"/>
-      <c r="AI9" s="269"/>
-      <c r="AL9" s="270" t="s">
+      <c r="AG9" s="264"/>
+      <c r="AH9" s="264"/>
+      <c r="AI9" s="265"/>
+      <c r="AL9" s="266" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="271"/>
-      <c r="AN9" s="271"/>
-      <c r="AO9" s="271"/>
-      <c r="AP9" s="272"/>
+      <c r="AM9" s="267"/>
+      <c r="AN9" s="267"/>
+      <c r="AO9" s="267"/>
+      <c r="AP9" s="268"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -10357,11 +10365,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="273"/>
-      <c r="AM10" s="254"/>
-      <c r="AN10" s="254"/>
-      <c r="AO10" s="254"/>
-      <c r="AP10" s="274"/>
+      <c r="AL10" s="269"/>
+      <c r="AM10" s="270"/>
+      <c r="AN10" s="270"/>
+      <c r="AO10" s="270"/>
+      <c r="AP10" s="271"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -10425,7 +10433,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="20"/>
-      <c r="V11" s="264" t="s">
+      <c r="V11" s="260" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -10447,7 +10455,7 @@
         <f>SUM(AC17:AI24)</f>
         <v>1</v>
       </c>
-      <c r="AD11" s="264" t="s">
+      <c r="AD11" s="260" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -10555,7 +10563,7 @@
         <v>3</v>
       </c>
       <c r="T12" s="20"/>
-      <c r="V12" s="265"/>
+      <c r="V12" s="261"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -10575,7 +10583,7 @@
         <f>SUM(AC27:AI34)</f>
         <v>4</v>
       </c>
-      <c r="AD12" s="265"/>
+      <c r="AD12" s="261"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -10681,7 +10689,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="20"/>
-      <c r="V13" s="265"/>
+      <c r="V13" s="261"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -10701,7 +10709,7 @@
         <f>SUM(AC37:AI44)</f>
         <v>1</v>
       </c>
-      <c r="AD13" s="265"/>
+      <c r="AD13" s="261"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -10759,7 +10767,7 @@
       <c r="R14" s="20"/>
       <c r="S14" s="20"/>
       <c r="T14" s="20"/>
-      <c r="V14" s="266"/>
+      <c r="V14" s="262"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -10779,7 +10787,7 @@
         <f>SUM(AC47:AI54)</f>
         <v>1</v>
       </c>
-      <c r="AD14" s="266"/>
+      <c r="AD14" s="262"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -15219,7 +15227,7 @@
       <c r="AJ55" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="D3cnX6YsrsqICfmB3pnBjFV6yS/VcPrGLKoDYeUPS+JJqTlpltiMLbavojwuBdamDitXX+orRoGKC2iyOFI/Eg==" saltValue="N0qYW7kzVVGJppr6k1Fnyw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="J5sA7RkA+OqzVnmjd2tS6vcNg7XdF+3jZM+guJNplWu1hsBzPEDbDpnbsie2w/HsmYNWUQBPPpdcDeNfOES9Hw==" saltValue="5SOYsLTXAhodbgs++3Vlpg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="5">
     <mergeCell ref="V11:V14"/>
     <mergeCell ref="AD11:AD14"/>
@@ -15269,7 +15277,7 @@
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4 Z3:Z4 AB3:AB4 AH3:AH4 AJ3:AJ4" xr:uid="{995BD10A-B62E-4A28-9BFA-BCA2ECCB985D}"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{50CA87CD-2A4A-4B8C-ADEB-70F4715E58AB}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{52447681-5A7D-463F-BEB5-A4E45CFF14B0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -15389,14 +15397,14 @@
         <v>0</v>
       </c>
       <c r="Z3" s="211"/>
-      <c r="AA3" s="276" t="s">
+      <c r="AA3" s="273" t="s">
         <v>72</v>
       </c>
-      <c r="AB3" s="276"/>
-      <c r="AC3" s="276"/>
-      <c r="AD3" s="276"/>
-      <c r="AE3" s="276"/>
-      <c r="AF3" s="276"/>
+      <c r="AB3" s="273"/>
+      <c r="AC3" s="273"/>
+      <c r="AD3" s="273"/>
+      <c r="AE3" s="273"/>
+      <c r="AF3" s="273"/>
     </row>
     <row r="4" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B4" s="28" t="s">
@@ -15446,24 +15454,24 @@
       <c r="Z4" s="211" t="s">
         <v>60</v>
       </c>
-      <c r="AA4" s="275" t="s">
+      <c r="AA4" s="272" t="s">
         <v>70</v>
       </c>
-      <c r="AB4" s="275"/>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="275"/>
-      <c r="AE4" s="275"/>
-      <c r="AF4" s="275"/>
-      <c r="AG4" s="275"/>
-      <c r="AH4" s="275"/>
-      <c r="AI4" s="275"/>
-      <c r="AJ4" s="275"/>
-      <c r="AK4" s="275"/>
-      <c r="AL4" s="275"/>
-      <c r="AM4" s="275"/>
-      <c r="AN4" s="275"/>
-      <c r="AO4" s="275"/>
-      <c r="AP4" s="275"/>
+      <c r="AB4" s="272"/>
+      <c r="AC4" s="272"/>
+      <c r="AD4" s="272"/>
+      <c r="AE4" s="272"/>
+      <c r="AF4" s="272"/>
+      <c r="AG4" s="272"/>
+      <c r="AH4" s="272"/>
+      <c r="AI4" s="272"/>
+      <c r="AJ4" s="272"/>
+      <c r="AK4" s="272"/>
+      <c r="AL4" s="272"/>
+      <c r="AM4" s="272"/>
+      <c r="AN4" s="272"/>
+      <c r="AO4" s="272"/>
+      <c r="AP4" s="272"/>
     </row>
     <row r="5" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -15816,25 +15824,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="267" t="s">
+      <c r="X9" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="268"/>
-      <c r="Z9" s="268"/>
-      <c r="AA9" s="269"/>
-      <c r="AF9" s="267" t="s">
+      <c r="Y9" s="264"/>
+      <c r="Z9" s="264"/>
+      <c r="AA9" s="265"/>
+      <c r="AF9" s="263" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="268"/>
-      <c r="AH9" s="268"/>
-      <c r="AI9" s="269"/>
-      <c r="AL9" s="277" t="s">
+      <c r="AG9" s="264"/>
+      <c r="AH9" s="264"/>
+      <c r="AI9" s="265"/>
+      <c r="AL9" s="274" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="277"/>
-      <c r="AN9" s="277"/>
-      <c r="AO9" s="277"/>
-      <c r="AP9" s="277"/>
+      <c r="AM9" s="274"/>
+      <c r="AN9" s="274"/>
+      <c r="AO9" s="274"/>
+      <c r="AP9" s="274"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -15925,11 +15933,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="277"/>
-      <c r="AM10" s="277"/>
-      <c r="AN10" s="277"/>
-      <c r="AO10" s="277"/>
-      <c r="AP10" s="277"/>
+      <c r="AL10" s="274"/>
+      <c r="AM10" s="274"/>
+      <c r="AN10" s="274"/>
+      <c r="AO10" s="274"/>
+      <c r="AP10" s="274"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -15999,7 +16007,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="264" t="s">
+      <c r="V11" s="260" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -16021,7 +16029,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>4</v>
       </c>
-      <c r="AD11" s="264" t="s">
+      <c r="AD11" s="260" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -16135,7 +16143,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="265"/>
+      <c r="V12" s="261"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -16155,7 +16163,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>6</v>
       </c>
-      <c r="AD12" s="265"/>
+      <c r="AD12" s="261"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -16267,7 +16275,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="265"/>
+      <c r="V13" s="261"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -16287,7 +16295,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>2</v>
       </c>
-      <c r="AD13" s="265"/>
+      <c r="AD13" s="261"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -16375,7 +16383,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="266"/>
+      <c r="V14" s="262"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -16395,7 +16403,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>2</v>
       </c>
-      <c r="AD14" s="266"/>
+      <c r="AD14" s="262"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -21260,7 +21268,7 @@
       <c r="AK55" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="RMlVZshFWv7HKfGAhZCt1p2M0xKSbiW+fJE5WMYFeTaQ5Vz7ZYwiaX/ZAv2tLirdBbIa7AM33H0ks+h42utCBg==" saltValue="QchpNVrJa6YNLOdgVo/VKg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="s0Jca/d8TCvXuJ0z/JTMwQZiRF6+Xad3GbCs+0aoxfWdz6z1/ZLkiir27PC7aXIhA0VT8yuHYgm3r/WOQydqnQ==" saltValue="SQymzYS2YaCTKj+r7W6TCg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="AA4:AP4"/>
     <mergeCell ref="AA3:AF3"/>
@@ -21317,7 +21325,7 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{16E63979-D6EA-4719-95E7-99D2241FE87A}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{2919B750-5E2A-41DD-BFD7-F4850132DBC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -21892,25 +21900,25 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X9" s="284" t="s">
+      <c r="X9" s="275" t="s">
         <v>26</v>
       </c>
-      <c r="Y9" s="285"/>
-      <c r="Z9" s="285"/>
-      <c r="AA9" s="286"/>
-      <c r="AF9" s="284" t="s">
+      <c r="Y9" s="276"/>
+      <c r="Z9" s="276"/>
+      <c r="AA9" s="277"/>
+      <c r="AF9" s="275" t="s">
         <v>26</v>
       </c>
-      <c r="AG9" s="285"/>
-      <c r="AH9" s="285"/>
-      <c r="AI9" s="286"/>
-      <c r="AL9" s="277" t="s">
+      <c r="AG9" s="276"/>
+      <c r="AH9" s="276"/>
+      <c r="AI9" s="277"/>
+      <c r="AL9" s="274" t="s">
         <v>57</v>
       </c>
-      <c r="AM9" s="277"/>
-      <c r="AN9" s="277"/>
-      <c r="AO9" s="277"/>
-      <c r="AP9" s="277"/>
+      <c r="AM9" s="274"/>
+      <c r="AN9" s="274"/>
+      <c r="AO9" s="274"/>
+      <c r="AP9" s="274"/>
     </row>
     <row r="10" spans="1:47" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B10" s="1">
@@ -22001,11 +22009,11 @@
       <c r="AI10" s="64">
         <v>4</v>
       </c>
-      <c r="AL10" s="277"/>
-      <c r="AM10" s="277"/>
-      <c r="AN10" s="277"/>
-      <c r="AO10" s="277"/>
-      <c r="AP10" s="277"/>
+      <c r="AL10" s="274"/>
+      <c r="AM10" s="274"/>
+      <c r="AN10" s="274"/>
+      <c r="AO10" s="274"/>
+      <c r="AP10" s="274"/>
       <c r="AR10" t="s">
         <v>33</v>
       </c>
@@ -22075,7 +22083,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V11" s="264" t="s">
+      <c r="V11" s="260" t="s">
         <v>29</v>
       </c>
       <c r="W11" s="65">
@@ -22097,7 +22105,7 @@
         <f>SUM(AC17:AJ24)</f>
         <v>13</v>
       </c>
-      <c r="AD11" s="264" t="s">
+      <c r="AD11" s="260" t="s">
         <v>29</v>
       </c>
       <c r="AE11" s="68">
@@ -22211,7 +22219,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="265"/>
+      <c r="V12" s="261"/>
       <c r="W12" s="72">
         <v>2</v>
       </c>
@@ -22231,7 +22239,7 @@
         <f>SUM(AC27:AJ34)</f>
         <v>20</v>
       </c>
-      <c r="AD12" s="265"/>
+      <c r="AD12" s="261"/>
       <c r="AE12" s="74">
         <v>2</v>
       </c>
@@ -22343,7 +22351,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V13" s="265"/>
+      <c r="V13" s="261"/>
       <c r="W13" s="72">
         <v>3</v>
       </c>
@@ -22363,7 +22371,7 @@
         <f>SUM(AC37:AJ44)</f>
         <v>7</v>
       </c>
-      <c r="AD13" s="265"/>
+      <c r="AD13" s="261"/>
       <c r="AE13" s="74">
         <v>3</v>
       </c>
@@ -22451,7 +22459,7 @@
         <f>(S14+T13)/2</f>
         <v>0</v>
       </c>
-      <c r="V14" s="266"/>
+      <c r="V14" s="262"/>
       <c r="W14" s="61">
         <v>4</v>
       </c>
@@ -22471,7 +22479,7 @@
         <f>SUM(AC47:AJ54)</f>
         <v>10</v>
       </c>
-      <c r="AD14" s="266"/>
+      <c r="AD14" s="262"/>
       <c r="AE14" s="78">
         <v>4</v>
       </c>
@@ -27336,18 +27344,18 @@
       <c r="AK55" s="82"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="a7AHORGKHpMUjRkn5ERUm+ygSQ4XxlgmW0+c9l1HPGNWdceOfaHMTxam3gp7rwV50up4xOklDw6DgOSDy+jgQg==" saltValue="iSPclcrsv8KynPC2yADwnA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="EzaQwV4nM4/ygp//Q0trgfGMQQIf2gCT7ia+8Bmj8xl+RUsmjuNtX77XroC5G31kSM6Ah0cmybypnJSQg2kt5A==" saltValue="4E6TR+Q0mdz9HNZ4Zj7bwQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="10">
+    <mergeCell ref="V2:AR2"/>
+    <mergeCell ref="V3:AR3"/>
+    <mergeCell ref="V4:AR4"/>
+    <mergeCell ref="V5:AR5"/>
+    <mergeCell ref="V6:AR6"/>
     <mergeCell ref="AL9:AP10"/>
     <mergeCell ref="X9:AA9"/>
     <mergeCell ref="AF9:AI9"/>
     <mergeCell ref="V11:V14"/>
     <mergeCell ref="AD11:AD14"/>
-    <mergeCell ref="V2:AR2"/>
-    <mergeCell ref="V3:AR3"/>
-    <mergeCell ref="V4:AR4"/>
-    <mergeCell ref="V5:AR5"/>
-    <mergeCell ref="V6:AR6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="B6:I13">
@@ -27391,7 +27399,7 @@
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4" xr:uid="{A2F48F23-233F-48A9-98A5-1E3C3D47166C}"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{0418C76F-B20A-44ED-BA79-F6CE0CE443C8}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{ABA74DA1-C329-4EC7-8669-84034C0E2677}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -27497,14 +27505,14 @@
       <c r="S3" s="28"/>
       <c r="T3" s="28"/>
       <c r="U3" s="215"/>
-      <c r="W3" s="251" t="s">
+      <c r="W3" s="284" t="s">
         <v>86</v>
       </c>
-      <c r="X3" s="251"/>
-      <c r="Y3" s="253" t="s">
+      <c r="X3" s="284"/>
+      <c r="Y3" s="286" t="s">
         <v>89</v>
       </c>
-      <c r="Z3" s="253"/>
+      <c r="Z3" s="286"/>
     </row>
     <row r="4" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="243" t="s">
@@ -27529,12 +27537,12 @@
       <c r="S4" s="245"/>
       <c r="T4" s="245"/>
       <c r="U4" s="246"/>
-      <c r="W4" s="252" t="s">
+      <c r="W4" s="285" t="s">
         <v>87</v>
       </c>
-      <c r="X4" s="252"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
+      <c r="X4" s="285"/>
+      <c r="Y4" s="286"/>
+      <c r="Z4" s="286"/>
       <c r="AE4" t="s">
         <v>69</v>
       </c>
@@ -27756,41 +27764,41 @@
       <c r="AH9" s="220"/>
     </row>
     <row r="10" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="M10" s="253" t="s">
+      <c r="M10" s="286" t="s">
         <v>90</v>
       </c>
-      <c r="N10" s="253"/>
-      <c r="O10" s="253"/>
-      <c r="P10" s="253"/>
-      <c r="R10" s="253" t="s">
+      <c r="N10" s="286"/>
+      <c r="O10" s="286"/>
+      <c r="P10" s="286"/>
+      <c r="R10" s="286" t="s">
         <v>91</v>
       </c>
-      <c r="S10" s="253"/>
-      <c r="T10" s="253"/>
-      <c r="U10" s="253"/>
+      <c r="S10" s="286"/>
+      <c r="T10" s="286"/>
+      <c r="U10" s="286"/>
     </row>
     <row r="11" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J11" s="251" t="s">
+      <c r="J11" s="284" t="s">
         <v>82</v>
       </c>
-      <c r="K11" s="251"/>
-      <c r="L11" s="251"/>
-      <c r="M11" s="254"/>
-      <c r="N11" s="254"/>
-      <c r="O11" s="254"/>
-      <c r="P11" s="254"/>
-      <c r="R11" s="254"/>
-      <c r="S11" s="254"/>
-      <c r="T11" s="254"/>
-      <c r="U11" s="254"/>
+      <c r="K11" s="284"/>
+      <c r="L11" s="284"/>
+      <c r="M11" s="270"/>
+      <c r="N11" s="270"/>
+      <c r="O11" s="270"/>
+      <c r="P11" s="270"/>
+      <c r="R11" s="270"/>
+      <c r="S11" s="270"/>
+      <c r="T11" s="270"/>
+      <c r="U11" s="270"/>
       <c r="X11" s="219"/>
       <c r="Y11" s="219"/>
-      <c r="AJ11" s="252" t="s">
+      <c r="AJ11" s="285" t="s">
         <v>81</v>
       </c>
-      <c r="AK11" s="252"/>
-      <c r="AL11" s="252"/>
-      <c r="AM11" s="252"/>
+      <c r="AK11" s="285"/>
+      <c r="AL11" s="285"/>
+      <c r="AM11" s="285"/>
     </row>
     <row r="12" spans="1:39" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.15">
       <c r="J12" s="82">
@@ -28975,7 +28983,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="eid3QjEvP9P3RAZ+HGyMrnh+frY0qO+PHPMapaSCn/D/UGasX9GQYlPv6mYncUsizlxe04N+cCnpzYe1E9yn3w==" saltValue="Qjoxmnv8NKNqkdBgATyUZA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="tcpyr2AQS04rPtz4qlpykrIbOxHVvXHvswtzNDQGcxsZ5l8o9uA51dT8l+rl+/t+/k9iN9NhmVKNfkmPGtqcaw==" saltValue="lVHXu/m3fqcl0cfyq0L99w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="J11:L11"/>
     <mergeCell ref="W3:X3"/>
@@ -28987,10 +28995,10 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{ADD3407C-F48E-4B24-927E-D7A0BDE66701}"/>
     <hyperlink ref="B5" r:id="rId1" xr:uid="{936E9B21-1CA6-4114-BDC3-AD2DA0FD1494}"/>
     <hyperlink ref="B6" r:id="rId2" xr:uid="{15F0E12B-B65A-4566-8A17-8D60D2CA6517}"/>
     <hyperlink ref="B8" r:id="rId3" xr:uid="{09E62C2C-A0B2-439D-A8CE-8683510470C9}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{3698D814-C273-4D5A-910A-4F0A26D7C728}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId4"/>
@@ -31536,7 +31544,7 @@
     </row>
     <row r="42" spans="2:37" ht="23.45" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="mHT+oa+MFud6Vb/mTv/DYOir/zd2ZtJvFD1/IEZy7+L/rX5sYXEIIWQDaaTMyaU/UJK2shn0jI95HnEUCpnQLQ==" saltValue="4x3BLSnSV3JQzvpYzMwgBw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="WtLgu3qZIcB3HMbH5Uhgtnw8ZC9FmZPkwffZ75+Cu0xODZUFaLFBlMf2OUwp98Z9qj/SkB5LeQ9gkI3hJiFDbw==" saltValue="vPRJ/EvPcy+47tWk1I6w0w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="7">
     <mergeCell ref="X4:AB4"/>
     <mergeCell ref="AF33:AG33"/>
@@ -31574,7 +31582,7 @@
     <dataValidation imeMode="off" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L6:S13 F3:F4 H3:H4 X8:Y8 AA8 AA5:AA6 X5:Y6" xr:uid="{DF5F91E0-C653-4F0E-B693-F7405715B82B}"/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A1" location="コンテンツ!A1" display="[目次へ]" xr:uid="{C569BDA4-DF0A-4F08-8E1A-7B756F6E8F3E}"/>
+    <hyperlink ref="A1" location="目次!A1" display="[目次へ]" xr:uid="{4ECC500D-871A-47C5-B5BD-7CCF63BFC62E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31589,6 +31597,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100391FC4B48EFC574D8C7A2D40410158D5" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="e1796b3d6213ab423053a88e303c3cd0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="564c14fb-bfcd-4e52-83e8-2447e9c77f65" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e97de00b467dbc69daf19340855f519c" ns3:_="">
     <xsd:import namespace="564c14fb-bfcd-4e52-83e8-2447e9c77f65"/>
@@ -31778,15 +31795,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D9E7E2A7-086F-4414-A818-C355190A2115}">
   <ds:schemaRefs>
@@ -31804,6 +31812,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2764B03-5387-4537-A949-7B2C7AF6C83E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B8DD7E-13F6-4F5D-964D-0CB27623D7E4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -31820,12 +31836,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2764B03-5387-4537-A949-7B2C7AF6C83E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>